--- a/planilhas/Contratos de Locação.xlsx
+++ b/planilhas/Contratos de Locação.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$BJ$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$BJ$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$BJ$51</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="468">
   <si>
     <t>Contratos de Locação</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quinta-feira, 28 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em sábado, 6 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Ano Modelo</t>
@@ -250,7 +250,7 @@
     <t>LOC-1038-1/24</t>
   </si>
   <si>
-    <t>28</t>
+    <t>37</t>
   </si>
   <si>
     <t>41.153.812/0001-54</t>
@@ -295,822 +295,816 @@
     <t>TERCEIRIZAÇÃO DE FROTA</t>
   </si>
   <si>
+    <t>ATIVUZ VEÍCULOS</t>
+  </si>
+  <si>
+    <t>EGX-2E31</t>
+  </si>
+  <si>
+    <t>PRINCIPAL</t>
+  </si>
+  <si>
+    <t>9C2KD0810RR165173</t>
+  </si>
+  <si>
+    <t>LOC-1038-2/24</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>MOTO</t>
+  </si>
+  <si>
+    <t>NXR 160 BROS ESDD FLEXONE</t>
+  </si>
+  <si>
+    <t>1413837562</t>
+  </si>
+  <si>
+    <t>RQJ-7H29</t>
+  </si>
+  <si>
+    <t>9C2KC2500RR115224</t>
+  </si>
+  <si>
+    <t>LOC-1038-3/24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>CG 160 START</t>
+  </si>
+  <si>
+    <t>1412406037</t>
+  </si>
+  <si>
+    <t>RQI-7A69</t>
+  </si>
+  <si>
+    <t>9C2KC2500RR115213</t>
+  </si>
+  <si>
+    <t>LOC-1038-4/24</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1412409583</t>
+  </si>
+  <si>
+    <t>RQI-7A89</t>
+  </si>
+  <si>
+    <t>122.136.017-55</t>
+  </si>
+  <si>
+    <t>9BWAG45U9MT107528</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>CTO-1032</t>
+  </si>
+  <si>
+    <t>LOC-1032-1/1</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1253794178</t>
+  </si>
+  <si>
+    <t>84 99837-3901</t>
+  </si>
+  <si>
+    <t>PESSOA FÍSICA</t>
+  </si>
+  <si>
+    <t>MOTORISTA DE APLICATIVO</t>
+  </si>
+  <si>
+    <t>RGE-7H03</t>
+  </si>
+  <si>
+    <t>480.697.874-49</t>
+  </si>
+  <si>
+    <t>9BWDB45U5KT135660</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>CTO-1022</t>
+  </si>
+  <si>
+    <t>LOC-1022-1/4</t>
+  </si>
+  <si>
+    <t>SEDAN</t>
+  </si>
+  <si>
+    <t>VOYAGE 1.6 MSI FLEX 8V 4P</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1189763750</t>
+  </si>
+  <si>
+    <t>(84) 996369127</t>
+  </si>
+  <si>
+    <t>QGU-1H54</t>
+  </si>
+  <si>
+    <t>790.887.914-49</t>
+  </si>
+  <si>
+    <t>9BWDG45U1PT092539</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>CTO-1018</t>
+  </si>
+  <si>
+    <t>LOC-1018-1/2</t>
+  </si>
+  <si>
+    <t>VOYAGE 1.0 FLEX 12V 4P</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>01329662196</t>
+  </si>
+  <si>
+    <t>(84) 81731538</t>
+  </si>
+  <si>
+    <t>EMQ-6C26</t>
+  </si>
+  <si>
+    <t>009.554.944-78</t>
+  </si>
+  <si>
+    <t>9BWDG45U1PT010258</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>CTO-1023</t>
+  </si>
+  <si>
+    <t>LOC-1023-1/13</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>01298307187</t>
+  </si>
+  <si>
+    <t>84 99212-8471</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>GIY-6G96</t>
+  </si>
+  <si>
+    <t>117.936.764-29</t>
+  </si>
+  <si>
+    <t>9BWDG45U7PT091086</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>CTO-1016</t>
+  </si>
+  <si>
+    <t>LOC-1016-1/5</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1329648010</t>
+  </si>
+  <si>
+    <t>84 98890-2831</t>
+  </si>
+  <si>
+    <t>ECZ-8C02</t>
+  </si>
+  <si>
+    <t>101.093.374-41</t>
+  </si>
+  <si>
+    <t>9BWDG45U3PT091098</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>CTO-1011</t>
+  </si>
+  <si>
+    <t>LOC-1011-1/9</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1329647642</t>
+  </si>
+  <si>
+    <t>(84) 987180189</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>END-0I15</t>
+  </si>
+  <si>
+    <t>705.762.454-96</t>
+  </si>
+  <si>
+    <t>9BWDG45UXPT092720</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>CTO-1029</t>
+  </si>
+  <si>
+    <t>LOC-1029-1/2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1329889310</t>
+  </si>
+  <si>
+    <t>(84) 921697458</t>
+  </si>
+  <si>
+    <t>EXF-1F14</t>
+  </si>
+  <si>
+    <t>120.205.544-37</t>
+  </si>
+  <si>
+    <t>9BWAG45UXJT141960</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>CTO-1028</t>
+  </si>
+  <si>
+    <t>LOC-1028-1/8</t>
+  </si>
+  <si>
+    <t>GOL TRENDLINE 1.0 T.FLEX 12V 5P</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1149589393</t>
+  </si>
+  <si>
+    <t>84 99616-2852</t>
+  </si>
+  <si>
+    <t>QGX-7353</t>
+  </si>
+  <si>
+    <t>069.054.054-00</t>
+  </si>
+  <si>
+    <t>9BWDG45U8NT005796</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>CTO-1024</t>
+  </si>
+  <si>
+    <t>LOC-1024-1/7</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1253652063</t>
+  </si>
+  <si>
+    <t>(84) 981911956</t>
+  </si>
+  <si>
+    <t>RMK-2H75</t>
+  </si>
+  <si>
+    <t>071.198.454-97</t>
+  </si>
+  <si>
+    <t>9BWDB45U9KT124595</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>CTO-1015</t>
+  </si>
+  <si>
+    <t>LOC-1015-1/2</t>
+  </si>
+  <si>
+    <t>1190075218</t>
+  </si>
+  <si>
+    <t>(84) 981397610</t>
+  </si>
+  <si>
+    <t>QSE-8E63</t>
+  </si>
+  <si>
+    <t>017.712.914-00</t>
+  </si>
+  <si>
+    <t>9BWAG45U2KT043944</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>CTO-1019</t>
+  </si>
+  <si>
+    <t>LOC-1019-1/3</t>
+  </si>
+  <si>
+    <t>1164746763</t>
+  </si>
+  <si>
+    <t>(84) 921520363</t>
+  </si>
+  <si>
+    <t>QGN-9356</t>
+  </si>
+  <si>
+    <t>415.033.332-72</t>
+  </si>
+  <si>
+    <t>9BWAG45U8MT050030</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>CTO-1017</t>
+  </si>
+  <si>
+    <t>LOC-1017-1/2</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>1239198733</t>
+  </si>
+  <si>
+    <t>84 99639-9401</t>
+  </si>
+  <si>
+    <t>RGE-3I66</t>
+  </si>
+  <si>
+    <t>700.139.284-73</t>
+  </si>
+  <si>
+    <t>9BWAG45UXMT107456</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>CTO-1010</t>
+  </si>
+  <si>
+    <t>LOC-1010-1/9</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>1253118830</t>
+  </si>
+  <si>
+    <t>(84) 996939545</t>
+  </si>
+  <si>
+    <t>RGE-5D51</t>
+  </si>
+  <si>
+    <t>014.010.004-01</t>
+  </si>
+  <si>
+    <t>9BWAG45U6MT106935</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>CTO-1006</t>
+  </si>
+  <si>
+    <t>LOC-1006-1/12</t>
+  </si>
+  <si>
+    <t>EM MANUTENÇÃO</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1253913371</t>
+  </si>
+  <si>
+    <t>84 98651-5656</t>
+  </si>
+  <si>
+    <t>RGE-7G92</t>
+  </si>
+  <si>
+    <t>092.354.354-63</t>
+  </si>
+  <si>
+    <t>9BWDB45U1LT065429</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>CTO-1004</t>
+  </si>
+  <si>
+    <t>LOC-1004-1/5</t>
+  </si>
+  <si>
+    <t>1206436686</t>
+  </si>
+  <si>
+    <t>84 92148-9407</t>
+  </si>
+  <si>
+    <t>QGS-6G16</t>
+  </si>
+  <si>
+    <t>100.144.684-41</t>
+  </si>
+  <si>
+    <t>9BWDG45U2PT004842</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>BRYAN LEITE</t>
+  </si>
+  <si>
+    <t>CTO-1041</t>
+  </si>
+  <si>
+    <t>LOC-1041-1/12</t>
+  </si>
+  <si>
+    <t>01297099068</t>
+  </si>
+  <si>
+    <t>(84) 994770401</t>
+  </si>
+  <si>
+    <t>RUC-8C45</t>
+  </si>
+  <si>
+    <t>704.201.114-76</t>
+  </si>
+  <si>
+    <t>9BWDG45U2PT060313</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>CTO-1043</t>
+  </si>
+  <si>
+    <t>LOC-1043-1/12</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>1319762945</t>
+  </si>
+  <si>
+    <t>(84) 987574610</t>
+  </si>
+  <si>
+    <t>EVE-7G53</t>
+  </si>
+  <si>
+    <t>090.251.774-09</t>
+  </si>
+  <si>
+    <t>9BWDG45U7PT080055</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>CTO-1047</t>
+  </si>
+  <si>
+    <t>LOC-1047-1/12</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>1327877853</t>
+  </si>
+  <si>
+    <t>(84) 921482452</t>
+  </si>
+  <si>
+    <t>EJZ-3D41</t>
+  </si>
+  <si>
+    <t>104.338.594-07</t>
+  </si>
+  <si>
+    <t>9BWAG45U5MT005952</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>CTO-1049</t>
+  </si>
+  <si>
+    <t>LOC-1049-1/12</t>
+  </si>
+  <si>
+    <t>1225842287</t>
+  </si>
+  <si>
+    <t>(84) 987067181</t>
+  </si>
+  <si>
+    <t>QGT-9D76</t>
+  </si>
+  <si>
+    <t>033.444.532-97</t>
+  </si>
+  <si>
+    <t>9BWDG45U4PT034716</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>CTO-1051</t>
+  </si>
+  <si>
+    <t>LOC-1051-1/12</t>
+  </si>
+  <si>
+    <t>1303892356</t>
+  </si>
+  <si>
+    <t>(84) 991236644</t>
+  </si>
+  <si>
+    <t>EZY-6E03</t>
+  </si>
+  <si>
+    <t>720.839.894-14</t>
+  </si>
+  <si>
+    <t>9BWDG45U4PT003479</t>
+  </si>
+  <si>
+    <t>MILENA PORTILHA UGOLINI</t>
+  </si>
+  <si>
+    <t>CTO-1052</t>
+  </si>
+  <si>
+    <t>LOC-1052-1/3</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>01296669901</t>
+  </si>
+  <si>
+    <t>CARRO POR ASSINATURA</t>
+  </si>
+  <si>
+    <t>RUC-5C24</t>
+  </si>
+  <si>
+    <t>061.040.714-73</t>
+  </si>
+  <si>
+    <t>9BWDG45U0PT034373</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>CTO-1056</t>
+  </si>
+  <si>
+    <t>LOC-1056-1/12</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>1318410840</t>
+  </si>
+  <si>
+    <t>(84) 99263873</t>
+  </si>
+  <si>
+    <t>EWJ-2I45</t>
+  </si>
+  <si>
+    <t>9BWAG45UXMT107795</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>CTO-1060</t>
+  </si>
+  <si>
+    <t>LOC-1060-1/12</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>23.802.049/0001-63</t>
+  </si>
+  <si>
+    <t>1253120061</t>
+  </si>
+  <si>
+    <t>(84) 999250268</t>
+  </si>
+  <si>
+    <t>RGE-5D71</t>
+  </si>
+  <si>
+    <t>017.778.694-98</t>
+  </si>
+  <si>
+    <t>9BWDG45U5PT081673</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>CTO-1063</t>
+  </si>
+  <si>
+    <t>LOC-1063-1/12</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>01327467981</t>
+  </si>
+  <si>
+    <t>(84) 991660839</t>
+  </si>
+  <si>
+    <t>EFF-7I05</t>
+  </si>
+  <si>
+    <t>081.855.524-60</t>
+  </si>
+  <si>
+    <t>9BWAB45U9LT064192</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>CTO-1064</t>
+  </si>
+  <si>
+    <t>LOC-1064-1/12</t>
+  </si>
+  <si>
+    <t>1206038150</t>
+  </si>
+  <si>
+    <t>(84) 996176525</t>
+  </si>
+  <si>
+    <t>QGS-5J76</t>
+  </si>
+  <si>
+    <t>035.542.114-35</t>
+  </si>
+  <si>
+    <t>9BWAG5R19RT023738</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>KAROL MEDEIROS</t>
+  </si>
+  <si>
+    <t>CTO-1067</t>
+  </si>
+  <si>
+    <t>LOC-1067-1/12</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>POLO TRACK 1.0 FLEX 12V 5P</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>SSW-1A28</t>
+  </si>
+  <si>
+    <t>086.170.784-21</t>
+  </si>
+  <si>
+    <t>9BWDG45U2PT077211</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>CTO-1068</t>
+  </si>
+  <si>
+    <t>LOC-1068-1/12</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>1325953650</t>
+  </si>
+  <si>
     <t>CONFORME UNIDADE DO VEÍCULO</t>
   </si>
   <si>
-    <t>EGX-2E31</t>
-  </si>
-  <si>
-    <t>PRINCIPAL</t>
-  </si>
-  <si>
-    <t>9C2KD0810RR165173</t>
-  </si>
-  <si>
-    <t>LOC-1038-2/24</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>MOTO</t>
-  </si>
-  <si>
-    <t>NXR 160 BROS ESDD FLEXONE</t>
-  </si>
-  <si>
-    <t>1413837562</t>
-  </si>
-  <si>
-    <t>RQJ-7H29</t>
-  </si>
-  <si>
-    <t>9C2KC2500RR115224</t>
-  </si>
-  <si>
-    <t>LOC-1038-3/24</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>CG 160 START</t>
-  </si>
-  <si>
-    <t>1412406037</t>
-  </si>
-  <si>
-    <t>RQI-7A69</t>
-  </si>
-  <si>
-    <t>9C2KC2500RR115213</t>
-  </si>
-  <si>
-    <t>LOC-1038-4/24</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>1412409583</t>
-  </si>
-  <si>
-    <t>RQI-7A89</t>
-  </si>
-  <si>
-    <t>122.136.017-55</t>
-  </si>
-  <si>
-    <t>9BWAG45U9MT107528</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>CTO-1032</t>
-  </si>
-  <si>
-    <t>LOC-1032-1/1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1253794178</t>
-  </si>
-  <si>
-    <t>84 99837-3901</t>
-  </si>
-  <si>
-    <t>PESSOA FÍSICA</t>
-  </si>
-  <si>
-    <t>MOTORISTA DE APLICATIVO</t>
-  </si>
-  <si>
-    <t>ATIVUZ VEÍCULOS</t>
-  </si>
-  <si>
-    <t>RGE-7H03</t>
-  </si>
-  <si>
-    <t>480.697.874-49</t>
-  </si>
-  <si>
-    <t>9BWDB45U5KT135660</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>CTO-1022</t>
-  </si>
-  <si>
-    <t>LOC-1022-1/4</t>
-  </si>
-  <si>
-    <t>SEDAN</t>
-  </si>
-  <si>
-    <t>VOYAGE 1.6 MSI FLEX 8V 4P</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1189763750</t>
-  </si>
-  <si>
-    <t>(84) 996369127</t>
-  </si>
-  <si>
-    <t>QGU-1H54</t>
-  </si>
-  <si>
-    <t>790.887.914-49</t>
-  </si>
-  <si>
-    <t>9BWDG45U1PT092539</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>CTO-1018</t>
-  </si>
-  <si>
-    <t>LOC-1018-1/2</t>
-  </si>
-  <si>
-    <t>VOYAGE 1.0 FLEX 12V 4P</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>01329662196</t>
-  </si>
-  <si>
-    <t>(84) 81731538</t>
-  </si>
-  <si>
-    <t>EMQ-6C26</t>
-  </si>
-  <si>
-    <t>009.554.944-78</t>
-  </si>
-  <si>
-    <t>9BWDG45U1PT010258</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>CTO-1023</t>
-  </si>
-  <si>
-    <t>LOC-1023-1/13</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>01298307187</t>
-  </si>
-  <si>
-    <t>84 99212-8471</t>
-  </si>
-  <si>
-    <t>GIY-6G96</t>
-  </si>
-  <si>
-    <t>117.936.764-29</t>
-  </si>
-  <si>
-    <t>9BWDG45U7PT091086</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>CTO-1016</t>
-  </si>
-  <si>
-    <t>LOC-1016-1/5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>1329648010</t>
-  </si>
-  <si>
-    <t>84 98890-2831</t>
-  </si>
-  <si>
-    <t>ECZ-8C02</t>
-  </si>
-  <si>
-    <t>101.093.374-41</t>
-  </si>
-  <si>
-    <t>9BWDG45U3PT091098</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>CTO-1011</t>
-  </si>
-  <si>
-    <t>LOC-1011-1/9</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1329647642</t>
-  </si>
-  <si>
-    <t>(84) 987180189</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>END-0I15</t>
-  </si>
-  <si>
-    <t>705.762.454-96</t>
-  </si>
-  <si>
-    <t>9BWDG45UXPT092720</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>CTO-1029</t>
-  </si>
-  <si>
-    <t>LOC-1029-1/2</t>
-  </si>
-  <si>
-    <t>1329889310</t>
-  </si>
-  <si>
-    <t>(84) 921697458</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>EXF-1F14</t>
-  </si>
-  <si>
-    <t>120.205.544-37</t>
-  </si>
-  <si>
-    <t>9BWAG45UXJT141960</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>CTO-1028</t>
-  </si>
-  <si>
-    <t>LOC-1028-1/8</t>
-  </si>
-  <si>
-    <t>GOL TRENDLINE 1.0 T.FLEX 12V 5P</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>1149589393</t>
-  </si>
-  <si>
-    <t>84 99616-2852</t>
-  </si>
-  <si>
-    <t>QGX-7353</t>
-  </si>
-  <si>
-    <t>069.054.054-00</t>
-  </si>
-  <si>
-    <t>9BWDG45U8NT005796</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>CTO-1024</t>
-  </si>
-  <si>
-    <t>LOC-1024-1/7</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>1253652063</t>
-  </si>
-  <si>
-    <t>(84) 981911956</t>
-  </si>
-  <si>
-    <t>RMK-2H75</t>
-  </si>
-  <si>
-    <t>071.198.454-97</t>
-  </si>
-  <si>
-    <t>9BWDB45U9KT124595</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>CTO-1015</t>
-  </si>
-  <si>
-    <t>LOC-1015-1/2</t>
-  </si>
-  <si>
-    <t>1190075218</t>
-  </si>
-  <si>
-    <t>(84) 981397610</t>
-  </si>
-  <si>
-    <t>QSE-8E63</t>
-  </si>
-  <si>
-    <t>017.712.914-00</t>
-  </si>
-  <si>
-    <t>9BWAG45U2KT043944</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>CTO-1019</t>
-  </si>
-  <si>
-    <t>LOC-1019-1/3</t>
-  </si>
-  <si>
-    <t>1164746763</t>
-  </si>
-  <si>
-    <t>(84) 921520363</t>
-  </si>
-  <si>
-    <t>QGN-9356</t>
-  </si>
-  <si>
-    <t>966.730.874-04</t>
-  </si>
-  <si>
-    <t>9BWDG45U5NT045320</t>
-  </si>
-  <si>
-    <t>MARCELO BENTO DE ARAUJO</t>
-  </si>
-  <si>
-    <t>CTO-1013</t>
-  </si>
-  <si>
-    <t>LOC-1013-1/8</t>
-  </si>
-  <si>
-    <t>(84) 921505105</t>
-  </si>
-  <si>
-    <t>RNC-4J20</t>
-  </si>
-  <si>
-    <t>415.033.332-72</t>
-  </si>
-  <si>
-    <t>9BWAG45U8MT050030</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>CTO-1017</t>
-  </si>
-  <si>
-    <t>LOC-1017-1/2</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>1239198733</t>
-  </si>
-  <si>
-    <t>84 99639-9401</t>
-  </si>
-  <si>
-    <t>RGE-3I66</t>
-  </si>
-  <si>
-    <t>700.139.284-73</t>
-  </si>
-  <si>
-    <t>9BWAG45UXMT107456</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>CTO-1010</t>
-  </si>
-  <si>
-    <t>LOC-1010-1/9</t>
-  </si>
-  <si>
-    <t>1253118830</t>
-  </si>
-  <si>
-    <t>(84) 996939545</t>
-  </si>
-  <si>
-    <t>RGE-5D51</t>
-  </si>
-  <si>
-    <t>014.010.004-01</t>
-  </si>
-  <si>
-    <t>9BWAG45U6MT106935</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>CTO-1006</t>
-  </si>
-  <si>
-    <t>LOC-1006-1/12</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>1253913371</t>
-  </si>
-  <si>
-    <t>84 98651-5656</t>
-  </si>
-  <si>
-    <t>RGE-7G92</t>
-  </si>
-  <si>
-    <t>092.354.354-63</t>
-  </si>
-  <si>
-    <t>9BWDB45U1LT065429</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t>CTO-1004</t>
-  </si>
-  <si>
-    <t>LOC-1004-1/5</t>
-  </si>
-  <si>
-    <t>1206436686</t>
-  </si>
-  <si>
-    <t>84 92148-9407</t>
-  </si>
-  <si>
-    <t>QGS-6G16</t>
-  </si>
-  <si>
-    <t>100.144.684-41</t>
-  </si>
-  <si>
-    <t>9BWDG45U2PT004842</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>BRYAN LEITE</t>
-  </si>
-  <si>
-    <t>CTO-1041</t>
-  </si>
-  <si>
-    <t>LOC-1041-1/12</t>
-  </si>
-  <si>
-    <t>01297099068</t>
-  </si>
-  <si>
-    <t>(84) 994770401</t>
-  </si>
-  <si>
-    <t>RUC-8C45</t>
-  </si>
-  <si>
-    <t>704.201.114-76</t>
-  </si>
-  <si>
-    <t>9BWDG45U2PT060313</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>CTO-1043</t>
-  </si>
-  <si>
-    <t>LOC-1043-1/12</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>1319762945</t>
-  </si>
-  <si>
-    <t>(84) 987574610</t>
-  </si>
-  <si>
-    <t>EVE-7G53</t>
-  </si>
-  <si>
-    <t>090.251.774-09</t>
-  </si>
-  <si>
-    <t>9BWDG45U7PT080055</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>CTO-1047</t>
-  </si>
-  <si>
-    <t>LOC-1047-1/12</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>1327877853</t>
-  </si>
-  <si>
-    <t>(84) 921482452</t>
-  </si>
-  <si>
-    <t>EJZ-3D41</t>
-  </si>
-  <si>
-    <t>104.338.594-07</t>
-  </si>
-  <si>
-    <t>9BWAG45U5MT005952</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>CTO-1049</t>
-  </si>
-  <si>
-    <t>LOC-1049-1/12</t>
-  </si>
-  <si>
-    <t>1225842287</t>
-  </si>
-  <si>
-    <t>(84) 987067181</t>
-  </si>
-  <si>
-    <t>QGT-9D76</t>
-  </si>
-  <si>
-    <t>033.444.532-97</t>
-  </si>
-  <si>
-    <t>9BWDG45U4PT034716</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>CTO-1051</t>
-  </si>
-  <si>
-    <t>LOC-1051-1/12</t>
-  </si>
-  <si>
-    <t>1303892356</t>
-  </si>
-  <si>
-    <t>(84) 991236644</t>
-  </si>
-  <si>
-    <t>EZY-6E03</t>
-  </si>
-  <si>
-    <t>720.839.894-14</t>
-  </si>
-  <si>
-    <t>9BWDG45U4PT003479</t>
-  </si>
-  <si>
-    <t>MILENA PORTILHA UGOLINI</t>
-  </si>
-  <si>
-    <t>CTO-1052</t>
-  </si>
-  <si>
-    <t>LOC-1052-1/3</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>01296669901</t>
-  </si>
-  <si>
-    <t>CARRO POR ASSINATURA</t>
-  </si>
-  <si>
-    <t>RUC-5C24</t>
-  </si>
-  <si>
-    <t>061.040.714-73</t>
-  </si>
-  <si>
-    <t>9BWDG45U0PT034373</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>CTO-1056</t>
-  </si>
-  <si>
-    <t>LOC-1056-1/12</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>1318410840</t>
-  </si>
-  <si>
-    <t>(84) 99263873</t>
-  </si>
-  <si>
-    <t>EWJ-2I45</t>
-  </si>
-  <si>
-    <t>9BWAG45UXMT107795</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>CTO-1060</t>
-  </si>
-  <si>
-    <t>LOC-1060-1/12</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>23.802.049/0001-63</t>
-  </si>
-  <si>
-    <t>1253120061</t>
-  </si>
-  <si>
-    <t>(84) 999250268</t>
-  </si>
-  <si>
-    <t>RGE-5D71</t>
-  </si>
-  <si>
-    <t>017.778.694-98</t>
-  </si>
-  <si>
-    <t>9BWDG45U5PT081673</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>CTO-1063</t>
-  </si>
-  <si>
-    <t>LOC-1063-1/12</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>01327467981</t>
-  </si>
-  <si>
-    <t>(84) 991660839</t>
-  </si>
-  <si>
-    <t>EFF-7I05</t>
-  </si>
-  <si>
-    <t>081.855.524-60</t>
-  </si>
-  <si>
-    <t>9BWAB45U9LT064192</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>CTO-1064</t>
-  </si>
-  <si>
-    <t>LOC-1064-1/12</t>
-  </si>
-  <si>
-    <t>1206038150</t>
-  </si>
-  <si>
-    <t>(84) 996176525</t>
-  </si>
-  <si>
-    <t>QGS-5J76</t>
-  </si>
-  <si>
-    <t>035.542.114-35</t>
-  </si>
-  <si>
-    <t>9BWAG5R19RT023738</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>KAROL MEDEIROS</t>
-  </si>
-  <si>
-    <t>CTO-1067</t>
-  </si>
-  <si>
-    <t>LOC-1067-1/12</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>POLO TRACK 1.0 FLEX 12V 5P</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>SSW-1A28</t>
-  </si>
-  <si>
-    <t>086.170.784-21</t>
-  </si>
-  <si>
-    <t>9BWDG45U2PT077211</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>CTO-1068</t>
-  </si>
-  <si>
-    <t>LOC-1068-1/12</t>
-  </si>
-  <si>
-    <t>1325953650</t>
-  </si>
-  <si>
     <t>ECM-1C93</t>
   </si>
   <si>
@@ -1129,9 +1123,6 @@
     <t>LOC-1070-1/12</t>
   </si>
   <si>
-    <t>EM MANUTENÇÃO</t>
-  </si>
-  <si>
     <t>1207486415</t>
   </si>
   <si>
@@ -1195,7 +1186,7 @@
     <t>LOC-1075-1/12</t>
   </si>
   <si>
-    <t>22</t>
+    <t>31</t>
   </si>
   <si>
     <t>DOLPHIN MINI (ELÉTRICO)</t>
@@ -1270,7 +1261,7 @@
     <t>LOC-1078-1/12</t>
   </si>
   <si>
-    <t>17</t>
+    <t>26</t>
   </si>
   <si>
     <t>GOL (NOVO) 1.6 MI TOTAL FLEX 8V 4P</t>
@@ -1342,6 +1333,9 @@
     <t>LOC-1079-1/12</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>01489397822</t>
   </si>
   <si>
@@ -1433,9 +1427,6 @@
   </si>
   <si>
     <t>LOC-1084-1/8</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>1327460677</t>
@@ -1571,10 +1562,10 @@
     <xf numFmtId="10" applyNumberFormat="1" fontId="5" applyFont="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="1" applyNumberFormat="1" fontId="4" applyFont="1" fillId="3" applyFill="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="1" applyNumberFormat="1" fontId="4" applyFont="1" fillId="3" applyFill="1" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="3" applyFill="1" xfId="0" applyAlignment="1">
@@ -1600,71 +1591,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:BJ52"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:BJ51"/>
+  <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.267584800720215" customWidth="1" style="1"/>
-    <col min="2" max="2" width="20.137897491455078" customWidth="1" style="1"/>
-    <col min="3" max="3" width="16.17369842529297" customWidth="1" style="1"/>
-    <col min="4" max="4" width="17.892821311950684" customWidth="1" style="1"/>
-    <col min="5" max="5" width="23.430490493774414" customWidth="1" style="1"/>
-    <col min="6" max="6" width="26.36599349975586" customWidth="1" style="1"/>
-    <col min="7" max="7" width="43.70395278930664" customWidth="1" style="1"/>
-    <col min="8" max="8" width="32.26651573181152" customWidth="1" style="1"/>
-    <col min="9" max="9" width="32.580657958984375" customWidth="1" style="1"/>
-    <col min="10" max="10" width="21.04229164123535" customWidth="1" style="1"/>
-    <col min="11" max="11" width="31.881608963012695" customWidth="1" style="1"/>
-    <col min="12" max="12" width="21.047510147094727" customWidth="1" style="1"/>
-    <col min="13" max="13" width="21.944995880126953" customWidth="1" style="1"/>
-    <col min="14" max="14" width="21.430696487426758" customWidth="1" style="1"/>
-    <col min="15" max="15" width="21.833349227905273" customWidth="1" style="1"/>
-    <col min="16" max="16" width="18.172935485839844" customWidth="1" style="1"/>
-    <col min="17" max="17" width="17.789782524108887" customWidth="1" style="1"/>
-    <col min="18" max="18" width="20.88944435119629" customWidth="1" style="1"/>
-    <col min="19" max="19" width="20.376359939575195" customWidth="1" style="1"/>
-    <col min="20" max="20" width="20.333646774291992" customWidth="1" style="1"/>
-    <col min="21" max="21" width="17.95619773864746" customWidth="1" style="1"/>
-    <col min="22" max="22" width="41.808128356933594" customWidth="1" style="1"/>
-    <col min="23" max="23" width="24.719308853149414" customWidth="1" style="1"/>
-    <col min="24" max="24" width="22.13438606262207" customWidth="1" style="1"/>
-    <col min="25" max="25" width="19.504261016845703" customWidth="1" style="1"/>
-    <col min="26" max="26" width="15" customWidth="1" style="1"/>
-    <col min="27" max="27" width="15" customWidth="1" style="1"/>
+    <col min="1" max="1" width="12" customWidth="1" style="1"/>
+    <col min="2" max="2" width="19" customWidth="1" style="1"/>
+    <col min="3" max="3" width="16" customWidth="1" style="1"/>
+    <col min="4" max="4" width="21" customWidth="1" style="1"/>
+    <col min="5" max="5" width="19" customWidth="1" style="1"/>
+    <col min="6" max="6" width="27" customWidth="1" style="1"/>
+    <col min="7" max="7" width="38" customWidth="1" style="1"/>
+    <col min="8" max="8" width="31" customWidth="1" style="1"/>
+    <col min="9" max="9" width="32" customWidth="1" style="1"/>
+    <col min="10" max="10" width="20" customWidth="1" style="1"/>
+    <col min="11" max="11" width="31" customWidth="1" style="1"/>
+    <col min="12" max="12" width="20" customWidth="1" style="1"/>
+    <col min="13" max="13" width="21" customWidth="1" style="1"/>
+    <col min="14" max="14" width="20" customWidth="1" style="1"/>
+    <col min="15" max="15" width="20" customWidth="1" style="1"/>
+    <col min="16" max="16" width="21" customWidth="1" style="1"/>
+    <col min="17" max="17" width="21" customWidth="1" style="1"/>
+    <col min="18" max="18" width="22" customWidth="1" style="1"/>
+    <col min="19" max="19" width="21" customWidth="1" style="1"/>
+    <col min="20" max="20" width="20" customWidth="1" style="1"/>
+    <col min="21" max="21" width="17" customWidth="1" style="1"/>
+    <col min="22" max="22" width="33" customWidth="1" style="1"/>
+    <col min="23" max="23" width="23" customWidth="1" style="1"/>
+    <col min="24" max="24" width="21" customWidth="1" style="1"/>
+    <col min="25" max="25" width="17" customWidth="1" style="1"/>
+    <col min="26" max="26" width="18" customWidth="1" style="1"/>
+    <col min="27" max="27" width="17" customWidth="1" style="1"/>
     <col min="28" max="28" width="15" customWidth="1" style="1"/>
-    <col min="29" max="29" width="9.484076499938965" customWidth="1" style="1"/>
-    <col min="30" max="30" width="19.70718765258789" customWidth="1" style="1"/>
-    <col min="31" max="31" width="19.67469596862793" customWidth="1" style="1"/>
-    <col min="32" max="32" width="17.599953651428223" customWidth="1" style="1"/>
-    <col min="33" max="33" width="20.800935745239258" customWidth="1" style="1"/>
-    <col min="34" max="34" width="16.33533477783203" customWidth="1" style="1"/>
-    <col min="35" max="35" width="23.47739028930664" customWidth="1" style="1"/>
-    <col min="36" max="36" width="31.531396865844727" customWidth="1" style="1"/>
-    <col min="37" max="37" width="36.26475524902344" customWidth="1" style="1"/>
-    <col min="38" max="38" width="43.70395278930664" customWidth="1" style="1"/>
-    <col min="39" max="39" width="35.66214370727539" customWidth="1" style="1"/>
-    <col min="40" max="40" width="33.07217216491699" customWidth="1" style="1"/>
-    <col min="41" max="41" width="29.473464965820312" customWidth="1" style="1"/>
-    <col min="42" max="42" width="18.11282253265381" customWidth="1" style="1"/>
+    <col min="29" max="29" width="10" customWidth="1" style="1"/>
+    <col min="30" max="30" width="17" customWidth="1" style="1"/>
+    <col min="31" max="31" width="21" customWidth="1" style="1"/>
+    <col min="32" max="32" width="15" customWidth="1" style="1"/>
+    <col min="33" max="33" width="21" customWidth="1" style="1"/>
+    <col min="34" max="34" width="14" customWidth="1" style="1"/>
+    <col min="35" max="35" width="24" customWidth="1" style="1"/>
+    <col min="36" max="36" width="33" customWidth="1" style="1"/>
+    <col min="37" max="37" width="36" customWidth="1" style="1"/>
+    <col min="38" max="38" width="38" customWidth="1" style="1"/>
+    <col min="39" max="39" width="35" customWidth="1" style="1"/>
+    <col min="40" max="40" width="33" customWidth="1" style="1"/>
+    <col min="41" max="41" width="27" customWidth="1" style="1"/>
+    <col min="42" max="42" width="17" customWidth="1" style="1"/>
     <col min="43" max="43" width="15" customWidth="1" style="1"/>
-    <col min="44" max="44" width="12.840845108032227" customWidth="1" style="1"/>
-    <col min="45" max="45" width="13.953447341918945" customWidth="1" style="1"/>
-    <col min="46" max="46" width="22.284286499023438" customWidth="1" style="1"/>
-    <col min="47" max="47" width="16.874731063842773" customWidth="1" style="1"/>
-    <col min="48" max="48" width="26.31397819519043" customWidth="1" style="1"/>
-    <col min="49" max="49" width="20.376461029052734" customWidth="1" style="1"/>
-    <col min="50" max="50" width="17.21027946472168" customWidth="1" style="1"/>
-    <col min="51" max="51" width="26.941875457763672" customWidth="1" style="1"/>
-    <col min="52" max="52" width="16.648768424987793" customWidth="1" style="1"/>
-    <col min="53" max="53" width="18.84095573425293" customWidth="1" style="1"/>
-    <col min="54" max="54" width="22.72743797302246" customWidth="1" style="1"/>
-    <col min="55" max="55" width="33.940982818603516" customWidth="1" style="1"/>
-    <col min="56" max="56" width="15" customWidth="1" style="1"/>
-    <col min="57" max="57" width="15" customWidth="1" style="1"/>
-    <col min="58" max="58" width="15" customWidth="1" style="1"/>
-    <col min="59" max="59" width="15" customWidth="1" style="1"/>
-    <col min="60" max="60" width="15.586050987243652" customWidth="1" style="1"/>
-    <col min="61" max="61" width="18.183012008666992" customWidth="1" style="1"/>
-    <col min="62" max="62" width="21.558679580688477" customWidth="1" style="1"/>
+    <col min="44" max="44" width="10" customWidth="1" style="1"/>
+    <col min="45" max="45" width="13" customWidth="1" style="1"/>
+    <col min="46" max="46" width="19" customWidth="1" style="1"/>
+    <col min="47" max="47" width="14" customWidth="1" style="1"/>
+    <col min="48" max="48" width="25" customWidth="1" style="1"/>
+    <col min="49" max="49" width="21" customWidth="1" style="1"/>
+    <col min="50" max="50" width="17" customWidth="1" style="1"/>
+    <col min="51" max="51" width="25" customWidth="1" style="1"/>
+    <col min="52" max="52" width="17" customWidth="1" style="1"/>
+    <col min="53" max="53" width="21" customWidth="1" style="1"/>
+    <col min="54" max="54" width="21" customWidth="1" style="1"/>
+    <col min="55" max="55" width="29" customWidth="1" style="1"/>
+    <col min="56" max="56" width="25" customWidth="1" style="1"/>
+    <col min="57" max="57" width="28" customWidth="1" style="1"/>
+    <col min="58" max="58" width="26" customWidth="1" style="1"/>
+    <col min="59" max="59" width="26" customWidth="1" style="1"/>
+    <col min="60" max="60" width="15" customWidth="1" style="1"/>
+    <col min="61" max="61" width="19" customWidth="1" style="1"/>
+    <col min="62" max="62" width="21" customWidth="1" style="1"/>
     <col min="63" max="16384" width="9.140625" customWidth="1" style="1"/>
   </cols>
   <sheetData>
@@ -1872,7 +1863,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" ht="23" customHeight="1">
+    <row r="6">
       <c r="A6" s="7">
         <v>2023</v>
       </c>
@@ -1967,10 +1958,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF6" s="7">
-        <v>83104</v>
+        <v>83783</v>
       </c>
       <c r="AG6" s="9">
-        <v>46168.634791666664</v>
+        <v>46175.35753472222</v>
       </c>
       <c r="AH6" s="6" t="s">
         <v>77</v>
@@ -2009,7 +2000,7 @@
         <v>81</v>
       </c>
       <c r="AT6" s="7">
-        <v>4299</v>
+        <v>4268</v>
       </c>
       <c r="AU6" s="6" t="s">
         <v>82</v>
@@ -2060,7 +2051,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" ht="23" customHeight="1">
+    <row r="7">
       <c r="A7" s="7">
         <v>2024</v>
       </c>
@@ -2155,10 +2146,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF7" s="7">
-        <v>29989</v>
+        <v>30242</v>
       </c>
       <c r="AG7" s="9">
-        <v>46168.63483796296</v>
+        <v>46175.35753472222</v>
       </c>
       <c r="AH7" s="6" t="s">
         <v>77</v>
@@ -2197,7 +2188,7 @@
         <v>95</v>
       </c>
       <c r="AT7" s="7">
-        <v>1551</v>
+        <v>1540</v>
       </c>
       <c r="AU7" s="6" t="s">
         <v>82</v>
@@ -2248,7 +2239,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" ht="23" customHeight="1">
+    <row r="8">
       <c r="A8" s="7">
         <v>2024</v>
       </c>
@@ -2343,10 +2334,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF8" s="7">
-        <v>18313</v>
+        <v>18462</v>
       </c>
       <c r="AG8" s="9">
-        <v>46168.63483796296</v>
+        <v>46175.35753472222</v>
       </c>
       <c r="AH8" s="6" t="s">
         <v>77</v>
@@ -2385,7 +2376,7 @@
         <v>101</v>
       </c>
       <c r="AT8" s="7">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="AU8" s="6" t="s">
         <v>82</v>
@@ -2436,7 +2427,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" ht="23" customHeight="1">
+    <row r="9">
       <c r="A9" s="7">
         <v>2024</v>
       </c>
@@ -2513,13 +2504,13 @@
         <v>75</v>
       </c>
       <c r="Z9" s="10">
-        <v>65.58</v>
+        <v>98.37</v>
       </c>
       <c r="AA9" s="10">
         <v>0</v>
       </c>
       <c r="AB9" s="10">
-        <v>65.58</v>
+        <v>98.37</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>93</v>
@@ -2531,10 +2522,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF9" s="7">
-        <v>14769</v>
+        <v>15278</v>
       </c>
       <c r="AG9" s="9">
-        <v>46160.497662037036</v>
+        <v>46176.41266203704</v>
       </c>
       <c r="AH9" s="6" t="s">
         <v>77</v>
@@ -2573,7 +2564,7 @@
         <v>106</v>
       </c>
       <c r="AT9" s="7">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="AU9" s="6" t="s">
         <v>82</v>
@@ -2624,7 +2615,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" ht="23" customHeight="1">
+    <row r="10">
       <c r="A10" s="7">
         <v>2021</v>
       </c>
@@ -2719,10 +2710,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF10" s="7">
-        <v>176153</v>
+        <v>176690</v>
       </c>
       <c r="AG10" s="9">
-        <v>46168.63482638889</v>
+        <v>46175.35753472222</v>
       </c>
       <c r="AH10" s="6" t="s">
         <v>65</v>
@@ -2761,7 +2752,7 @@
         <v>115</v>
       </c>
       <c r="AT10" s="7">
-        <v>2682</v>
+        <v>2655</v>
       </c>
       <c r="AU10" s="6" t="s">
         <v>82</v>
@@ -2788,7 +2779,7 @@
         <v>65</v>
       </c>
       <c r="BC10" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD10" s="10">
         <v>0</v>
@@ -2803,16 +2794,16 @@
         <v>620</v>
       </c>
       <c r="BH10" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BI10" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ10" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="11" ht="23" customHeight="1">
+    <row r="11">
       <c r="A11" s="7">
         <v>2019</v>
       </c>
@@ -2820,19 +2811,19 @@
         <v>2019</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>65</v>
@@ -2841,7 +2832,7 @@
         <v>68</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>68</v>
@@ -2850,7 +2841,7 @@
         <v>65</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N11" s="6" t="s">
         <v>65</v>
@@ -2871,7 +2862,7 @@
         <v>113</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U11" s="6" t="s">
         <v>65</v>
@@ -2898,7 +2889,7 @@
         <v>1190.42</v>
       </c>
       <c r="AC11" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD11" s="6" t="s">
         <v>65</v>
@@ -2907,10 +2898,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF11" s="7">
-        <v>271441</v>
+        <v>273298</v>
       </c>
       <c r="AG11" s="9">
-        <v>46168.63481481482</v>
+        <v>46175.357523148145</v>
       </c>
       <c r="AH11" s="6" t="s">
         <v>65</v>
@@ -2922,34 +2913,34 @@
         <v>0.014823529411764</v>
       </c>
       <c r="AK11" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL11" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="AM11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP11" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="AL11" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="AM11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP11" s="6" t="s">
+      <c r="AQ11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS11" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="AQ11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS11" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="AT11" s="7">
-        <v>18760</v>
+        <v>18390</v>
       </c>
       <c r="AU11" s="6" t="s">
         <v>82</v>
@@ -2958,7 +2949,7 @@
         <v>83</v>
       </c>
       <c r="AW11" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AX11" s="6" t="s">
         <v>117</v>
@@ -2976,7 +2967,7 @@
         <v>65</v>
       </c>
       <c r="BC11" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD11" s="10">
         <v>0</v>
@@ -2991,16 +2982,16 @@
         <v>630</v>
       </c>
       <c r="BH11" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BI11" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BJ11" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="12" ht="23" customHeight="1">
+    <row r="12">
       <c r="A12" s="7">
         <v>2023</v>
       </c>
@@ -3008,19 +2999,19 @@
         <v>2022</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>65</v>
@@ -3029,7 +3020,7 @@
         <v>68</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>68</v>
@@ -3038,7 +3029,7 @@
         <v>65</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>65</v>
@@ -3059,7 +3050,7 @@
         <v>72</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="U12" s="6" t="s">
         <v>65</v>
@@ -3086,7 +3077,7 @@
         <v>766.78</v>
       </c>
       <c r="AC12" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD12" s="6" t="s">
         <v>65</v>
@@ -3095,10 +3086,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF12" s="7">
-        <v>87341</v>
+        <v>88758</v>
       </c>
       <c r="AG12" s="9">
-        <v>46168.634791666664</v>
+        <v>46175.3575</v>
       </c>
       <c r="AH12" s="6" t="s">
         <v>65</v>
@@ -3110,34 +3101,34 @@
         <v>0</v>
       </c>
       <c r="AK12" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL12" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AM12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP12" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AL12" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP12" s="6" t="s">
+      <c r="AQ12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS12" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="AQ12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS12" s="6" t="s">
-        <v>139</v>
-      </c>
       <c r="AT12" s="7">
-        <v>18000</v>
+        <v>16640</v>
       </c>
       <c r="AU12" s="6" t="s">
         <v>82</v>
@@ -3146,7 +3137,7 @@
         <v>83</v>
       </c>
       <c r="AW12" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AX12" s="6" t="s">
         <v>117</v>
@@ -3164,7 +3155,7 @@
         <v>65</v>
       </c>
       <c r="BC12" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD12" s="10">
         <v>0</v>
@@ -3179,16 +3170,16 @@
         <v>600</v>
       </c>
       <c r="BH12" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BI12" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BJ12" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" ht="23" customHeight="1">
+    <row r="13">
       <c r="A13" s="7">
         <v>2023</v>
       </c>
@@ -3196,19 +3187,19 @@
         <v>2022</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="F13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>65</v>
@@ -3217,7 +3208,7 @@
         <v>68</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>68</v>
@@ -3226,7 +3217,7 @@
         <v>65</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N13" s="6" t="s">
         <v>65</v>
@@ -3244,10 +3235,10 @@
         <v>65</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="U13" s="6" t="s">
         <v>65</v>
@@ -3274,7 +3265,7 @@
         <v>390.72</v>
       </c>
       <c r="AC13" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD13" s="6" t="s">
         <v>65</v>
@@ -3283,10 +3274,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF13" s="7">
-        <v>100431</v>
+        <v>101633</v>
       </c>
       <c r="AG13" s="9">
-        <v>46168.63480324074</v>
+        <v>46175.357511574075</v>
       </c>
       <c r="AH13" s="6" t="s">
         <v>65</v>
@@ -3298,10 +3289,10 @@
         <v>0</v>
       </c>
       <c r="AK13" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AL13" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AM13" s="6" t="s">
         <v>65</v>
@@ -3313,7 +3304,7 @@
         <v>65</v>
       </c>
       <c r="AP13" s="6" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="AQ13" s="10" t="s">
         <v>65</v>
@@ -3325,7 +3316,7 @@
         <v>148</v>
       </c>
       <c r="AT13" s="7">
-        <v>25179</v>
+        <v>22826</v>
       </c>
       <c r="AU13" s="6" t="s">
         <v>82</v>
@@ -3346,13 +3337,13 @@
         <v>65</v>
       </c>
       <c r="BA13" s="8">
-        <v>46174.99998842592</v>
+        <v>46202.99998842592</v>
       </c>
       <c r="BB13" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC13" s="6" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="BD13" s="10" t="s">
         <v>65</v>
@@ -3367,16 +3358,16 @@
         <v>620</v>
       </c>
       <c r="BH13" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BI13" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BJ13" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" ht="23" customHeight="1">
+    <row r="14">
       <c r="A14" s="7">
         <v>2023</v>
       </c>
@@ -3384,19 +3375,19 @@
         <v>2022</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>65</v>
@@ -3405,7 +3396,7 @@
         <v>68</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>68</v>
@@ -3414,7 +3405,7 @@
         <v>65</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N14" s="6" t="s">
         <v>65</v>
@@ -3435,7 +3426,7 @@
         <v>72</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="U14" s="6" t="s">
         <v>65</v>
@@ -3462,7 +3453,7 @@
         <v>2155.84</v>
       </c>
       <c r="AC14" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD14" s="6" t="s">
         <v>65</v>
@@ -3471,10 +3462,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF14" s="7">
-        <v>147702</v>
+        <v>148702</v>
       </c>
       <c r="AG14" s="9">
-        <v>46168.634780092594</v>
+        <v>46175.35748842593</v>
       </c>
       <c r="AH14" s="6" t="s">
         <v>65</v>
@@ -3486,10 +3477,10 @@
         <v>650</v>
       </c>
       <c r="AK14" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AL14" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM14" s="6" t="s">
         <v>65</v>
@@ -3501,7 +3492,7 @@
         <v>65</v>
       </c>
       <c r="AP14" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AQ14" s="10" t="s">
         <v>65</v>
@@ -3510,10 +3501,10 @@
         <v>65</v>
       </c>
       <c r="AS14" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AT14" s="7">
-        <v>7332</v>
+        <v>7214</v>
       </c>
       <c r="AU14" s="6" t="s">
         <v>82</v>
@@ -3522,7 +3513,7 @@
         <v>83</v>
       </c>
       <c r="AW14" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AX14" s="6" t="s">
         <v>117</v>
@@ -3534,13 +3525,13 @@
         <v>65</v>
       </c>
       <c r="BA14" s="8">
-        <v>46174.99998842592</v>
+        <v>46195.458333333336</v>
       </c>
       <c r="BB14" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC14" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD14" s="10" t="s">
         <v>65</v>
@@ -3555,16 +3546,16 @@
         <v>650</v>
       </c>
       <c r="BH14" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BI14" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BJ14" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="15" ht="23" customHeight="1">
+    <row r="15">
       <c r="A15" s="7">
         <v>2023</v>
       </c>
@@ -3572,19 +3563,19 @@
         <v>2022</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D15" s="8">
         <v>45854.96678059028</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>65</v>
@@ -3593,7 +3584,7 @@
         <v>68</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>68</v>
@@ -3602,7 +3593,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>65</v>
@@ -3620,10 +3611,10 @@
         <v>65</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>65</v>
@@ -3650,7 +3641,7 @@
         <v>433.8</v>
       </c>
       <c r="AC15" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD15" s="6" t="s">
         <v>65</v>
@@ -3659,10 +3650,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF15" s="7">
-        <v>128145</v>
+        <v>129783</v>
       </c>
       <c r="AG15" s="9">
-        <v>46170.3549537037</v>
+        <v>46175.3575</v>
       </c>
       <c r="AH15" s="6" t="s">
         <v>65</v>
@@ -3674,10 +3665,10 @@
         <v>0.014028056112224</v>
       </c>
       <c r="AK15" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AL15" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM15" s="6" t="s">
         <v>65</v>
@@ -3701,7 +3692,7 @@
         <v>167</v>
       </c>
       <c r="AT15" s="7">
-        <v>-13378</v>
+        <v>-11572</v>
       </c>
       <c r="AU15" s="6" t="s">
         <v>82</v>
@@ -3722,13 +3713,13 @@
         <v>169</v>
       </c>
       <c r="BA15" s="8">
-        <v>46174.99998842592</v>
+        <v>46202.99998842592</v>
       </c>
       <c r="BB15" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC15" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD15" s="10">
         <v>0</v>
@@ -3752,7 +3743,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" ht="23" customHeight="1">
+    <row r="16">
       <c r="A16" s="7">
         <v>2023</v>
       </c>
@@ -3838,7 +3829,7 @@
         <v>299.75</v>
       </c>
       <c r="AC16" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD16" s="6" t="s">
         <v>65</v>
@@ -3847,10 +3838,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF16" s="7">
-        <v>119855</v>
+        <v>121204</v>
       </c>
       <c r="AG16" s="9">
-        <v>46168.634791666664</v>
+        <v>46175.3575</v>
       </c>
       <c r="AH16" s="6" t="s">
         <v>65</v>
@@ -3862,7 +3853,7 @@
         <v>0.014605100550499</v>
       </c>
       <c r="AK16" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AL16" s="6" t="s">
         <v>173</v>
@@ -3877,7 +3868,7 @@
         <v>65</v>
       </c>
       <c r="AP16" s="6" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="AQ16" s="10" t="s">
         <v>65</v>
@@ -3886,10 +3877,10 @@
         <v>65</v>
       </c>
       <c r="AS16" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AT16" s="7">
-        <v>5297</v>
+        <v>5274</v>
       </c>
       <c r="AU16" s="6" t="s">
         <v>82</v>
@@ -3898,7 +3889,7 @@
         <v>83</v>
       </c>
       <c r="AW16" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AX16" s="6" t="s">
         <v>117</v>
@@ -3916,7 +3907,7 @@
         <v>65</v>
       </c>
       <c r="BC16" s="6" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="BD16" s="10" t="s">
         <v>65</v>
@@ -3940,7 +3931,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" ht="23" customHeight="1">
+    <row r="17">
       <c r="A17" s="7">
         <v>2018</v>
       </c>
@@ -4035,10 +4026,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF17" s="7">
-        <v>178239</v>
+        <v>179292</v>
       </c>
       <c r="AG17" s="9">
-        <v>46168.63481481482</v>
+        <v>46175.357523148145</v>
       </c>
       <c r="AH17" s="6" t="s">
         <v>65</v>
@@ -4077,7 +4068,7 @@
         <v>187</v>
       </c>
       <c r="AT17" s="7">
-        <v>7657</v>
+        <v>7535</v>
       </c>
       <c r="AU17" s="6" t="s">
         <v>82</v>
@@ -4098,13 +4089,13 @@
         <v>65</v>
       </c>
       <c r="BA17" s="8">
-        <v>46174.99998842592</v>
+        <v>46202.99998842592</v>
       </c>
       <c r="BB17" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC17" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD17" s="10">
         <v>0</v>
@@ -4128,7 +4119,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" ht="23" customHeight="1">
+    <row r="18">
       <c r="A18" s="7">
         <v>2022</v>
       </c>
@@ -4184,7 +4175,7 @@
         <v>65</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T18" s="6" t="s">
         <v>190</v>
@@ -4214,7 +4205,7 @@
         <v>1039.98</v>
       </c>
       <c r="AC18" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD18" s="6" t="s">
         <v>65</v>
@@ -4223,10 +4214,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF18" s="7">
-        <v>186140</v>
+        <v>187088</v>
       </c>
       <c r="AG18" s="9">
-        <v>46168.63482638889</v>
+        <v>46175.35753472222</v>
       </c>
       <c r="AH18" s="6" t="s">
         <v>65</v>
@@ -4238,7 +4229,7 @@
         <v>0.013846153846153</v>
       </c>
       <c r="AK18" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AL18" s="6" t="s">
         <v>192</v>
@@ -4265,7 +4256,7 @@
         <v>196</v>
       </c>
       <c r="AT18" s="7">
-        <v>11361</v>
+        <v>11120</v>
       </c>
       <c r="AU18" s="6" t="s">
         <v>82</v>
@@ -4292,7 +4283,7 @@
         <v>65</v>
       </c>
       <c r="BC18" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD18" s="10">
         <v>0</v>
@@ -4316,7 +4307,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" ht="23" customHeight="1">
+    <row r="19">
       <c r="A19" s="7">
         <v>2019</v>
       </c>
@@ -4372,7 +4363,7 @@
         <v>65</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T19" s="6" t="s">
         <v>199</v>
@@ -4402,7 +4393,7 @@
         <v>2430.95</v>
       </c>
       <c r="AC19" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD19" s="6" t="s">
         <v>65</v>
@@ -4411,10 +4402,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF19" s="7">
-        <v>238739</v>
+        <v>239800</v>
       </c>
       <c r="AG19" s="9">
-        <v>46168.63482638889</v>
+        <v>46175.357523148145</v>
       </c>
       <c r="AH19" s="6" t="s">
         <v>65</v>
@@ -4426,7 +4417,7 @@
         <v>0.01575</v>
       </c>
       <c r="AK19" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AL19" s="6" t="s">
         <v>201</v>
@@ -4441,7 +4432,7 @@
         <v>65</v>
       </c>
       <c r="AP19" s="6" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="AQ19" s="10" t="s">
         <v>65</v>
@@ -4453,7 +4444,7 @@
         <v>204</v>
       </c>
       <c r="AT19" s="7">
-        <v>10737</v>
+        <v>10525</v>
       </c>
       <c r="AU19" s="6" t="s">
         <v>82</v>
@@ -4480,7 +4471,7 @@
         <v>65</v>
       </c>
       <c r="BC19" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD19" s="10" t="s">
         <v>65</v>
@@ -4504,7 +4495,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" ht="23" customHeight="1">
+    <row r="20">
       <c r="A20" s="7">
         <v>2019</v>
       </c>
@@ -4560,7 +4551,7 @@
         <v>65</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T20" s="6" t="s">
         <v>207</v>
@@ -4641,7 +4632,7 @@
         <v>212</v>
       </c>
       <c r="AT20" s="7">
-        <v>8634</v>
+        <v>8380</v>
       </c>
       <c r="AU20" s="6" t="s">
         <v>82</v>
@@ -4668,7 +4659,7 @@
         <v>65</v>
       </c>
       <c r="BC20" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD20" s="10">
         <v>0</v>
@@ -4692,12 +4683,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" ht="23" customHeight="1">
+    <row r="21">
       <c r="A21" s="7">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B21" s="7">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>215</v>
@@ -4736,10 +4727,10 @@
         <v>65</v>
       </c>
       <c r="O21" s="7">
-        <v>258544</v>
+        <v>258541</v>
       </c>
       <c r="P21" s="8">
-        <v>45833</v>
+        <v>45539.125</v>
       </c>
       <c r="Q21" s="9">
         <v>45873.333333333336</v>
@@ -4748,7 +4739,7 @@
         <v>65</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="T21" s="6" t="s">
         <v>215</v>
@@ -4769,16 +4760,16 @@
         <v>65</v>
       </c>
       <c r="Z21" s="10">
-        <v>169.51</v>
+        <v>229.09</v>
       </c>
       <c r="AA21" s="10">
-        <v>5608.43</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="10">
-        <v>5777.94</v>
+        <v>229.09</v>
       </c>
       <c r="AC21" s="6" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD21" s="6" t="s">
         <v>65</v>
@@ -4787,10 +4778,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF21" s="7">
-        <v>148340</v>
+        <v>153244</v>
       </c>
       <c r="AG21" s="9">
-        <v>46168.63482638889</v>
+        <v>46175.357523148145</v>
       </c>
       <c r="AH21" s="6" t="s">
         <v>65</v>
@@ -4799,10 +4790,10 @@
         <v>78</v>
       </c>
       <c r="AJ21" s="11">
-        <v>0.013709677419354</v>
+        <v>0.013793103448275</v>
       </c>
       <c r="AK21" s="6" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AL21" s="6" t="s">
         <v>217</v>
@@ -4817,19 +4808,19 @@
         <v>65</v>
       </c>
       <c r="AP21" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="AQ21" s="10" t="s">
-        <v>65</v>
+        <v>176</v>
+      </c>
+      <c r="AQ21" s="10">
+        <v>0</v>
       </c>
       <c r="AR21" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS21" s="6" t="s">
-        <v>65</v>
+        <v>221</v>
       </c>
       <c r="AT21" s="7">
-        <v>5474</v>
+        <v>9903</v>
       </c>
       <c r="AU21" s="6" t="s">
         <v>82</v>
@@ -4838,7 +4829,7 @@
         <v>83</v>
       </c>
       <c r="AW21" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AX21" s="6" t="s">
         <v>117</v>
@@ -4850,57 +4841,57 @@
         <v>65</v>
       </c>
       <c r="BA21" s="8">
-        <v>46174.99998842592</v>
+        <v>46223.458333333336</v>
       </c>
       <c r="BB21" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC21" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="BD21" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD21" s="10">
+        <v>0</v>
       </c>
       <c r="BE21" s="10">
-        <v>49600</v>
+        <v>43500</v>
       </c>
       <c r="BF21" s="10">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="BG21" s="10">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="BH21" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="BI21" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="BJ21" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="22" ht="23" customHeight="1">
+    <row r="22">
       <c r="A22" s="7">
         <v>2021</v>
       </c>
       <c r="B22" s="7">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>65</v>
+        <v>224</v>
+      </c>
+      <c r="D22" s="8">
+        <v>45854.9691099537</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>65</v>
@@ -4909,7 +4900,7 @@
         <v>68</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>68</v>
@@ -4918,16 +4909,16 @@
         <v>65</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O22" s="7">
-        <v>258541</v>
+        <v>281433</v>
       </c>
       <c r="P22" s="8">
-        <v>45539.125</v>
+        <v>45222.125</v>
       </c>
       <c r="Q22" s="9">
         <v>45873.333333333336</v>
@@ -4936,10 +4927,10 @@
         <v>65</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="U22" s="6" t="s">
         <v>65</v>
@@ -4957,13 +4948,13 @@
         <v>65</v>
       </c>
       <c r="Z22" s="10">
-        <v>229.09</v>
+        <v>857.24</v>
       </c>
       <c r="AA22" s="10">
         <v>0</v>
       </c>
       <c r="AB22" s="10">
-        <v>229.09</v>
+        <v>897.24</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>76</v>
@@ -4972,13 +4963,13 @@
         <v>65</v>
       </c>
       <c r="AE22" s="8">
-        <v>45861.54583333333</v>
+        <v>45861.56458333333</v>
       </c>
       <c r="AF22" s="7">
-        <v>152063</v>
+        <v>191102</v>
       </c>
       <c r="AG22" s="9">
-        <v>46168.63482638889</v>
+        <v>46163.392905092594</v>
       </c>
       <c r="AH22" s="6" t="s">
         <v>65</v>
@@ -4987,13 +4978,13 @@
         <v>78</v>
       </c>
       <c r="AJ22" s="11">
-        <v>0.013793103448275</v>
+        <v>0.015272727272727</v>
       </c>
       <c r="AK22" s="6" t="s">
         <v>79</v>
       </c>
       <c r="AL22" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AM22" s="6" t="s">
         <v>65</v>
@@ -5005,7 +4996,7 @@
         <v>65</v>
       </c>
       <c r="AP22" s="6" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="AQ22" s="10">
         <v>0</v>
@@ -5014,10 +5005,10 @@
         <v>65</v>
       </c>
       <c r="AS22" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AT22" s="7">
-        <v>10084</v>
+        <v>3545</v>
       </c>
       <c r="AU22" s="6" t="s">
         <v>82</v>
@@ -5026,7 +5017,7 @@
         <v>83</v>
       </c>
       <c r="AW22" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AX22" s="6" t="s">
         <v>117</v>
@@ -5035,40 +5026,40 @@
         <v>118</v>
       </c>
       <c r="AZ22" s="6" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="BA22" s="8">
-        <v>46223.458333333336</v>
+        <v>46202.99998842592</v>
       </c>
       <c r="BB22" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC22" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD22" s="10">
         <v>0</v>
       </c>
       <c r="BE22" s="10">
-        <v>43500</v>
+        <v>41250</v>
       </c>
       <c r="BF22" s="10">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="BG22" s="10">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="BH22" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BI22" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BJ22" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="23" ht="23" customHeight="1">
+    <row r="23">
       <c r="A23" s="7">
         <v>2021</v>
       </c>
@@ -5076,19 +5067,19 @@
         <v>2021</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D23" s="8">
-        <v>45854.9691099537</v>
+        <v>233</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>65</v>
@@ -5097,7 +5088,7 @@
         <v>68</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>68</v>
@@ -5106,28 +5097,28 @@
         <v>65</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O23" s="7">
-        <v>281433</v>
+        <v>258549</v>
       </c>
       <c r="P23" s="8">
-        <v>45222.125</v>
+        <v>45105.125</v>
       </c>
       <c r="Q23" s="9">
-        <v>45873.333333333336</v>
+        <v>45861.393055555556</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="U23" s="6" t="s">
         <v>65</v>
@@ -5145,13 +5136,13 @@
         <v>65</v>
       </c>
       <c r="Z23" s="10">
-        <v>857.24</v>
+        <v>2040.16</v>
       </c>
       <c r="AA23" s="10">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AB23" s="10">
-        <v>897.24</v>
+        <v>2440.16</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>76</v>
@@ -5160,28 +5151,28 @@
         <v>65</v>
       </c>
       <c r="AE23" s="8">
-        <v>45861.56458333333</v>
+        <v>45873.458333333336</v>
       </c>
       <c r="AF23" s="7">
-        <v>191102</v>
+        <v>292424</v>
       </c>
       <c r="AG23" s="9">
-        <v>46163.392905092594</v>
+        <v>46175.357523148145</v>
       </c>
       <c r="AH23" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AI23" s="6" t="s">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="AJ23" s="11">
-        <v>0.015272727272727</v>
+        <v>0.014545454545454</v>
       </c>
       <c r="AK23" s="6" t="s">
         <v>79</v>
       </c>
       <c r="AL23" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AM23" s="6" t="s">
         <v>65</v>
@@ -5193,7 +5184,7 @@
         <v>65</v>
       </c>
       <c r="AP23" s="6" t="s">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="AQ23" s="10">
         <v>0</v>
@@ -5202,10 +5193,10 @@
         <v>65</v>
       </c>
       <c r="AS23" s="6" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AT23" s="7">
-        <v>3653</v>
+        <v>20785</v>
       </c>
       <c r="AU23" s="6" t="s">
         <v>82</v>
@@ -5214,7 +5205,7 @@
         <v>83</v>
       </c>
       <c r="AW23" s="6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AX23" s="6" t="s">
         <v>117</v>
@@ -5223,16 +5214,16 @@
         <v>118</v>
       </c>
       <c r="AZ23" s="6" t="s">
-        <v>169</v>
+        <v>65</v>
       </c>
       <c r="BA23" s="8">
-        <v>46174.99998842592</v>
+        <v>46223.99998842592</v>
       </c>
       <c r="BB23" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC23" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD23" s="10">
         <v>0</v>
@@ -5241,42 +5232,42 @@
         <v>41250</v>
       </c>
       <c r="BF23" s="10">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="BG23" s="10">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="BH23" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="BI23" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="BJ23" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" ht="23" customHeight="1">
+    <row r="24">
       <c r="A24" s="7">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B24" s="7">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>65</v>
@@ -5285,7 +5276,7 @@
         <v>68</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>68</v>
@@ -5294,29 +5285,29 @@
         <v>65</v>
       </c>
       <c r="M24" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" s="7">
+        <v>258532</v>
+      </c>
+      <c r="P24" s="8">
+        <v>45344.125</v>
+      </c>
+      <c r="Q24" s="9">
+        <v>45873.333333333336</v>
+      </c>
+      <c r="R24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S24" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="T24" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="N24" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O24" s="7">
-        <v>258549</v>
-      </c>
-      <c r="P24" s="8">
-        <v>45105.125</v>
-      </c>
-      <c r="Q24" s="9">
-        <v>45861.393055555556</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S24" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="T24" s="6" t="s">
-        <v>239</v>
-      </c>
       <c r="U24" s="6" t="s">
         <v>65</v>
       </c>
@@ -5333,16 +5324,16 @@
         <v>65</v>
       </c>
       <c r="Z24" s="10">
-        <v>2040.16</v>
+        <v>381.44</v>
       </c>
       <c r="AA24" s="10">
-        <v>400</v>
+        <v>711.56</v>
       </c>
       <c r="AB24" s="10">
-        <v>2440.16</v>
+        <v>1093</v>
       </c>
       <c r="AC24" s="6" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AD24" s="6" t="s">
         <v>65</v>
@@ -5351,10 +5342,10 @@
         <v>45873.458333333336</v>
       </c>
       <c r="AF24" s="7">
-        <v>293001</v>
+        <v>286674</v>
       </c>
       <c r="AG24" s="9">
-        <v>46167.471284722225</v>
+        <v>46175.357511574075</v>
       </c>
       <c r="AH24" s="6" t="s">
         <v>65</v>
@@ -5363,13 +5354,13 @@
         <v>78</v>
       </c>
       <c r="AJ24" s="11">
-        <v>0.014545454545454</v>
+        <v>0.016190476190476</v>
       </c>
       <c r="AK24" s="6" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="AL24" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AM24" s="6" t="s">
         <v>65</v>
@@ -5381,7 +5372,7 @@
         <v>65</v>
       </c>
       <c r="AP24" s="6" t="s">
-        <v>244</v>
+        <v>157</v>
       </c>
       <c r="AQ24" s="10">
         <v>0</v>
@@ -5390,10 +5381,10 @@
         <v>65</v>
       </c>
       <c r="AS24" s="6" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AT24" s="7">
-        <v>21447</v>
+        <v>0</v>
       </c>
       <c r="AU24" s="6" t="s">
         <v>82</v>
@@ -5402,7 +5393,7 @@
         <v>83</v>
       </c>
       <c r="AW24" s="6" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AX24" s="6" t="s">
         <v>117</v>
@@ -5414,97 +5405,97 @@
         <v>65</v>
       </c>
       <c r="BA24" s="8">
-        <v>46223.99998842592</v>
+        <v>46188.99998842592</v>
       </c>
       <c r="BB24" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC24" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD24" s="10">
         <v>0</v>
       </c>
       <c r="BE24" s="10">
-        <v>41250</v>
+        <v>42000</v>
       </c>
       <c r="BF24" s="10">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="BG24" s="10">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="BH24" s="6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="BI24" s="6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="BJ24" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" ht="23" customHeight="1">
+    <row r="25">
       <c r="A25" s="7">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="B25" s="7">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>65</v>
+        <v>251</v>
+      </c>
+      <c r="D25" s="8">
+        <v>45911.83042086806</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>68</v>
+        <v>254</v>
       </c>
       <c r="J25" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O25" s="7">
+        <v>291360</v>
+      </c>
+      <c r="P25" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>46055.333333333336</v>
+      </c>
+      <c r="R25" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S25" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="T25" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="K25" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M25" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="N25" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O25" s="7">
-        <v>258532</v>
-      </c>
-      <c r="P25" s="8">
-        <v>45344.125</v>
-      </c>
-      <c r="Q25" s="9">
-        <v>45873.333333333336</v>
-      </c>
-      <c r="R25" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S25" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="T25" s="6" t="s">
-        <v>248</v>
-      </c>
       <c r="U25" s="6" t="s">
         <v>65</v>
       </c>
@@ -5521,28 +5512,28 @@
         <v>65</v>
       </c>
       <c r="Z25" s="10">
-        <v>381.44</v>
+        <v>479.38</v>
       </c>
       <c r="AA25" s="10">
-        <v>711.56</v>
+        <v>0</v>
       </c>
       <c r="AB25" s="10">
-        <v>1093</v>
+        <v>479.38</v>
       </c>
       <c r="AC25" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD25" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE25" s="8">
-        <v>45873.458333333336</v>
+        <v>45911.791666666664</v>
       </c>
       <c r="AF25" s="7">
-        <v>286517</v>
+        <v>128962</v>
       </c>
       <c r="AG25" s="9">
-        <v>46168.63480324074</v>
+        <v>46175.35753472222</v>
       </c>
       <c r="AH25" s="6" t="s">
         <v>65</v>
@@ -5551,13 +5542,13 @@
         <v>78</v>
       </c>
       <c r="AJ25" s="11">
-        <v>0.016190476190476</v>
+        <v>0.013737373737373</v>
       </c>
       <c r="AK25" s="6" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="AL25" s="6" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AM25" s="6" t="s">
         <v>65</v>
@@ -5569,7 +5560,7 @@
         <v>65</v>
       </c>
       <c r="AP25" s="6" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
       <c r="AQ25" s="10">
         <v>0</v>
@@ -5578,10 +5569,10 @@
         <v>65</v>
       </c>
       <c r="AS25" s="6" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AT25" s="7">
-        <v>0</v>
+        <v>6019</v>
       </c>
       <c r="AU25" s="6" t="s">
         <v>82</v>
@@ -5590,7 +5581,7 @@
         <v>83</v>
       </c>
       <c r="AW25" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AX25" s="6" t="s">
         <v>117</v>
@@ -5602,19 +5593,19 @@
         <v>65</v>
       </c>
       <c r="BA25" s="8">
-        <v>46188.99998842592</v>
+        <v>46181.48611111111</v>
       </c>
       <c r="BB25" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC25" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD25" s="10">
         <v>0</v>
       </c>
       <c r="BE25" s="10">
-        <v>42000</v>
+        <v>49500</v>
       </c>
       <c r="BF25" s="10">
         <v>680</v>
@@ -5623,16 +5614,16 @@
         <v>680</v>
       </c>
       <c r="BH25" s="6" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="BI25" s="6" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="BJ25" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="26" ht="23" customHeight="1">
+    <row r="26">
       <c r="A26" s="7">
         <v>2023</v>
       </c>
@@ -5640,59 +5631,59 @@
         <v>2022</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D26" s="8">
-        <v>45911.83042086806</v>
+        <v>45916.71897465278</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J26" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O26" s="7">
+        <v>292111</v>
+      </c>
+      <c r="P26" s="8">
+        <v>36526.083333333336</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>45917.333333333336</v>
+      </c>
+      <c r="R26" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S26" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="T26" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="K26" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O26" s="7">
-        <v>291360</v>
-      </c>
-      <c r="P26" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q26" s="9">
-        <v>46055.333333333336</v>
-      </c>
-      <c r="R26" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S26" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="T26" s="6" t="s">
-        <v>256</v>
-      </c>
       <c r="U26" s="6" t="s">
         <v>65</v>
       </c>
@@ -5709,28 +5700,28 @@
         <v>65</v>
       </c>
       <c r="Z26" s="10">
-        <v>479.38</v>
+        <v>610.62</v>
       </c>
       <c r="AA26" s="10">
         <v>0</v>
       </c>
       <c r="AB26" s="10">
-        <v>479.38</v>
+        <v>670.08</v>
       </c>
       <c r="AC26" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD26" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE26" s="8">
-        <v>45911.791666666664</v>
+        <v>45915.458333333336</v>
       </c>
       <c r="AF26" s="7">
-        <v>127758</v>
+        <v>117956</v>
       </c>
       <c r="AG26" s="9">
-        <v>46168.63483796296</v>
+        <v>46175.3575</v>
       </c>
       <c r="AH26" s="6" t="s">
         <v>65</v>
@@ -5739,13 +5730,13 @@
         <v>78</v>
       </c>
       <c r="AJ26" s="11">
-        <v>0.013737373737373</v>
+        <v>0.013765182186234</v>
       </c>
       <c r="AK26" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AL26" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AM26" s="6" t="s">
         <v>65</v>
@@ -5757,7 +5748,7 @@
         <v>65</v>
       </c>
       <c r="AP26" s="6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AQ26" s="10">
         <v>0</v>
@@ -5766,10 +5757,10 @@
         <v>65</v>
       </c>
       <c r="AS26" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AT26" s="7">
-        <v>6177</v>
+        <v>3886</v>
       </c>
       <c r="AU26" s="6" t="s">
         <v>82</v>
@@ -5778,7 +5769,7 @@
         <v>83</v>
       </c>
       <c r="AW26" s="6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AX26" s="6" t="s">
         <v>117</v>
@@ -5790,19 +5781,19 @@
         <v>65</v>
       </c>
       <c r="BA26" s="8">
-        <v>46181.48611111111</v>
+        <v>46181.99998842592</v>
       </c>
       <c r="BB26" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC26" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD26" s="10">
         <v>0</v>
       </c>
       <c r="BE26" s="10">
-        <v>49500</v>
+        <v>49400</v>
       </c>
       <c r="BF26" s="10">
         <v>680</v>
@@ -5811,16 +5802,16 @@
         <v>680</v>
       </c>
       <c r="BH26" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="BI26" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="BJ26" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="27" ht="23" customHeight="1">
+    <row r="27">
       <c r="A27" s="7">
         <v>2023</v>
       </c>
@@ -5828,58 +5819,58 @@
         <v>2022</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D27" s="8">
-        <v>45916.71897465278</v>
+        <v>45951.78161053241</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="N27" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O27" s="7">
-        <v>292111</v>
+        <v>312412</v>
       </c>
       <c r="P27" s="8">
         <v>36526.083333333336</v>
       </c>
       <c r="Q27" s="9">
-        <v>45917.333333333336</v>
+        <v>45957.333333333336</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S27" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>65</v>
@@ -5897,28 +5888,28 @@
         <v>65</v>
       </c>
       <c r="Z27" s="10">
-        <v>610.62</v>
+        <v>595.14</v>
       </c>
       <c r="AA27" s="10">
         <v>0</v>
       </c>
       <c r="AB27" s="10">
-        <v>670.08</v>
+        <v>595.14</v>
       </c>
       <c r="AC27" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD27" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE27" s="8">
-        <v>45915.458333333336</v>
+        <v>45957.458333333336</v>
       </c>
       <c r="AF27" s="7">
-        <v>116520</v>
+        <v>129846</v>
       </c>
       <c r="AG27" s="9">
-        <v>46168.634791666664</v>
+        <v>46175.3575</v>
       </c>
       <c r="AH27" s="6" t="s">
         <v>65</v>
@@ -5930,10 +5921,10 @@
         <v>0.013765182186234</v>
       </c>
       <c r="AK27" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AL27" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AM27" s="6" t="s">
         <v>65</v>
@@ -5945,7 +5936,7 @@
         <v>65</v>
       </c>
       <c r="AP27" s="6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AQ27" s="10">
         <v>0</v>
@@ -5954,10 +5945,10 @@
         <v>65</v>
       </c>
       <c r="AS27" s="6" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AT27" s="7">
-        <v>3854</v>
+        <v>5371</v>
       </c>
       <c r="AU27" s="6" t="s">
         <v>82</v>
@@ -5966,7 +5957,7 @@
         <v>83</v>
       </c>
       <c r="AW27" s="6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AX27" s="6" t="s">
         <v>117</v>
@@ -5978,7 +5969,7 @@
         <v>65</v>
       </c>
       <c r="BA27" s="8">
-        <v>46139.99998842592</v>
+        <v>46181.99998842592</v>
       </c>
       <c r="BB27" s="9" t="s">
         <v>65</v>
@@ -5999,76 +5990,76 @@
         <v>680</v>
       </c>
       <c r="BH27" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="BI27" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="BJ27" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="28" ht="23" customHeight="1">
+    <row r="28">
       <c r="A28" s="7">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B28" s="7">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D28" s="8">
-        <v>45951.78161053241</v>
+        <v>45959.49119818287</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M28" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O28" s="7">
+        <v>313409</v>
+      </c>
+      <c r="P28" s="8">
+        <v>45154.125</v>
+      </c>
+      <c r="Q28" s="9">
+        <v>45958.666666666664</v>
+      </c>
+      <c r="R28" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S28" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="T28" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="N28" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O28" s="7">
-        <v>312412</v>
-      </c>
-      <c r="P28" s="8">
-        <v>36526.083333333336</v>
-      </c>
-      <c r="Q28" s="9">
-        <v>45957.333333333336</v>
-      </c>
-      <c r="R28" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S28" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="T28" s="6" t="s">
-        <v>274</v>
-      </c>
       <c r="U28" s="6" t="s">
         <v>65</v>
       </c>
@@ -6085,28 +6076,28 @@
         <v>65</v>
       </c>
       <c r="Z28" s="10">
-        <v>595.14</v>
+        <v>832.5</v>
       </c>
       <c r="AA28" s="10">
         <v>0</v>
       </c>
       <c r="AB28" s="10">
-        <v>595.14</v>
+        <v>832.5</v>
       </c>
       <c r="AC28" s="6" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD28" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE28" s="8">
-        <v>45957.458333333336</v>
+        <v>45958.791666666664</v>
       </c>
       <c r="AF28" s="7">
-        <v>128737</v>
+        <v>211265</v>
       </c>
       <c r="AG28" s="9">
-        <v>46168.634791666664</v>
+        <v>46175.357511574075</v>
       </c>
       <c r="AH28" s="6" t="s">
         <v>65</v>
@@ -6115,13 +6106,13 @@
         <v>78</v>
       </c>
       <c r="AJ28" s="11">
-        <v>0.013765182186234</v>
+        <v>0.015089820359281</v>
       </c>
       <c r="AK28" s="6" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AL28" s="6" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AM28" s="6" t="s">
         <v>65</v>
@@ -6133,7 +6124,7 @@
         <v>65</v>
       </c>
       <c r="AP28" s="6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AQ28" s="10">
         <v>0</v>
@@ -6142,10 +6133,10 @@
         <v>65</v>
       </c>
       <c r="AS28" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AT28" s="7">
-        <v>5441</v>
+        <v>4878</v>
       </c>
       <c r="AU28" s="6" t="s">
         <v>82</v>
@@ -6154,7 +6145,7 @@
         <v>83</v>
       </c>
       <c r="AW28" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AX28" s="6" t="s">
         <v>117</v>
@@ -6166,97 +6157,97 @@
         <v>65</v>
       </c>
       <c r="BA28" s="8">
-        <v>46181.99998842592</v>
+        <v>46195.458333333336</v>
       </c>
       <c r="BB28" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC28" s="6" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="BD28" s="10">
         <v>0</v>
       </c>
       <c r="BE28" s="10">
-        <v>49400</v>
+        <v>41750</v>
       </c>
       <c r="BF28" s="10">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="BG28" s="10">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="BH28" s="6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="BI28" s="6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="BJ28" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="29" ht="23" customHeight="1">
+    <row r="29">
       <c r="A29" s="7">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B29" s="7">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D29" s="8">
-        <v>45959.49119818287</v>
+        <v>45986.703306284726</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J29" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O29" s="7">
+        <v>317589</v>
+      </c>
+      <c r="P29" s="8">
+        <v>45575</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>45980.541666666664</v>
+      </c>
+      <c r="R29" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S29" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="T29" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="K29" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M29" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="N29" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O29" s="7">
-        <v>313409</v>
-      </c>
-      <c r="P29" s="8">
-        <v>45154.125</v>
-      </c>
-      <c r="Q29" s="9">
-        <v>45958.666666666664</v>
-      </c>
-      <c r="R29" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S29" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="T29" s="6" t="s">
-        <v>283</v>
-      </c>
       <c r="U29" s="6" t="s">
         <v>65</v>
       </c>
@@ -6273,28 +6264,28 @@
         <v>65</v>
       </c>
       <c r="Z29" s="10">
-        <v>832.5</v>
+        <v>800.63</v>
       </c>
       <c r="AA29" s="10">
         <v>0</v>
       </c>
       <c r="AB29" s="10">
-        <v>832.5</v>
+        <v>800.63</v>
       </c>
       <c r="AC29" s="6" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AD29" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE29" s="8">
-        <v>45958.791666666664</v>
+        <v>45980.666666666664</v>
       </c>
       <c r="AF29" s="7">
-        <v>210264</v>
+        <v>127507</v>
       </c>
       <c r="AG29" s="9">
-        <v>46168.63481481482</v>
+        <v>46175.3575</v>
       </c>
       <c r="AH29" s="6" t="s">
         <v>65</v>
@@ -6303,13 +6294,13 @@
         <v>78</v>
       </c>
       <c r="AJ29" s="11">
-        <v>0.015089820359281</v>
+        <v>0.014639397201291</v>
       </c>
       <c r="AK29" s="6" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="AL29" s="6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AM29" s="6" t="s">
         <v>65</v>
@@ -6321,19 +6312,19 @@
         <v>65</v>
       </c>
       <c r="AP29" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ29" s="10">
-        <v>0</v>
+        <v>239</v>
+      </c>
+      <c r="AQ29" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR29" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS29" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AT29" s="7">
-        <v>4943</v>
+        <v>2913</v>
       </c>
       <c r="AU29" s="6" t="s">
         <v>82</v>
@@ -6342,7 +6333,7 @@
         <v>83</v>
       </c>
       <c r="AW29" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AX29" s="6" t="s">
         <v>117</v>
@@ -6354,37 +6345,37 @@
         <v>65</v>
       </c>
       <c r="BA29" s="8">
-        <v>46195.458333333336</v>
+        <v>46202.99998842592</v>
       </c>
       <c r="BB29" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC29" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD29" s="10">
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="BD29" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BE29" s="10">
-        <v>41750</v>
+        <v>46450</v>
       </c>
       <c r="BF29" s="10">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="BG29" s="10">
-        <v>630</v>
+        <v>700</v>
       </c>
       <c r="BH29" s="6" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="BI29" s="6" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="BJ29" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="30" ht="23" customHeight="1">
+    <row r="30">
       <c r="A30" s="7">
         <v>2023</v>
       </c>
@@ -6392,59 +6383,59 @@
         <v>2022</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D30" s="8">
-        <v>45986.703306284726</v>
+        <v>45988.58394895833</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>65</v>
+        <v>296</v>
+      </c>
+      <c r="H30" s="7">
+        <v>25</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J30" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O30" s="7">
+        <v>317975</v>
+      </c>
+      <c r="P30" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q30" s="9">
+        <v>45986.333333333336</v>
+      </c>
+      <c r="R30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S30" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="T30" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="K30" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O30" s="7">
-        <v>317589</v>
-      </c>
-      <c r="P30" s="8">
-        <v>45575</v>
-      </c>
-      <c r="Q30" s="9">
-        <v>45980.541666666664</v>
-      </c>
-      <c r="R30" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S30" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="T30" s="6" t="s">
-        <v>291</v>
-      </c>
       <c r="U30" s="6" t="s">
         <v>65</v>
       </c>
@@ -6461,28 +6452,28 @@
         <v>65</v>
       </c>
       <c r="Z30" s="10">
-        <v>420.63</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="10">
         <v>0</v>
       </c>
       <c r="AB30" s="10">
-        <v>420.63</v>
+        <v>0</v>
       </c>
       <c r="AC30" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE30" s="8">
-        <v>45980.666666666664</v>
+        <v>45986.458333333336</v>
       </c>
       <c r="AF30" s="7">
-        <v>127009</v>
+        <v>103022</v>
       </c>
       <c r="AG30" s="9">
-        <v>46168.63480324074</v>
+        <v>46175.35753472222</v>
       </c>
       <c r="AH30" s="6" t="s">
         <v>65</v>
@@ -6491,13 +6482,13 @@
         <v>78</v>
       </c>
       <c r="AJ30" s="11">
-        <v>0.014639397201291</v>
+        <v>0.050560747663551</v>
       </c>
       <c r="AK30" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AL30" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AM30" s="6" t="s">
         <v>65</v>
@@ -6509,19 +6500,19 @@
         <v>65</v>
       </c>
       <c r="AP30" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ30" s="10" t="s">
-        <v>65</v>
+        <v>300</v>
+      </c>
+      <c r="AQ30" s="10">
+        <v>0</v>
       </c>
       <c r="AR30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS30" s="6" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AT30" s="7">
-        <v>2972</v>
+        <v>3735</v>
       </c>
       <c r="AU30" s="6" t="s">
         <v>82</v>
@@ -6530,49 +6521,49 @@
         <v>83</v>
       </c>
       <c r="AW30" s="6" t="s">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c r="AX30" s="6" t="s">
         <v>117</v>
       </c>
       <c r="AY30" s="6" t="s">
-        <v>118</v>
+        <v>302</v>
       </c>
       <c r="AZ30" s="6" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="BA30" s="8">
-        <v>46174.99998842592</v>
+        <v>46198.53125</v>
       </c>
       <c r="BB30" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC30" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD30" s="10" t="s">
-        <v>65</v>
+        <v>150</v>
+      </c>
+      <c r="BD30" s="10">
+        <v>0</v>
       </c>
       <c r="BE30" s="10">
-        <v>46450</v>
+        <v>53500</v>
       </c>
       <c r="BF30" s="10">
-        <v>680</v>
+        <v>2705</v>
       </c>
       <c r="BG30" s="10">
-        <v>700</v>
+        <v>2705</v>
       </c>
       <c r="BH30" s="6" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="BI30" s="6" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="BJ30" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" ht="23" customHeight="1">
+    <row r="31">
       <c r="A31" s="7">
         <v>2023</v>
       </c>
@@ -6580,59 +6571,59 @@
         <v>2022</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D31" s="8">
-        <v>45988.58394895833</v>
+        <v>46035.78157329861</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="H31" s="7">
-        <v>25</v>
+        <v>306</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O31" s="7">
-        <v>317975</v>
-      </c>
-      <c r="P31" s="8" t="s">
-        <v>65</v>
+        <v>325267</v>
+      </c>
+      <c r="P31" s="8">
+        <v>45736</v>
       </c>
       <c r="Q31" s="9">
-        <v>45986.333333333336</v>
+        <v>46031.666666666664</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S31" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="T31" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="T31" s="6" t="s">
-        <v>299</v>
-      </c>
       <c r="U31" s="6" t="s">
         <v>65</v>
       </c>
@@ -6649,28 +6640,28 @@
         <v>65</v>
       </c>
       <c r="Z31" s="10">
-        <v>0</v>
+        <v>400.54</v>
       </c>
       <c r="AA31" s="10">
         <v>0</v>
       </c>
       <c r="AB31" s="10">
-        <v>0</v>
+        <v>400.54</v>
       </c>
       <c r="AC31" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD31" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE31" s="8">
-        <v>45986.458333333336</v>
+        <v>46031.791666666664</v>
       </c>
       <c r="AF31" s="7">
-        <v>103042</v>
+        <v>106081</v>
       </c>
       <c r="AG31" s="9">
-        <v>46168.63483796296</v>
+        <v>46175.3575</v>
       </c>
       <c r="AH31" s="6" t="s">
         <v>65</v>
@@ -6679,13 +6670,13 @@
         <v>78</v>
       </c>
       <c r="AJ31" s="11">
-        <v>0.050560747663551</v>
+        <v>0.013255360623781</v>
       </c>
       <c r="AK31" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AL31" s="6" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AM31" s="6" t="s">
         <v>65</v>
@@ -6697,19 +6688,19 @@
         <v>65</v>
       </c>
       <c r="AP31" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="AQ31" s="10">
-        <v>0</v>
+        <v>239</v>
+      </c>
+      <c r="AQ31" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR31" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS31" s="6" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AT31" s="7">
-        <v>3922</v>
+        <v>1519</v>
       </c>
       <c r="AU31" s="6" t="s">
         <v>82</v>
@@ -6718,108 +6709,108 @@
         <v>83</v>
       </c>
       <c r="AW31" s="6" t="s">
-        <v>65</v>
+        <v>311</v>
       </c>
       <c r="AX31" s="6" t="s">
         <v>117</v>
       </c>
       <c r="AY31" s="6" t="s">
-        <v>306</v>
+        <v>118</v>
       </c>
       <c r="AZ31" s="6" t="s">
-        <v>169</v>
+        <v>65</v>
       </c>
       <c r="BA31" s="8">
-        <v>46168.458333333336</v>
+        <v>46195.99998842592</v>
       </c>
       <c r="BB31" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC31" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="BD31" s="10">
-        <v>0</v>
+        <v>150</v>
+      </c>
+      <c r="BD31" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BE31" s="10">
-        <v>53500</v>
+        <v>51300</v>
       </c>
       <c r="BF31" s="10">
-        <v>2705</v>
+        <v>680</v>
       </c>
       <c r="BG31" s="10">
-        <v>2705</v>
+        <v>680</v>
       </c>
       <c r="BH31" s="6" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="BI31" s="6" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="BJ31" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="32" ht="23" customHeight="1">
+    <row r="32">
       <c r="A32" s="7">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B32" s="7">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>308</v>
+        <v>65</v>
       </c>
       <c r="D32" s="8">
-        <v>46035.78157329861</v>
+        <v>46056.538589965276</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="O32" s="7">
-        <v>325267</v>
+      <c r="O32" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="P32" s="8">
-        <v>45736</v>
+        <v>36526.083333333336</v>
       </c>
       <c r="Q32" s="9">
-        <v>46031.666666666664</v>
+        <v>46083.40277777778</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S32" s="6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="T32" s="6" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="U32" s="6" t="s">
         <v>65</v>
@@ -6837,28 +6828,28 @@
         <v>65</v>
       </c>
       <c r="Z32" s="10">
-        <v>400.54</v>
+        <v>112.22</v>
       </c>
       <c r="AA32" s="10">
         <v>0</v>
       </c>
       <c r="AB32" s="10">
-        <v>400.54</v>
+        <v>112.22</v>
       </c>
       <c r="AC32" s="6" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD32" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE32" s="8">
-        <v>46031.791666666664</v>
+        <v>46041.458333333336</v>
       </c>
       <c r="AF32" s="7">
-        <v>105709</v>
+        <v>225001</v>
       </c>
       <c r="AG32" s="9">
-        <v>46168.634791666664</v>
+        <v>46175.357523148145</v>
       </c>
       <c r="AH32" s="6" t="s">
         <v>65</v>
@@ -6867,13 +6858,13 @@
         <v>78</v>
       </c>
       <c r="AJ32" s="11">
-        <v>0.013255360623781</v>
+        <v>0.05090909090909</v>
       </c>
       <c r="AK32" s="6" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AL32" s="6" t="s">
-        <v>310</v>
+        <v>65</v>
       </c>
       <c r="AM32" s="6" t="s">
         <v>65</v>
@@ -6885,19 +6876,19 @@
         <v>65</v>
       </c>
       <c r="AP32" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ32" s="10" t="s">
-        <v>65</v>
+        <v>239</v>
+      </c>
+      <c r="AQ32" s="10">
+        <v>0</v>
       </c>
       <c r="AR32" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS32" s="6" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AT32" s="7">
-        <v>1538</v>
+        <v>2920</v>
       </c>
       <c r="AU32" s="6" t="s">
         <v>82</v>
@@ -6906,105 +6897,105 @@
         <v>83</v>
       </c>
       <c r="AW32" s="6" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AX32" s="6" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="AY32" s="6" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="AZ32" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA32" s="8">
-        <v>46195.99998842592</v>
+        <v>46406.458333333336</v>
       </c>
       <c r="BB32" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC32" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="BD32" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD32" s="10">
+        <v>0</v>
       </c>
       <c r="BE32" s="10">
-        <v>51300</v>
+        <v>41250</v>
       </c>
       <c r="BF32" s="10">
-        <v>680</v>
+        <v>2100</v>
       </c>
       <c r="BG32" s="10">
-        <v>680</v>
+        <v>2100</v>
       </c>
       <c r="BH32" s="6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="BI32" s="6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="BJ32" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="33" ht="23" customHeight="1">
+    <row r="33">
       <c r="A33" s="7">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B33" s="7">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>65</v>
+        <v>322</v>
       </c>
       <c r="D33" s="8">
-        <v>46056.538589965276</v>
+        <v>46092.505066701386</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="O33" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="P33" s="8">
-        <v>36526.083333333336</v>
+      <c r="O33" s="7">
+        <v>335821</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="Q33" s="9">
-        <v>46083.40277777778</v>
+        <v>46087.5</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S33" s="6" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="T33" s="6" t="s">
         <v>322</v>
@@ -7025,28 +7016,28 @@
         <v>65</v>
       </c>
       <c r="Z33" s="10">
-        <v>112.22</v>
+        <v>143.59</v>
       </c>
       <c r="AA33" s="10">
         <v>0</v>
       </c>
       <c r="AB33" s="10">
-        <v>112.22</v>
+        <v>143.59</v>
       </c>
       <c r="AC33" s="6" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AD33" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE33" s="8">
-        <v>46041.458333333336</v>
+        <v>46087.625</v>
       </c>
       <c r="AF33" s="7">
-        <v>224732</v>
+        <v>82643</v>
       </c>
       <c r="AG33" s="9">
-        <v>46168.63482638889</v>
+        <v>46175.3575</v>
       </c>
       <c r="AH33" s="6" t="s">
         <v>65</v>
@@ -7055,13 +7046,13 @@
         <v>78</v>
       </c>
       <c r="AJ33" s="11">
-        <v>0.05090909090909</v>
+        <v>0</v>
       </c>
       <c r="AK33" s="6" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="AL33" s="6" t="s">
-        <v>65</v>
+        <v>324</v>
       </c>
       <c r="AM33" s="6" t="s">
         <v>65</v>
@@ -7073,19 +7064,19 @@
         <v>65</v>
       </c>
       <c r="AP33" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ33" s="10">
-        <v>0</v>
+        <v>239</v>
+      </c>
+      <c r="AQ33" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR33" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS33" s="6" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AT33" s="7">
-        <v>3130</v>
+        <v>8678</v>
       </c>
       <c r="AU33" s="6" t="s">
         <v>82</v>
@@ -7094,109 +7085,109 @@
         <v>83</v>
       </c>
       <c r="AW33" s="6" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AX33" s="6" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="AY33" s="6" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="AZ33" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA33" s="8">
-        <v>46406.458333333336</v>
+        <v>46209.99998842592</v>
       </c>
       <c r="BB33" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC33" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD33" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE33" s="10">
-        <v>41250</v>
+        <v>87</v>
+      </c>
+      <c r="BD33" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE33" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF33" s="10">
-        <v>2100</v>
+        <v>700</v>
       </c>
       <c r="BG33" s="10">
-        <v>2100</v>
+        <v>700</v>
       </c>
       <c r="BH33" s="6" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="BI33" s="6" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="BJ33" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" ht="23" customHeight="1">
+    <row r="34">
       <c r="A34" s="7">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B34" s="7">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D34" s="8">
-        <v>46092.505066701386</v>
+        <v>46092.55300158565</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O34" s="7">
-        <v>335821</v>
-      </c>
-      <c r="P34" s="8" t="s">
-        <v>65</v>
+        <v>335848</v>
+      </c>
+      <c r="P34" s="8">
+        <v>45364.125</v>
       </c>
       <c r="Q34" s="9">
-        <v>46087.5</v>
+        <v>46092.583333333336</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S34" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="T34" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="T34" s="6" t="s">
-        <v>326</v>
-      </c>
       <c r="U34" s="6" t="s">
         <v>65</v>
       </c>
@@ -7213,28 +7204,28 @@
         <v>65</v>
       </c>
       <c r="Z34" s="10">
-        <v>143.59</v>
+        <v>294.79</v>
       </c>
       <c r="AA34" s="10">
         <v>0</v>
       </c>
       <c r="AB34" s="10">
-        <v>143.59</v>
+        <v>294.79</v>
       </c>
       <c r="AC34" s="6" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD34" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE34" s="8">
-        <v>46087.625</v>
+        <v>46092.708333333336</v>
       </c>
       <c r="AF34" s="7">
-        <v>81734</v>
+        <v>155332</v>
       </c>
       <c r="AG34" s="9">
-        <v>46168.634791666664</v>
+        <v>46175.357511574075</v>
       </c>
       <c r="AH34" s="6" t="s">
         <v>65</v>
@@ -7243,13 +7234,13 @@
         <v>78</v>
       </c>
       <c r="AJ34" s="11">
-        <v>0</v>
+        <v>0.015831660251596</v>
       </c>
       <c r="AK34" s="6" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AL34" s="6" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AM34" s="6" t="s">
         <v>65</v>
@@ -7261,19 +7252,19 @@
         <v>65</v>
       </c>
       <c r="AP34" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ34" s="10" t="s">
-        <v>65</v>
+        <v>239</v>
+      </c>
+      <c r="AQ34" s="10">
+        <v>0</v>
       </c>
       <c r="AR34" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS34" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AT34" s="7">
-        <v>9290</v>
+        <v>-10230</v>
       </c>
       <c r="AU34" s="6" t="s">
         <v>82</v>
@@ -7282,7 +7273,7 @@
         <v>83</v>
       </c>
       <c r="AW34" s="6" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AX34" s="6" t="s">
         <v>117</v>
@@ -7294,97 +7285,97 @@
         <v>65</v>
       </c>
       <c r="BA34" s="8">
-        <v>46209.99998842592</v>
+        <v>46202.99998842592</v>
       </c>
       <c r="BB34" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC34" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD34" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE34" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD34" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE34" s="10">
+        <v>41056.97</v>
       </c>
       <c r="BF34" s="10">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="BG34" s="10">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="BH34" s="6" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="BI34" s="6" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="BJ34" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="35" ht="23" customHeight="1">
+    <row r="35">
       <c r="A35" s="7">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="B35" s="7">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D35" s="8">
-        <v>46092.55300158565</v>
+        <v>46098.67728869213</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M35" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O35" s="7">
+        <v>336908</v>
+      </c>
+      <c r="P35" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>46097.666666666664</v>
+      </c>
+      <c r="R35" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S35" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="T35" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="N35" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O35" s="7">
-        <v>335848</v>
-      </c>
-      <c r="P35" s="8">
-        <v>45364.125</v>
-      </c>
-      <c r="Q35" s="9">
-        <v>46092.583333333336</v>
-      </c>
-      <c r="R35" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S35" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="T35" s="6" t="s">
-        <v>335</v>
-      </c>
       <c r="U35" s="6" t="s">
         <v>65</v>
       </c>
@@ -7401,13 +7392,13 @@
         <v>65</v>
       </c>
       <c r="Z35" s="10">
-        <v>294.79</v>
+        <v>194.95</v>
       </c>
       <c r="AA35" s="10">
         <v>0</v>
       </c>
       <c r="AB35" s="10">
-        <v>294.79</v>
+        <v>194.95</v>
       </c>
       <c r="AC35" s="6" t="s">
         <v>76</v>
@@ -7416,13 +7407,13 @@
         <v>65</v>
       </c>
       <c r="AE35" s="8">
-        <v>46092.708333333336</v>
+        <v>46097.791666666664</v>
       </c>
       <c r="AF35" s="7">
-        <v>154167</v>
+        <v>45764</v>
       </c>
       <c r="AG35" s="9">
-        <v>46168.63480324074</v>
+        <v>46100.406643518516</v>
       </c>
       <c r="AH35" s="6" t="s">
         <v>65</v>
@@ -7431,13 +7422,13 @@
         <v>78</v>
       </c>
       <c r="AJ35" s="11">
-        <v>0.015831660251596</v>
+        <v>0</v>
       </c>
       <c r="AK35" s="6" t="s">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="AL35" s="6" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="AM35" s="6" t="s">
         <v>65</v>
@@ -7449,19 +7440,19 @@
         <v>65</v>
       </c>
       <c r="AP35" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ35" s="10">
-        <v>0</v>
+        <v>239</v>
+      </c>
+      <c r="AQ35" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR35" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS35" s="6" t="s">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="AT35" s="7">
-        <v>-11858</v>
+        <v>1</v>
       </c>
       <c r="AU35" s="6" t="s">
         <v>82</v>
@@ -7470,7 +7461,7 @@
         <v>83</v>
       </c>
       <c r="AW35" s="6" t="s">
-        <v>341</v>
+        <v>65</v>
       </c>
       <c r="AX35" s="6" t="s">
         <v>117</v>
@@ -7482,97 +7473,97 @@
         <v>65</v>
       </c>
       <c r="BA35" s="8">
-        <v>46174.99998842592</v>
+        <v>46181.458333333336</v>
       </c>
       <c r="BB35" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC35" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD35" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE35" s="10">
-        <v>41056.97</v>
+        <v>347</v>
+      </c>
+      <c r="BD35" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE35" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF35" s="10">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="BG35" s="10">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="BH35" s="6" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="BI35" s="6" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="BJ35" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="36" ht="23" customHeight="1">
+    <row r="36">
       <c r="A36" s="7">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B36" s="7">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D36" s="8">
-        <v>46098.67728869213</v>
+        <v>46099.78041990741</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O36" s="7">
-        <v>336908</v>
-      </c>
-      <c r="P36" s="8" t="s">
-        <v>65</v>
+        <v>337252</v>
+      </c>
+      <c r="P36" s="8">
+        <v>45739.125</v>
       </c>
       <c r="Q36" s="9">
-        <v>46097.666666666664</v>
+        <v>46097.680555555555</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S36" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="T36" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="T36" s="6" t="s">
-        <v>343</v>
-      </c>
       <c r="U36" s="6" t="s">
         <v>65</v>
       </c>
@@ -7589,28 +7580,28 @@
         <v>65</v>
       </c>
       <c r="Z36" s="10">
-        <v>194.95</v>
+        <v>581.49</v>
       </c>
       <c r="AA36" s="10">
         <v>0</v>
       </c>
       <c r="AB36" s="10">
-        <v>194.95</v>
+        <v>581.49</v>
       </c>
       <c r="AC36" s="6" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AD36" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE36" s="8">
-        <v>46097.791666666664</v>
+        <v>46097.805555555555</v>
       </c>
       <c r="AF36" s="7">
-        <v>45764</v>
+        <v>102507</v>
       </c>
       <c r="AG36" s="9">
-        <v>46100.406643518516</v>
+        <v>46175.35748842593</v>
       </c>
       <c r="AH36" s="6" t="s">
         <v>65</v>
@@ -7619,13 +7610,13 @@
         <v>78</v>
       </c>
       <c r="AJ36" s="11">
-        <v>0</v>
+        <v>0.013207547169811</v>
       </c>
       <c r="AK36" s="6" t="s">
-        <v>350</v>
+        <v>136</v>
       </c>
       <c r="AL36" s="6" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AM36" s="6" t="s">
         <v>65</v>
@@ -7637,19 +7628,19 @@
         <v>65</v>
       </c>
       <c r="AP36" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ36" s="10" t="s">
-        <v>65</v>
+        <v>239</v>
+      </c>
+      <c r="AQ36" s="10">
+        <v>0</v>
       </c>
       <c r="AR36" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS36" s="6" t="s">
-        <v>65</v>
+        <v>355</v>
       </c>
       <c r="AT36" s="7">
-        <v>2</v>
+        <v>4367</v>
       </c>
       <c r="AU36" s="6" t="s">
         <v>82</v>
@@ -7670,87 +7661,87 @@
         <v>65</v>
       </c>
       <c r="BA36" s="8">
-        <v>46181.458333333336</v>
+        <v>46181.99998842592</v>
       </c>
       <c r="BB36" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC36" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="BD36" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE36" s="10" t="s">
-        <v>65</v>
+        <v>356</v>
+      </c>
+      <c r="BD36" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE36" s="10">
+        <v>53000</v>
       </c>
       <c r="BF36" s="10">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="BG36" s="10">
         <v>700</v>
       </c>
       <c r="BH36" s="6" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="BI36" s="6" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="BJ36" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="37" ht="23" customHeight="1">
+    <row r="37">
       <c r="A37" s="7">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B37" s="7">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D37" s="8">
-        <v>46099.78041990741</v>
+        <v>46119.56219482639</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O37" s="7">
-        <v>337252</v>
+        <v>340486</v>
       </c>
       <c r="P37" s="8">
-        <v>45739.125</v>
+        <v>45307.125</v>
       </c>
       <c r="Q37" s="9">
-        <v>46097.680555555555</v>
+        <v>46118.72222222222</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>65</v>
@@ -7759,7 +7750,7 @@
         <v>105</v>
       </c>
       <c r="T37" s="6" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="U37" s="6" t="s">
         <v>65</v>
@@ -7777,28 +7768,28 @@
         <v>65</v>
       </c>
       <c r="Z37" s="10">
-        <v>581.49</v>
+        <v>832.11</v>
       </c>
       <c r="AA37" s="10">
         <v>0</v>
       </c>
       <c r="AB37" s="10">
-        <v>581.49</v>
+        <v>832.11</v>
       </c>
       <c r="AC37" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD37" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE37" s="8">
-        <v>46097.805555555555</v>
+        <v>46118.850694444445</v>
       </c>
       <c r="AF37" s="7">
-        <v>101722</v>
+        <v>185000</v>
       </c>
       <c r="AG37" s="9">
-        <v>46168.634780092594</v>
+        <v>46176.39858796296</v>
       </c>
       <c r="AH37" s="6" t="s">
         <v>65</v>
@@ -7807,13 +7798,13 @@
         <v>78</v>
       </c>
       <c r="AJ37" s="11">
-        <v>0.013207547169811</v>
+        <v>0.015764705882352</v>
       </c>
       <c r="AK37" s="6" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="AL37" s="6" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AM37" s="6" t="s">
         <v>65</v>
@@ -7825,7 +7816,7 @@
         <v>65</v>
       </c>
       <c r="AP37" s="6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AQ37" s="10">
         <v>0</v>
@@ -7834,10 +7825,10 @@
         <v>65</v>
       </c>
       <c r="AS37" s="6" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AT37" s="7">
-        <v>4583</v>
+        <v>2038</v>
       </c>
       <c r="AU37" s="6" t="s">
         <v>82</v>
@@ -7858,7 +7849,7 @@
         <v>65</v>
       </c>
       <c r="BA37" s="8">
-        <v>46181.99998842592</v>
+        <v>46202.99998842592</v>
       </c>
       <c r="BB37" s="9" t="s">
         <v>65</v>
@@ -7870,84 +7861,84 @@
         <v>0</v>
       </c>
       <c r="BE37" s="10">
-        <v>53000</v>
+        <v>42500</v>
       </c>
       <c r="BF37" s="10">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="BG37" s="10">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="BH37" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="BI37" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="BJ37" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="38" ht="23" customHeight="1">
+    <row r="38">
       <c r="A38" s="7">
+        <v>2021</v>
+      </c>
+      <c r="B38" s="7">
         <v>2020</v>
       </c>
-      <c r="B38" s="7">
-        <v>2019</v>
-      </c>
       <c r="C38" s="6" t="s">
-        <v>360</v>
+        <v>65</v>
       </c>
       <c r="D38" s="8">
-        <v>46119.56219482639</v>
+        <v>46135.522659375</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="O38" s="7">
-        <v>340486</v>
+      <c r="O38" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="P38" s="8">
-        <v>45307.125</v>
+        <v>45182.125</v>
       </c>
       <c r="Q38" s="9">
-        <v>46118.72222222222</v>
+        <v>46119.583333333336</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S38" s="6" t="s">
-        <v>165</v>
+        <v>354</v>
       </c>
       <c r="T38" s="6" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="U38" s="6" t="s">
         <v>65</v>
@@ -7965,43 +7956,43 @@
         <v>65</v>
       </c>
       <c r="Z38" s="10">
-        <v>603.9</v>
+        <v>90.96</v>
       </c>
       <c r="AA38" s="10">
         <v>0</v>
       </c>
       <c r="AB38" s="10">
-        <v>603.9</v>
+        <v>90.96</v>
       </c>
       <c r="AC38" s="6" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD38" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE38" s="8">
-        <v>46118.850694444445</v>
+        <v>46119.708333333336</v>
       </c>
       <c r="AF38" s="7">
-        <v>183592</v>
+        <v>248739</v>
       </c>
       <c r="AG38" s="9">
-        <v>46168.63481481482</v>
+        <v>46175.357511574075</v>
       </c>
       <c r="AH38" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AI38" s="6" t="s">
-        <v>365</v>
+        <v>78</v>
       </c>
       <c r="AJ38" s="11">
-        <v>0.015764705882352</v>
+        <v>0.053635736725155</v>
       </c>
       <c r="AK38" s="6" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="AL38" s="6" t="s">
-        <v>362</v>
+        <v>65</v>
       </c>
       <c r="AM38" s="6" t="s">
         <v>65</v>
@@ -8013,7 +8004,7 @@
         <v>65</v>
       </c>
       <c r="AP38" s="6" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="AQ38" s="10">
         <v>0</v>
@@ -8022,10 +8013,10 @@
         <v>65</v>
       </c>
       <c r="AS38" s="6" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AT38" s="7">
-        <v>1578</v>
+        <v>383</v>
       </c>
       <c r="AU38" s="6" t="s">
         <v>82</v>
@@ -8037,16 +8028,16 @@
         <v>65</v>
       </c>
       <c r="AX38" s="6" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="AY38" s="6" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="AZ38" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA38" s="8">
-        <v>46202.99998842592</v>
+        <v>46180.708333333336</v>
       </c>
       <c r="BB38" s="9" t="s">
         <v>65</v>
@@ -8058,81 +8049,81 @@
         <v>0</v>
       </c>
       <c r="BE38" s="10">
-        <v>42500</v>
+        <v>39153</v>
       </c>
       <c r="BF38" s="10">
-        <v>670</v>
+        <v>2100</v>
       </c>
       <c r="BG38" s="10">
-        <v>670</v>
+        <v>2100</v>
       </c>
       <c r="BH38" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="BI38" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="BJ38" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="39" ht="23" customHeight="1">
+    <row r="39">
       <c r="A39" s="7">
         <v>2021</v>
       </c>
       <c r="B39" s="7">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>65</v>
+        <v>372</v>
       </c>
       <c r="D39" s="8">
-        <v>46135.522659375</v>
+        <v>46127.52819641204</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="O39" s="7" t="s">
-        <v>65</v>
+      <c r="O39" s="7">
+        <v>341919</v>
       </c>
       <c r="P39" s="8">
-        <v>45182.125</v>
+        <v>45105.125</v>
       </c>
       <c r="Q39" s="9">
-        <v>46119.583333333336</v>
+        <v>46126.604166666664</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S39" s="6" t="s">
-        <v>105</v>
+        <v>220</v>
       </c>
       <c r="T39" s="6" t="s">
         <v>372</v>
@@ -8159,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="AB39" s="10">
-        <v>90.96</v>
+        <v>150.96</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>76</v>
@@ -8168,13 +8159,13 @@
         <v>65</v>
       </c>
       <c r="AE39" s="8">
-        <v>46119.708333333336</v>
+        <v>46125.458333333336</v>
       </c>
       <c r="AF39" s="7">
-        <v>248313</v>
+        <v>200440</v>
       </c>
       <c r="AG39" s="9">
-        <v>46168.63481481482</v>
+        <v>46175.357523148145</v>
       </c>
       <c r="AH39" s="6" t="s">
         <v>65</v>
@@ -8183,13 +8174,13 @@
         <v>78</v>
       </c>
       <c r="AJ39" s="11">
-        <v>0.053635736725155</v>
+        <v>0.0208</v>
       </c>
       <c r="AK39" s="6" t="s">
         <v>79</v>
       </c>
       <c r="AL39" s="6" t="s">
-        <v>65</v>
+        <v>374</v>
       </c>
       <c r="AM39" s="6" t="s">
         <v>65</v>
@@ -8201,7 +8192,7 @@
         <v>65</v>
       </c>
       <c r="AP39" s="6" t="s">
-        <v>113</v>
+        <v>239</v>
       </c>
       <c r="AQ39" s="10">
         <v>0</v>
@@ -8210,10 +8201,10 @@
         <v>65</v>
       </c>
       <c r="AS39" s="6" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AT39" s="7">
-        <v>200</v>
+        <v>4010</v>
       </c>
       <c r="AU39" s="6" t="s">
         <v>82</v>
@@ -8225,16 +8216,16 @@
         <v>65</v>
       </c>
       <c r="AX39" s="6" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="AY39" s="6" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="AZ39" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA39" s="8">
-        <v>46180.708333333336</v>
+        <v>46209.99998842592</v>
       </c>
       <c r="BB39" s="9" t="s">
         <v>65</v>
@@ -8246,85 +8237,85 @@
         <v>0</v>
       </c>
       <c r="BE39" s="10">
-        <v>39153</v>
+        <v>31250</v>
       </c>
       <c r="BF39" s="10">
-        <v>2100</v>
+        <v>650</v>
       </c>
       <c r="BG39" s="10">
-        <v>2100</v>
+        <v>650</v>
       </c>
       <c r="BH39" s="6" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="BI39" s="6" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="BJ39" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="40" ht="23" customHeight="1">
+    <row r="40">
       <c r="A40" s="7">
-        <v>2021</v>
+        <v>2027</v>
       </c>
       <c r="B40" s="7">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D40" s="8">
-        <v>46127.52819641204</v>
+        <v>46148.59058966435</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M40" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O40" s="7">
+        <v>345722</v>
+      </c>
+      <c r="P40" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q40" s="9">
+        <v>46142.5</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S40" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="T40" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="N40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O40" s="7">
-        <v>341919</v>
-      </c>
-      <c r="P40" s="8">
-        <v>45105.125</v>
-      </c>
-      <c r="Q40" s="9">
-        <v>46126.604166666664</v>
-      </c>
-      <c r="R40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S40" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="T40" s="6" t="s">
-        <v>375</v>
-      </c>
       <c r="U40" s="6" t="s">
         <v>65</v>
       </c>
@@ -8341,13 +8332,13 @@
         <v>65</v>
       </c>
       <c r="Z40" s="10">
-        <v>90.96</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="10">
         <v>0</v>
       </c>
       <c r="AB40" s="10">
-        <v>150.96</v>
+        <v>0</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>76</v>
@@ -8356,13 +8347,13 @@
         <v>65</v>
       </c>
       <c r="AE40" s="8">
-        <v>46125.458333333336</v>
+        <v>46142.625</v>
       </c>
       <c r="AF40" s="7">
-        <v>199199</v>
+        <v>25</v>
       </c>
       <c r="AG40" s="9">
-        <v>46168.63482638889</v>
+        <v>46142.5</v>
       </c>
       <c r="AH40" s="6" t="s">
         <v>65</v>
@@ -8371,13 +8362,13 @@
         <v>78</v>
       </c>
       <c r="AJ40" s="11">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="AK40" s="6" t="s">
-        <v>79</v>
+        <v>385</v>
       </c>
       <c r="AL40" s="6" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AM40" s="6" t="s">
         <v>65</v>
@@ -8389,19 +8380,19 @@
         <v>65</v>
       </c>
       <c r="AP40" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ40" s="10">
-        <v>0</v>
+        <v>239</v>
+      </c>
+      <c r="AQ40" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR40" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS40" s="6" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="AT40" s="7">
-        <v>3985</v>
+        <v>0</v>
       </c>
       <c r="AU40" s="6" t="s">
         <v>82</v>
@@ -8422,96 +8413,96 @@
         <v>65</v>
       </c>
       <c r="BA40" s="8">
-        <v>46209.99998842592</v>
+        <v>46223.99998842592</v>
       </c>
       <c r="BB40" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC40" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD40" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE40" s="10">
-        <v>31250</v>
+        <v>387</v>
+      </c>
+      <c r="BD40" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE40" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF40" s="10">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="BG40" s="10">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="BH40" s="6" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="BI40" s="6" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="BJ40" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="41" ht="23" customHeight="1">
+    <row r="41">
       <c r="A41" s="7">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="B41" s="7">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="D41" s="8">
-        <v>46148.59058966435</v>
+        <v>45889.59072010417</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="L41" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O41" s="7">
-        <v>345722</v>
-      </c>
-      <c r="P41" s="8" t="s">
-        <v>65</v>
+        <v>287442</v>
+      </c>
+      <c r="P41" s="8">
+        <v>45030</v>
       </c>
       <c r="Q41" s="9">
-        <v>46142.5</v>
+        <v>46146.17013888889</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S41" s="6" t="s">
-        <v>387</v>
+        <v>166</v>
       </c>
       <c r="T41" s="6" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="U41" s="6" t="s">
         <v>65</v>
@@ -8529,13 +8520,13 @@
         <v>65</v>
       </c>
       <c r="Z41" s="10">
-        <v>0</v>
+        <v>944.54</v>
       </c>
       <c r="AA41" s="10">
         <v>0</v>
       </c>
       <c r="AB41" s="10">
-        <v>0</v>
+        <v>944.54</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>76</v>
@@ -8544,13 +8535,13 @@
         <v>65</v>
       </c>
       <c r="AE41" s="8">
-        <v>46142.625</v>
+        <v>46146.458333333336</v>
       </c>
       <c r="AF41" s="7">
-        <v>25</v>
+        <v>224499</v>
       </c>
       <c r="AG41" s="9">
-        <v>46142.5</v>
+        <v>46175.357523148145</v>
       </c>
       <c r="AH41" s="6" t="s">
         <v>65</v>
@@ -8559,13 +8550,13 @@
         <v>78</v>
       </c>
       <c r="AJ41" s="11">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="AK41" s="6" t="s">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="AL41" s="6" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AM41" s="6" t="s">
         <v>65</v>
@@ -8577,7 +8568,7 @@
         <v>65</v>
       </c>
       <c r="AP41" s="6" t="s">
-        <v>244</v>
+        <v>127</v>
       </c>
       <c r="AQ41" s="10" t="s">
         <v>65</v>
@@ -8586,10 +8577,10 @@
         <v>65</v>
       </c>
       <c r="AS41" s="6" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AT41" s="7">
-        <v>0</v>
+        <v>3293</v>
       </c>
       <c r="AU41" s="6" t="s">
         <v>82</v>
@@ -8598,7 +8589,7 @@
         <v>83</v>
       </c>
       <c r="AW41" s="6" t="s">
-        <v>65</v>
+        <v>395</v>
       </c>
       <c r="AX41" s="6" t="s">
         <v>117</v>
@@ -8610,96 +8601,96 @@
         <v>65</v>
       </c>
       <c r="BA41" s="8">
-        <v>46223.99998842592</v>
+        <v>46202.99998842592</v>
       </c>
       <c r="BB41" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC41" s="6" t="s">
-        <v>390</v>
+        <v>87</v>
       </c>
       <c r="BD41" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="BE41" s="10" t="s">
-        <v>65</v>
+      <c r="BE41" s="10">
+        <v>45000</v>
       </c>
       <c r="BF41" s="10">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="BG41" s="10">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="BH41" s="6" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="BI41" s="6" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="BJ41" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="42" ht="23" customHeight="1">
+    <row r="42">
       <c r="A42" s="7">
-        <v>2020</v>
+        <v>2027</v>
       </c>
       <c r="B42" s="7">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D42" s="8">
-        <v>45889.59072010417</v>
+        <v>46148.57752453704</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="L42" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O42" s="7">
-        <v>287442</v>
-      </c>
-      <c r="P42" s="8">
-        <v>45030</v>
+        <v>345716</v>
+      </c>
+      <c r="P42" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="Q42" s="9">
-        <v>46146.17013888889</v>
+        <v>46147.625</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S42" s="6" t="s">
-        <v>165</v>
+        <v>384</v>
       </c>
       <c r="T42" s="6" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="U42" s="6" t="s">
         <v>65</v>
@@ -8717,13 +8708,13 @@
         <v>65</v>
       </c>
       <c r="Z42" s="10">
-        <v>944.54</v>
+        <v>0</v>
       </c>
       <c r="AA42" s="10">
         <v>0</v>
       </c>
       <c r="AB42" s="10">
-        <v>944.54</v>
+        <v>0</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>76</v>
@@ -8732,13 +8723,13 @@
         <v>65</v>
       </c>
       <c r="AE42" s="8">
-        <v>46146.458333333336</v>
+        <v>46147.75</v>
       </c>
       <c r="AF42" s="7">
-        <v>224000</v>
+        <v>24</v>
       </c>
       <c r="AG42" s="9">
-        <v>46170.36310185185</v>
+        <v>46147.625</v>
       </c>
       <c r="AH42" s="6" t="s">
         <v>65</v>
@@ -8747,13 +8738,13 @@
         <v>78</v>
       </c>
       <c r="AJ42" s="11">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="AK42" s="6" t="s">
-        <v>79</v>
+        <v>385</v>
       </c>
       <c r="AL42" s="6" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AM42" s="6" t="s">
         <v>65</v>
@@ -8765,7 +8756,7 @@
         <v>65</v>
       </c>
       <c r="AP42" s="6" t="s">
-        <v>128</v>
+        <v>239</v>
       </c>
       <c r="AQ42" s="10" t="s">
         <v>65</v>
@@ -8774,10 +8765,10 @@
         <v>65</v>
       </c>
       <c r="AS42" s="6" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AT42" s="7">
-        <v>3905</v>
+        <v>0</v>
       </c>
       <c r="AU42" s="6" t="s">
         <v>82</v>
@@ -8786,7 +8777,7 @@
         <v>83</v>
       </c>
       <c r="AW42" s="6" t="s">
-        <v>398</v>
+        <v>65</v>
       </c>
       <c r="AX42" s="6" t="s">
         <v>117</v>
@@ -8798,96 +8789,96 @@
         <v>65</v>
       </c>
       <c r="BA42" s="8">
-        <v>46174.99998842592</v>
+        <v>46230.99998842592</v>
       </c>
       <c r="BB42" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC42" s="6" t="s">
-        <v>87</v>
+        <v>387</v>
       </c>
       <c r="BD42" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="BE42" s="10">
-        <v>45000</v>
+      <c r="BE42" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF42" s="10">
-        <v>630</v>
+        <v>1200</v>
       </c>
       <c r="BG42" s="10">
-        <v>630</v>
+        <v>1200</v>
       </c>
       <c r="BH42" s="6" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="BI42" s="6" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="BJ42" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="43" ht="23" customHeight="1">
+    <row r="43">
       <c r="A43" s="7">
-        <v>2027</v>
+        <v>2018</v>
       </c>
       <c r="B43" s="7">
-        <v>2026</v>
+        <v>2017</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D43" s="8">
-        <v>46148.57752453704</v>
+        <v>46153.58720679398</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="L43" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M43" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O43" s="7">
+        <v>346470</v>
+      </c>
+      <c r="P43" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>46150.583333333336</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S43" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="T43" s="6" t="s">
         <v>404</v>
-      </c>
-      <c r="N43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O43" s="7">
-        <v>345716</v>
-      </c>
-      <c r="P43" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q43" s="9">
-        <v>46147.625</v>
-      </c>
-      <c r="R43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S43" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="T43" s="6" t="s">
-        <v>400</v>
       </c>
       <c r="U43" s="6" t="s">
         <v>65</v>
@@ -8920,13 +8911,13 @@
         <v>65</v>
       </c>
       <c r="AE43" s="8">
-        <v>46147.75</v>
+        <v>46150.67013888889</v>
       </c>
       <c r="AF43" s="7">
-        <v>24</v>
+        <v>107165</v>
       </c>
       <c r="AG43" s="9">
-        <v>46147.625</v>
+        <v>46150.583333333336</v>
       </c>
       <c r="AH43" s="6" t="s">
         <v>65</v>
@@ -8938,10 +8929,10 @@
         <v>0</v>
       </c>
       <c r="AK43" s="6" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="AL43" s="6" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AM43" s="6" t="s">
         <v>65</v>
@@ -8953,7 +8944,7 @@
         <v>65</v>
       </c>
       <c r="AP43" s="6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AQ43" s="10" t="s">
         <v>65</v>
@@ -8962,7 +8953,7 @@
         <v>65</v>
       </c>
       <c r="AS43" s="6" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="AT43" s="7">
         <v>0</v>
@@ -8992,7 +8983,7 @@
         <v>65</v>
       </c>
       <c r="BC43" s="6" t="s">
-        <v>390</v>
+        <v>87</v>
       </c>
       <c r="BD43" s="10" t="s">
         <v>65</v>
@@ -9001,81 +8992,81 @@
         <v>65</v>
       </c>
       <c r="BF43" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BG43" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BH43" s="6" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="BI43" s="6" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="BJ43" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="44" ht="23" customHeight="1">
+    <row r="44">
       <c r="A44" s="7">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B44" s="7">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D44" s="8">
-        <v>46153.58720679398</v>
+        <v>45890.75695732639</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O44" s="7">
-        <v>346470</v>
-      </c>
-      <c r="P44" s="8" t="s">
-        <v>65</v>
+        <v>287667</v>
+      </c>
+      <c r="P44" s="8">
+        <v>45832.125</v>
       </c>
       <c r="Q44" s="9">
-        <v>46150.583333333336</v>
+        <v>46153.333333333336</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S44" s="6" t="s">
-        <v>412</v>
+        <v>146</v>
       </c>
       <c r="T44" s="6" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="U44" s="6" t="s">
         <v>65</v>
@@ -9102,19 +9093,19 @@
         <v>0</v>
       </c>
       <c r="AC44" s="6" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AD44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE44" s="8">
-        <v>46150.67013888889</v>
+        <v>46153.458333333336</v>
       </c>
       <c r="AF44" s="7">
-        <v>107165</v>
+        <v>118640</v>
       </c>
       <c r="AG44" s="9">
-        <v>46150.583333333336</v>
+        <v>46175.3575</v>
       </c>
       <c r="AH44" s="6" t="s">
         <v>65</v>
@@ -9123,13 +9114,13 @@
         <v>78</v>
       </c>
       <c r="AJ44" s="11">
-        <v>0</v>
+        <v>0.012903225806451</v>
       </c>
       <c r="AK44" s="6" t="s">
-        <v>413</v>
+        <v>136</v>
       </c>
       <c r="AL44" s="6" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="AM44" s="6" t="s">
         <v>65</v>
@@ -9141,19 +9132,19 @@
         <v>65</v>
       </c>
       <c r="AP44" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ44" s="10" t="s">
-        <v>65</v>
+        <v>186</v>
+      </c>
+      <c r="AQ44" s="10">
+        <v>0</v>
       </c>
       <c r="AR44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS44" s="6" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AT44" s="7">
-        <v>0</v>
+        <v>2349</v>
       </c>
       <c r="AU44" s="6" t="s">
         <v>82</v>
@@ -9162,7 +9153,7 @@
         <v>83</v>
       </c>
       <c r="AW44" s="6" t="s">
-        <v>65</v>
+        <v>419</v>
       </c>
       <c r="AX44" s="6" t="s">
         <v>117</v>
@@ -9174,96 +9165,96 @@
         <v>65</v>
       </c>
       <c r="BA44" s="8">
-        <v>46230.99998842592</v>
+        <v>46209.99998842592</v>
       </c>
       <c r="BB44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC44" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD44" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE44" s="10" t="s">
-        <v>65</v>
+        <v>356</v>
+      </c>
+      <c r="BD44" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE44" s="10">
+        <v>52700</v>
       </c>
       <c r="BF44" s="10">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="BG44" s="10">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="BH44" s="6" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="BI44" s="6" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="BJ44" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="45" ht="23" customHeight="1">
+    <row r="45">
       <c r="A45" s="7">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B45" s="7">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D45" s="8">
-        <v>45890.75695732639</v>
+        <v>46101.54787534722</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="L45" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O45" s="7">
-        <v>287667</v>
-      </c>
-      <c r="P45" s="8">
-        <v>45832.125</v>
+        <v>337543</v>
+      </c>
+      <c r="P45" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="Q45" s="9">
-        <v>46153.333333333336</v>
+        <v>46147.625</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S45" s="6" t="s">
-        <v>147</v>
+        <v>384</v>
       </c>
       <c r="T45" s="6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="U45" s="6" t="s">
         <v>65</v>
@@ -9290,19 +9281,19 @@
         <v>0</v>
       </c>
       <c r="AC45" s="6" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD45" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE45" s="8">
-        <v>46153.458333333336</v>
+        <v>46153.75</v>
       </c>
       <c r="AF45" s="7">
-        <v>116840</v>
+        <v>55000</v>
       </c>
       <c r="AG45" s="9">
-        <v>46168.634791666664</v>
+        <v>46147.625</v>
       </c>
       <c r="AH45" s="6" t="s">
         <v>65</v>
@@ -9311,13 +9302,13 @@
         <v>78</v>
       </c>
       <c r="AJ45" s="11">
-        <v>0.012903225806451</v>
+        <v>0</v>
       </c>
       <c r="AK45" s="6" t="s">
-        <v>137</v>
+        <v>346</v>
       </c>
       <c r="AL45" s="6" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AM45" s="6" t="s">
         <v>65</v>
@@ -9329,19 +9320,19 @@
         <v>65</v>
       </c>
       <c r="AP45" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="AQ45" s="10">
-        <v>0</v>
+        <v>239</v>
+      </c>
+      <c r="AQ45" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR45" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS45" s="6" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AT45" s="7">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="AU45" s="6" t="s">
         <v>82</v>
@@ -9350,7 +9341,7 @@
         <v>83</v>
       </c>
       <c r="AW45" s="6" t="s">
-        <v>422</v>
+        <v>65</v>
       </c>
       <c r="AX45" s="6" t="s">
         <v>117</v>
@@ -9362,96 +9353,96 @@
         <v>65</v>
       </c>
       <c r="BA45" s="8">
-        <v>46209.99998842592</v>
+        <v>46237.99998842592</v>
       </c>
       <c r="BB45" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC45" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD45" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE45" s="10">
-        <v>52700</v>
+        <v>347</v>
+      </c>
+      <c r="BD45" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE45" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF45" s="10">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="BG45" s="10">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="BH45" s="6" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="BI45" s="6" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="BJ45" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="46" ht="23" customHeight="1">
+    <row r="46">
       <c r="A46" s="7">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="B46" s="7">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D46" s="8">
-        <v>46101.54787534722</v>
+        <v>46160.53526894676</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="L46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M46" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O46" s="7">
+        <v>347450</v>
+      </c>
+      <c r="P46" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q46" s="9">
+        <v>46154.333333333336</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S46" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="T46" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O46" s="7">
-        <v>337543</v>
-      </c>
-      <c r="P46" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q46" s="9">
-        <v>46147.625</v>
-      </c>
-      <c r="R46" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S46" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="T46" s="6" t="s">
-        <v>424</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>65</v>
@@ -9484,13 +9475,13 @@
         <v>65</v>
       </c>
       <c r="AE46" s="8">
-        <v>46153.75</v>
+        <v>46154.458333333336</v>
       </c>
       <c r="AF46" s="7">
-        <v>55000</v>
+        <v>1</v>
       </c>
       <c r="AG46" s="9">
-        <v>46147.625</v>
+        <v>46154.333333333336</v>
       </c>
       <c r="AH46" s="6" t="s">
         <v>65</v>
@@ -9502,10 +9493,10 @@
         <v>0</v>
       </c>
       <c r="AK46" s="6" t="s">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="AL46" s="6" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AM46" s="6" t="s">
         <v>65</v>
@@ -9517,7 +9508,7 @@
         <v>65</v>
       </c>
       <c r="AP46" s="6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AQ46" s="10" t="s">
         <v>65</v>
@@ -9526,7 +9517,7 @@
         <v>65</v>
       </c>
       <c r="AS46" s="6" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AT46" s="7">
         <v>0</v>
@@ -9547,7 +9538,7 @@
         <v>118</v>
       </c>
       <c r="AZ46" s="6" t="s">
-        <v>65</v>
+        <v>435</v>
       </c>
       <c r="BA46" s="8">
         <v>46237.99998842592</v>
@@ -9556,7 +9547,7 @@
         <v>65</v>
       </c>
       <c r="BC46" s="6" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="BD46" s="10" t="s">
         <v>65</v>
@@ -9565,81 +9556,81 @@
         <v>65</v>
       </c>
       <c r="BF46" s="10">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="BG46" s="10">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="BH46" s="6" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="BI46" s="6" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="BJ46" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="47" ht="23" customHeight="1">
+    <row r="47">
       <c r="A47" s="7">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="B47" s="7">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D47" s="8">
-        <v>46160.53526894676</v>
+        <v>46160.537332175925</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="L47" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O47" s="7">
-        <v>347450</v>
-      </c>
-      <c r="P47" s="8" t="s">
-        <v>65</v>
+        <v>347451</v>
+      </c>
+      <c r="P47" s="8">
+        <v>45061.125</v>
       </c>
       <c r="Q47" s="9">
-        <v>46154.333333333336</v>
+        <v>46157.416666666664</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S47" s="6" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="T47" s="6" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="U47" s="6" t="s">
         <v>65</v>
@@ -9657,13 +9648,13 @@
         <v>65</v>
       </c>
       <c r="Z47" s="10">
-        <v>0</v>
+        <v>266.88</v>
       </c>
       <c r="AA47" s="10">
         <v>0</v>
       </c>
       <c r="AB47" s="10">
-        <v>0</v>
+        <v>266.88</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>76</v>
@@ -9672,13 +9663,13 @@
         <v>65</v>
       </c>
       <c r="AE47" s="8">
-        <v>46154.458333333336</v>
+        <v>46157.541666666664</v>
       </c>
       <c r="AF47" s="7">
-        <v>1</v>
+        <v>216088</v>
       </c>
       <c r="AG47" s="9">
-        <v>46154.333333333336</v>
+        <v>46176.428391203706</v>
       </c>
       <c r="AH47" s="6" t="s">
         <v>65</v>
@@ -9687,13 +9678,13 @@
         <v>78</v>
       </c>
       <c r="AJ47" s="11">
-        <v>0</v>
+        <v>0.015662650602409</v>
       </c>
       <c r="AK47" s="6" t="s">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="AL47" s="6" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="AM47" s="6" t="s">
         <v>65</v>
@@ -9705,19 +9696,19 @@
         <v>65</v>
       </c>
       <c r="AP47" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ47" s="10" t="s">
-        <v>65</v>
+        <v>239</v>
+      </c>
+      <c r="AQ47" s="10">
+        <v>0</v>
       </c>
       <c r="AR47" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS47" s="6" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="AT47" s="7">
-        <v>0</v>
+        <v>3849</v>
       </c>
       <c r="AU47" s="6" t="s">
         <v>82</v>
@@ -9735,7 +9726,7 @@
         <v>118</v>
       </c>
       <c r="AZ47" s="6" t="s">
-        <v>437</v>
+        <v>65</v>
       </c>
       <c r="BA47" s="8">
         <v>46237.99998842592</v>
@@ -9744,90 +9735,90 @@
         <v>65</v>
       </c>
       <c r="BC47" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD47" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE47" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD47" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE47" s="10">
+        <v>41500</v>
       </c>
       <c r="BF47" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BG47" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BH47" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="BI47" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="BJ47" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="48" ht="23" customHeight="1">
+    <row r="48">
       <c r="A48" s="7">
-        <v>2020</v>
+        <v>2027</v>
       </c>
       <c r="B48" s="7">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D48" s="8">
-        <v>46160.537332175925</v>
+        <v>46160.53851987269</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="L48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O48" s="7">
-        <v>347451</v>
-      </c>
-      <c r="P48" s="8">
-        <v>45061.125</v>
+        <v>347452</v>
+      </c>
+      <c r="P48" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="Q48" s="9">
-        <v>46157.416666666664</v>
+        <v>46158.333333333336</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S48" s="6" t="s">
-        <v>195</v>
+        <v>433</v>
       </c>
       <c r="T48" s="6" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="U48" s="6" t="s">
         <v>65</v>
@@ -9860,13 +9851,13 @@
         <v>65</v>
       </c>
       <c r="AE48" s="8">
-        <v>46157.541666666664</v>
+        <v>46158.458333333336</v>
       </c>
       <c r="AF48" s="7">
-        <v>214976</v>
+        <v>1</v>
       </c>
       <c r="AG48" s="9">
-        <v>46168.63481481482</v>
+        <v>46158.333333333336</v>
       </c>
       <c r="AH48" s="6" t="s">
         <v>65</v>
@@ -9875,13 +9866,13 @@
         <v>78</v>
       </c>
       <c r="AJ48" s="11">
-        <v>0.015662650602409</v>
+        <v>0</v>
       </c>
       <c r="AK48" s="6" t="s">
-        <v>79</v>
+        <v>385</v>
       </c>
       <c r="AL48" s="6" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AM48" s="6" t="s">
         <v>65</v>
@@ -9893,19 +9884,19 @@
         <v>65</v>
       </c>
       <c r="AP48" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ48" s="10">
-        <v>0</v>
+        <v>239</v>
+      </c>
+      <c r="AQ48" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS48" s="6" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AT48" s="7">
-        <v>3948</v>
+        <v>0</v>
       </c>
       <c r="AU48" s="6" t="s">
         <v>82</v>
@@ -9923,7 +9914,7 @@
         <v>118</v>
       </c>
       <c r="AZ48" s="6" t="s">
-        <v>65</v>
+        <v>435</v>
       </c>
       <c r="BA48" s="8">
         <v>46237.99998842592</v>
@@ -9932,90 +9923,90 @@
         <v>65</v>
       </c>
       <c r="BC48" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD48" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE48" s="10">
-        <v>41500</v>
+        <v>387</v>
+      </c>
+      <c r="BD48" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE48" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF48" s="10">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="BG48" s="10">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="BH48" s="6" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="BI48" s="6" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="BJ48" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="49" ht="23" customHeight="1">
+    <row r="49">
       <c r="A49" s="7">
-        <v>2027</v>
+        <v>2021</v>
       </c>
       <c r="B49" s="7">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D49" s="8">
-        <v>46160.53851987269</v>
+        <v>46003.72969502315</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="L49" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O49" s="7">
-        <v>347452</v>
-      </c>
-      <c r="P49" s="8" t="s">
-        <v>65</v>
+        <v>320775</v>
+      </c>
+      <c r="P49" s="8">
+        <v>36526.083333333336</v>
       </c>
       <c r="Q49" s="9">
-        <v>46158.333333333336</v>
+        <v>46160.336805555555</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S49" s="6" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="T49" s="6" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="U49" s="6" t="s">
         <v>65</v>
@@ -10033,13 +10024,13 @@
         <v>65</v>
       </c>
       <c r="Z49" s="10">
-        <v>0</v>
+        <v>280.3</v>
       </c>
       <c r="AA49" s="10">
         <v>0</v>
       </c>
       <c r="AB49" s="10">
-        <v>0</v>
+        <v>280.3</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>76</v>
@@ -10048,13 +10039,13 @@
         <v>65</v>
       </c>
       <c r="AE49" s="8">
-        <v>46158.458333333336</v>
+        <v>46160.461805555555</v>
       </c>
       <c r="AF49" s="7">
-        <v>1</v>
+        <v>193340</v>
       </c>
       <c r="AG49" s="9">
-        <v>46158.333333333336</v>
+        <v>46176.39202546296</v>
       </c>
       <c r="AH49" s="6" t="s">
         <v>65</v>
@@ -10063,13 +10054,13 @@
         <v>78</v>
       </c>
       <c r="AJ49" s="11">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="AK49" s="6" t="s">
-        <v>388</v>
+        <v>456</v>
       </c>
       <c r="AL49" s="6" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AM49" s="6" t="s">
         <v>65</v>
@@ -10081,19 +10072,19 @@
         <v>65</v>
       </c>
       <c r="AP49" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ49" s="10" t="s">
-        <v>65</v>
+        <v>186</v>
+      </c>
+      <c r="AQ49" s="10">
+        <v>0</v>
       </c>
       <c r="AR49" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS49" s="6" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AT49" s="7">
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="AU49" s="6" t="s">
         <v>82</v>
@@ -10102,7 +10093,7 @@
         <v>83</v>
       </c>
       <c r="AW49" s="6" t="s">
-        <v>65</v>
+        <v>458</v>
       </c>
       <c r="AX49" s="6" t="s">
         <v>117</v>
@@ -10111,99 +10102,99 @@
         <v>118</v>
       </c>
       <c r="AZ49" s="6" t="s">
-        <v>437</v>
+        <v>65</v>
       </c>
       <c r="BA49" s="8">
-        <v>46237.99998842592</v>
+        <v>46216.99998842592</v>
       </c>
       <c r="BB49" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC49" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD49" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE49" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD49" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE49" s="10">
+        <v>1</v>
       </c>
       <c r="BF49" s="10">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="BG49" s="10">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="BH49" s="6" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="BI49" s="6" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="BJ49" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50" ht="23" customHeight="1">
+    <row r="50">
       <c r="A50" s="7">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B50" s="7">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="D50" s="8">
-        <v>46003.72969502315</v>
+        <v>46057.51524019676</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="N50" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O50" s="7">
-        <v>320775</v>
+        <v>329595</v>
       </c>
       <c r="P50" s="8">
-        <v>36526.083333333336</v>
+        <v>45934.125</v>
       </c>
       <c r="Q50" s="9">
-        <v>46160.336805555555</v>
+        <v>46160.375</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S50" s="6" t="s">
-        <v>165</v>
+        <v>239</v>
       </c>
       <c r="T50" s="6" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="U50" s="6" t="s">
         <v>65</v>
@@ -10221,43 +10212,43 @@
         <v>65</v>
       </c>
       <c r="Z50" s="10">
-        <v>61.5</v>
+        <v>0</v>
       </c>
       <c r="AA50" s="10">
         <v>0</v>
       </c>
       <c r="AB50" s="10">
-        <v>61.5</v>
+        <v>0</v>
       </c>
       <c r="AC50" s="6" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AD50" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE50" s="8">
-        <v>46160.461805555555</v>
+        <v>46160.5</v>
       </c>
       <c r="AF50" s="7">
-        <v>28436</v>
+        <v>134362</v>
       </c>
       <c r="AG50" s="9">
-        <v>46168.63482638889</v>
+        <v>46175.357511574075</v>
       </c>
       <c r="AH50" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AI50" s="6" t="s">
-        <v>365</v>
+        <v>78</v>
       </c>
       <c r="AJ50" s="11">
-        <v>630</v>
+        <v>0.013359528487229</v>
       </c>
       <c r="AK50" s="6" t="s">
-        <v>458</v>
+        <v>136</v>
       </c>
       <c r="AL50" s="6" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="AM50" s="6" t="s">
         <v>65</v>
@@ -10278,10 +10269,10 @@
         <v>65</v>
       </c>
       <c r="AS50" s="6" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="AT50" s="7">
-        <v>-497975</v>
+        <v>2003</v>
       </c>
       <c r="AU50" s="6" t="s">
         <v>82</v>
@@ -10290,7 +10281,7 @@
         <v>83</v>
       </c>
       <c r="AW50" s="6" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="AX50" s="6" t="s">
         <v>117</v>
@@ -10308,412 +10299,106 @@
         <v>65</v>
       </c>
       <c r="BC50" s="6" t="s">
-        <v>119</v>
+        <v>356</v>
       </c>
       <c r="BD50" s="10">
         <v>0</v>
       </c>
       <c r="BE50" s="10">
-        <v>1</v>
+        <v>50900</v>
       </c>
       <c r="BF50" s="10">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="BG50" s="10">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="BH50" s="6" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="BI50" s="6" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="BJ50" s="6" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
-      <c r="A51" s="7">
-        <v>2023</v>
-      </c>
-      <c r="B51" s="7">
-        <v>2022</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="D51" s="8">
-        <v>46057.51524019676</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="K51" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M51" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="N51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O51" s="7">
-        <v>329595</v>
-      </c>
-      <c r="P51" s="8">
-        <v>45934.125</v>
-      </c>
-      <c r="Q51" s="9">
-        <v>46160.375</v>
-      </c>
-      <c r="R51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S51" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="T51" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="U51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="V51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="W51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z51" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB51" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC51" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="AD51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE51" s="8">
-        <v>46160.5</v>
-      </c>
-      <c r="AF51" s="7">
-        <v>133455</v>
-      </c>
-      <c r="AG51" s="9">
-        <v>46168.63480324074</v>
-      </c>
-      <c r="AH51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI51" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ51" s="11">
-        <v>0.013359528487229</v>
-      </c>
-      <c r="AK51" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL51" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="AM51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP51" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="AQ51" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS51" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="AT51" s="7">
-        <v>1075</v>
-      </c>
-      <c r="AU51" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV51" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW51" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="AX51" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY51" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="BA51" s="8">
-        <v>46216.99998842592</v>
-      </c>
-      <c r="BB51" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="BC51" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD51" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE51" s="10">
-        <v>50900</v>
-      </c>
-      <c r="BF51" s="10">
-        <v>680</v>
-      </c>
-      <c r="BG51" s="10">
-        <v>680</v>
-      </c>
-      <c r="BH51" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="BI51" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="BJ51" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="52" ht="23" customHeight="1">
-      <c r="A52" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="H52" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="J52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="K52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="L52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="N52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="O52" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="P52" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q52" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="R52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="S52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="T52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="U52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="V52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="W52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="X52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z52" s="16">
-        <f>SUM(Z6:Z51)</f>
-      </c>
-      <c r="AA52" s="16">
-        <f>SUM(AA6:AA51)</f>
-      </c>
-      <c r="AB52" s="16">
-        <f>SUM(AB6:AB51)</f>
-      </c>
-      <c r="AC52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE52" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="AF52" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="AG52" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ52" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AL52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AM52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AQ52" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="AR52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AT52" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="AU52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AV52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AW52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AY52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="AZ52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="BA52" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="BB52" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BC52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="BD52" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE52" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="BF52" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="BG52" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="BH52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI52" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="BJ52" s="13" t="s">
-        <v>65</v>
-      </c>
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="12"/>
+      <c r="M51" s="12"/>
+      <c r="N51" s="12"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="14"/>
+      <c r="Q51" s="15"/>
+      <c r="R51" s="12"/>
+      <c r="S51" s="12"/>
+      <c r="T51" s="12"/>
+      <c r="U51" s="12"/>
+      <c r="V51" s="12"/>
+      <c r="W51" s="12"/>
+      <c r="X51" s="12"/>
+      <c r="Y51" s="12"/>
+      <c r="Z51" s="16">
+        <f>SUM(Z6:Z50)</f>
+      </c>
+      <c r="AA51" s="16">
+        <f>SUM(AA6:AA50)</f>
+      </c>
+      <c r="AB51" s="16">
+        <f>SUM(AB6:AB50)</f>
+      </c>
+      <c r="AC51" s="12"/>
+      <c r="AD51" s="12"/>
+      <c r="AE51" s="14"/>
+      <c r="AF51" s="13"/>
+      <c r="AG51" s="15"/>
+      <c r="AH51" s="12"/>
+      <c r="AI51" s="12"/>
+      <c r="AJ51" s="17"/>
+      <c r="AK51" s="12"/>
+      <c r="AL51" s="12"/>
+      <c r="AM51" s="12"/>
+      <c r="AN51" s="12"/>
+      <c r="AO51" s="12"/>
+      <c r="AP51" s="12"/>
+      <c r="AQ51" s="16"/>
+      <c r="AR51" s="12"/>
+      <c r="AS51" s="12"/>
+      <c r="AT51" s="13"/>
+      <c r="AU51" s="12"/>
+      <c r="AV51" s="12"/>
+      <c r="AW51" s="12"/>
+      <c r="AX51" s="12"/>
+      <c r="AY51" s="12"/>
+      <c r="AZ51" s="12"/>
+      <c r="BA51" s="14"/>
+      <c r="BB51" s="15"/>
+      <c r="BC51" s="12"/>
+      <c r="BD51" s="16"/>
+      <c r="BE51" s="16"/>
+      <c r="BF51" s="16"/>
+      <c r="BG51" s="16"/>
+      <c r="BH51" s="12"/>
+      <c r="BI51" s="12"/>
+      <c r="BJ51" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:BJ5"/>
   <mergeCells>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:BJ1"/>
+    <mergeCell ref="A2:BJ2"/>
+    <mergeCell ref="A3:BJ3"/>
   </mergeCells>
   <pageMargins left="0.7087" right="0.7087" top="0.7480" bottom="0.7480" header="0.315" footer="0.20"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/planilhas/Contratos de Locação.xlsx
+++ b/planilhas/Contratos de Locação.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$BJ$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$BJ$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$BJ$50</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="462">
   <si>
     <t>Contratos de Locação</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sábado, 6 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em segunda-feira, 15 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Ano Modelo</t>
@@ -232,505 +232,532 @@
     <t/>
   </si>
   <si>
+    <t>9C2KC2500RR115224</t>
+  </si>
+  <si>
+    <t>SEGCOMP</t>
+  </si>
+  <si>
+    <t>JOEL LOPES</t>
+  </si>
+  <si>
+    <t>CTO-1038</t>
+  </si>
+  <si>
+    <t>NOVO CONTRATO</t>
+  </si>
+  <si>
+    <t>LOC-1038-3/24</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>41.153.812/0001-54</t>
+  </si>
+  <si>
+    <t>BPOFINANCEIRO@GRUPOECOMP.COM.BR</t>
+  </si>
+  <si>
+    <t>2.000 KM</t>
+  </si>
+  <si>
+    <t>MOTO</t>
+  </si>
+  <si>
+    <t>R$ 0,00</t>
+  </si>
+  <si>
+    <t>EM UTILIZAÇÃO</t>
+  </si>
+  <si>
+    <t>CG 160 START</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>1412406037</t>
+  </si>
+  <si>
+    <t>EM ANDAMENTO</t>
+  </si>
+  <si>
+    <t>FATURAR</t>
+  </si>
+  <si>
+    <t>(84) 30133030</t>
+  </si>
+  <si>
+    <t>PESSOA JURÍDICA</t>
+  </si>
+  <si>
+    <t>TERCEIRIZAÇÃO DE FROTA</t>
+  </si>
+  <si>
+    <t>ATIVUZ VEÍCULOS</t>
+  </si>
+  <si>
+    <t>RQI-7A69</t>
+  </si>
+  <si>
+    <t>PRINCIPAL</t>
+  </si>
+  <si>
+    <t>9C2KC2500RR115213</t>
+  </si>
+  <si>
+    <t>LOC-1038-4/24</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1412409583</t>
+  </si>
+  <si>
+    <t>RQI-7A89</t>
+  </si>
+  <si>
+    <t>9C2KD0810RR165173</t>
+  </si>
+  <si>
+    <t>LOC-1038-2/24</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>NXR 160 BROS ESDD FLEXONE</t>
+  </si>
+  <si>
+    <t>1413837562</t>
+  </si>
+  <si>
+    <t>RQJ-7H29</t>
+  </si>
+  <si>
     <t>9BWAG45U9PT049067</t>
   </si>
   <si>
-    <t>SEGCOMP</t>
-  </si>
-  <si>
-    <t>JOEL LOPES</t>
-  </si>
-  <si>
-    <t>CTO-1038</t>
-  </si>
-  <si>
-    <t>NOVO CONTRATO</t>
-  </si>
-  <si>
     <t>LOC-1038-1/24</t>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>41.153.812/0001-54</t>
-  </si>
-  <si>
-    <t>BPOFINANCEIRO@GRUPOECOMP.COM.BR</t>
-  </si>
-  <si>
-    <t>2.000 KM</t>
+    <t>46</t>
   </si>
   <si>
     <t>HATCH</t>
   </si>
   <si>
-    <t>R$ 0,00</t>
-  </si>
-  <si>
-    <t>EM UTILIZAÇÃO</t>
-  </si>
-  <si>
     <t>GOL 1.0 FLEX 12V 5P</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>1317566103</t>
   </si>
   <si>
-    <t>EM ANDAMENTO</t>
-  </si>
-  <si>
-    <t>FATURAR</t>
-  </si>
-  <si>
-    <t>(84) 30133030</t>
-  </si>
-  <si>
-    <t>PESSOA JURÍDICA</t>
-  </si>
-  <si>
-    <t>TERCEIRIZAÇÃO DE FROTA</t>
-  </si>
-  <si>
-    <t>ATIVUZ VEÍCULOS</t>
-  </si>
-  <si>
     <t>EGX-2E31</t>
   </si>
   <si>
-    <t>PRINCIPAL</t>
-  </si>
-  <si>
-    <t>9C2KD0810RR165173</t>
-  </si>
-  <si>
-    <t>LOC-1038-2/24</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>MOTO</t>
-  </si>
-  <si>
-    <t>NXR 160 BROS ESDD FLEXONE</t>
-  </si>
-  <si>
-    <t>1413837562</t>
-  </si>
-  <si>
-    <t>RQJ-7H29</t>
-  </si>
-  <si>
-    <t>9C2KC2500RR115224</t>
-  </si>
-  <si>
-    <t>LOC-1038-3/24</t>
+    <t>122.136.017-55</t>
+  </si>
+  <si>
+    <t>9BWAG45U9MT107528</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>CTO-1032</t>
+  </si>
+  <si>
+    <t>LOC-1032-1/1</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1253794178</t>
+  </si>
+  <si>
+    <t>84 99837-3901</t>
+  </si>
+  <si>
+    <t>PESSOA FÍSICA</t>
+  </si>
+  <si>
+    <t>MOTORISTA DE APLICATIVO</t>
+  </si>
+  <si>
+    <t>RGE-7H03</t>
+  </si>
+  <si>
+    <t>480.697.874-49</t>
+  </si>
+  <si>
+    <t>9BWDB45U5KT135660</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>CTO-1022</t>
+  </si>
+  <si>
+    <t>LOC-1022-1/4</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>SEDAN</t>
+  </si>
+  <si>
+    <t>VOYAGE 1.6 MSI FLEX 8V 4P</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1189763750</t>
+  </si>
+  <si>
+    <t>(84) 996369127</t>
+  </si>
+  <si>
+    <t>QGU-1H54</t>
+  </si>
+  <si>
+    <t>117.936.764-29</t>
+  </si>
+  <si>
+    <t>9BWDG45U7PT091086</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>CTO-1016</t>
+  </si>
+  <si>
+    <t>LOC-1016-1/5</t>
+  </si>
+  <si>
+    <t>VOYAGE 1.0 FLEX 12V 4P</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1329648010</t>
+  </si>
+  <si>
+    <t>84 98890-2831</t>
+  </si>
+  <si>
+    <t>ECZ-8C02</t>
+  </si>
+  <si>
+    <t>069.054.054-00</t>
+  </si>
+  <si>
+    <t>9BWDG45U8NT005796</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>CTO-1024</t>
+  </si>
+  <si>
+    <t>LOC-1024-1/7</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1253652063</t>
+  </si>
+  <si>
+    <t>(84) 981911956</t>
+  </si>
+  <si>
+    <t>RMK-2H75</t>
+  </si>
+  <si>
+    <t>071.198.454-97</t>
+  </si>
+  <si>
+    <t>9BWDB45U9KT124595</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>CTO-1015</t>
+  </si>
+  <si>
+    <t>LOC-1015-1/2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1190075218</t>
+  </si>
+  <si>
+    <t>(84) 981397610</t>
+  </si>
+  <si>
+    <t>QSE-8E63</t>
+  </si>
+  <si>
+    <t>101.093.374-41</t>
+  </si>
+  <si>
+    <t>9BWDG45U3PT091098</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>CTO-1011</t>
+  </si>
+  <si>
+    <t>LOC-1011-1/9</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1329647642</t>
+  </si>
+  <si>
+    <t>(84) 987180189</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>END-0I15</t>
+  </si>
+  <si>
+    <t>120.205.544-37</t>
+  </si>
+  <si>
+    <t>9BWAG45UXJT141960</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>CTO-1028</t>
+  </si>
+  <si>
+    <t>LOC-1028-1/8</t>
+  </si>
+  <si>
+    <t>GOL TRENDLINE 1.0 T.FLEX 12V 5P</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1149589393</t>
+  </si>
+  <si>
+    <t>84 99616-2852</t>
+  </si>
+  <si>
+    <t>QGX-7353</t>
+  </si>
+  <si>
+    <t>009.554.944-78</t>
+  </si>
+  <si>
+    <t>9BWDG45U1PT010258</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>CTO-1023</t>
+  </si>
+  <si>
+    <t>LOC-1023-1/13</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>01298307187</t>
+  </si>
+  <si>
+    <t>84 99212-8471</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>GIY-6G96</t>
+  </si>
+  <si>
+    <t>705.762.454-96</t>
+  </si>
+  <si>
+    <t>9BWDG45UXPT092720</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>CTO-1029</t>
+  </si>
+  <si>
+    <t>LOC-1029-1/2</t>
+  </si>
+  <si>
+    <t>1329889310</t>
+  </si>
+  <si>
+    <t>(84) 921697458</t>
+  </si>
+  <si>
+    <t>EXF-1F14</t>
+  </si>
+  <si>
+    <t>790.887.914-49</t>
+  </si>
+  <si>
+    <t>9BWDG45U1PT092539</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>CTO-1018</t>
+  </si>
+  <si>
+    <t>LOC-1018-1/2</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>01329662196</t>
+  </si>
+  <si>
+    <t>(84) 81731538</t>
+  </si>
+  <si>
+    <t>EMQ-6C26</t>
+  </si>
+  <si>
+    <t>017.712.914-00</t>
+  </si>
+  <si>
+    <t>9BWAG45U2KT043944</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>CTO-1019</t>
+  </si>
+  <si>
+    <t>LOC-1019-1/3</t>
+  </si>
+  <si>
+    <t>1164746763</t>
+  </si>
+  <si>
+    <t>(84) 921520363</t>
+  </si>
+  <si>
+    <t>QGN-9356</t>
+  </si>
+  <si>
+    <t>415.033.332-72</t>
+  </si>
+  <si>
+    <t>9BWAG45U8MT050030</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>CTO-1017</t>
+  </si>
+  <si>
+    <t>LOC-1017-1/2</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>1239198733</t>
+  </si>
+  <si>
+    <t>84 99639-9401</t>
+  </si>
+  <si>
+    <t>RGE-3I66</t>
+  </si>
+  <si>
+    <t>700.139.284-73</t>
+  </si>
+  <si>
+    <t>9BWAG45UXMT107456</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>CTO-1010</t>
+  </si>
+  <si>
+    <t>LOC-1010-1/9</t>
+  </si>
+  <si>
+    <t>1253118830</t>
+  </si>
+  <si>
+    <t>(84) 996939545</t>
+  </si>
+  <si>
+    <t>RGE-5D51</t>
+  </si>
+  <si>
+    <t>092.354.354-63</t>
+  </si>
+  <si>
+    <t>9BWDB45U1LT065429</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>CTO-1004</t>
+  </si>
+  <si>
+    <t>LOC-1004-1/5</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>CG 160 START</t>
-  </si>
-  <si>
-    <t>1412406037</t>
-  </si>
-  <si>
-    <t>RQI-7A69</t>
-  </si>
-  <si>
-    <t>9C2KC2500RR115213</t>
-  </si>
-  <si>
-    <t>LOC-1038-4/24</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1412409583</t>
-  </si>
-  <si>
-    <t>RQI-7A89</t>
-  </si>
-  <si>
-    <t>122.136.017-55</t>
-  </si>
-  <si>
-    <t>9BWAG45U9MT107528</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>CTO-1032</t>
-  </si>
-  <si>
-    <t>LOC-1032-1/1</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1253794178</t>
-  </si>
-  <si>
-    <t>84 99837-3901</t>
-  </si>
-  <si>
-    <t>PESSOA FÍSICA</t>
-  </si>
-  <si>
-    <t>MOTORISTA DE APLICATIVO</t>
-  </si>
-  <si>
-    <t>RGE-7H03</t>
-  </si>
-  <si>
-    <t>480.697.874-49</t>
-  </si>
-  <si>
-    <t>9BWDB45U5KT135660</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>CTO-1022</t>
-  </si>
-  <si>
-    <t>LOC-1022-1/4</t>
-  </si>
-  <si>
-    <t>SEDAN</t>
-  </si>
-  <si>
-    <t>VOYAGE 1.6 MSI FLEX 8V 4P</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1189763750</t>
-  </si>
-  <si>
-    <t>(84) 996369127</t>
-  </si>
-  <si>
-    <t>QGU-1H54</t>
-  </si>
-  <si>
-    <t>790.887.914-49</t>
-  </si>
-  <si>
-    <t>9BWDG45U1PT092539</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>CTO-1018</t>
-  </si>
-  <si>
-    <t>LOC-1018-1/2</t>
-  </si>
-  <si>
-    <t>VOYAGE 1.0 FLEX 12V 4P</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>01329662196</t>
-  </si>
-  <si>
-    <t>(84) 81731538</t>
-  </si>
-  <si>
-    <t>EMQ-6C26</t>
-  </si>
-  <si>
-    <t>009.554.944-78</t>
-  </si>
-  <si>
-    <t>9BWDG45U1PT010258</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>CTO-1023</t>
-  </si>
-  <si>
-    <t>LOC-1023-1/13</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>01298307187</t>
-  </si>
-  <si>
-    <t>84 99212-8471</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>GIY-6G96</t>
-  </si>
-  <si>
-    <t>117.936.764-29</t>
-  </si>
-  <si>
-    <t>9BWDG45U7PT091086</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>CTO-1016</t>
-  </si>
-  <si>
-    <t>LOC-1016-1/5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>1329648010</t>
-  </si>
-  <si>
-    <t>84 98890-2831</t>
-  </si>
-  <si>
-    <t>ECZ-8C02</t>
-  </si>
-  <si>
-    <t>101.093.374-41</t>
-  </si>
-  <si>
-    <t>9BWDG45U3PT091098</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>CTO-1011</t>
-  </si>
-  <si>
-    <t>LOC-1011-1/9</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1329647642</t>
-  </si>
-  <si>
-    <t>(84) 987180189</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>END-0I15</t>
-  </si>
-  <si>
-    <t>705.762.454-96</t>
-  </si>
-  <si>
-    <t>9BWDG45UXPT092720</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>CTO-1029</t>
-  </si>
-  <si>
-    <t>LOC-1029-1/2</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1329889310</t>
-  </si>
-  <si>
-    <t>(84) 921697458</t>
-  </si>
-  <si>
-    <t>EXF-1F14</t>
-  </si>
-  <si>
-    <t>120.205.544-37</t>
-  </si>
-  <si>
-    <t>9BWAG45UXJT141960</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>CTO-1028</t>
-  </si>
-  <si>
-    <t>LOC-1028-1/8</t>
-  </si>
-  <si>
-    <t>GOL TRENDLINE 1.0 T.FLEX 12V 5P</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>1149589393</t>
-  </si>
-  <si>
-    <t>84 99616-2852</t>
-  </si>
-  <si>
-    <t>QGX-7353</t>
-  </si>
-  <si>
-    <t>069.054.054-00</t>
-  </si>
-  <si>
-    <t>9BWDG45U8NT005796</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>CTO-1024</t>
-  </si>
-  <si>
-    <t>LOC-1024-1/7</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>1253652063</t>
-  </si>
-  <si>
-    <t>(84) 981911956</t>
-  </si>
-  <si>
-    <t>RMK-2H75</t>
-  </si>
-  <si>
-    <t>071.198.454-97</t>
-  </si>
-  <si>
-    <t>9BWDB45U9KT124595</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>CTO-1015</t>
-  </si>
-  <si>
-    <t>LOC-1015-1/2</t>
-  </si>
-  <si>
-    <t>1190075218</t>
-  </si>
-  <si>
-    <t>(84) 981397610</t>
-  </si>
-  <si>
-    <t>QSE-8E63</t>
-  </si>
-  <si>
-    <t>017.712.914-00</t>
-  </si>
-  <si>
-    <t>9BWAG45U2KT043944</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>CTO-1019</t>
-  </si>
-  <si>
-    <t>LOC-1019-1/3</t>
-  </si>
-  <si>
-    <t>1164746763</t>
-  </si>
-  <si>
-    <t>(84) 921520363</t>
-  </si>
-  <si>
-    <t>QGN-9356</t>
-  </si>
-  <si>
-    <t>415.033.332-72</t>
-  </si>
-  <si>
-    <t>9BWAG45U8MT050030</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>CTO-1017</t>
-  </si>
-  <si>
-    <t>LOC-1017-1/2</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>1239198733</t>
-  </si>
-  <si>
-    <t>84 99639-9401</t>
-  </si>
-  <si>
-    <t>RGE-3I66</t>
-  </si>
-  <si>
-    <t>700.139.284-73</t>
-  </si>
-  <si>
-    <t>9BWAG45UXMT107456</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>CTO-1010</t>
-  </si>
-  <si>
-    <t>LOC-1010-1/9</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>1253118830</t>
-  </si>
-  <si>
-    <t>(84) 996939545</t>
-  </si>
-  <si>
-    <t>RGE-5D51</t>
+    <t>1206436686</t>
+  </si>
+  <si>
+    <t>84 92148-9407</t>
+  </si>
+  <si>
+    <t>QGS-6G16</t>
   </si>
   <si>
     <t>014.010.004-01</t>
@@ -751,9 +778,6 @@
     <t>EM MANUTENÇÃO</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>1253913371</t>
   </si>
   <si>
@@ -763,30 +787,6 @@
     <t>RGE-7G92</t>
   </si>
   <si>
-    <t>092.354.354-63</t>
-  </si>
-  <si>
-    <t>9BWDB45U1LT065429</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t>CTO-1004</t>
-  </si>
-  <si>
-    <t>LOC-1004-1/5</t>
-  </si>
-  <si>
-    <t>1206436686</t>
-  </si>
-  <si>
-    <t>84 92148-9407</t>
-  </si>
-  <si>
-    <t>QGS-6G16</t>
-  </si>
-  <si>
     <t>100.144.684-41</t>
   </si>
   <si>
@@ -829,7 +829,7 @@
     <t>LOC-1043-1/12</t>
   </si>
   <si>
-    <t>43</t>
+    <t>52</t>
   </si>
   <si>
     <t>1319762945</t>
@@ -856,7 +856,7 @@
     <t>LOC-1047-1/12</t>
   </si>
   <si>
-    <t>23</t>
+    <t>32</t>
   </si>
   <si>
     <t>1327877853</t>
@@ -931,7 +931,7 @@
     <t>LOC-1052-1/3</t>
   </si>
   <si>
-    <t>138</t>
+    <t>147</t>
   </si>
   <si>
     <t>6</t>
@@ -961,7 +961,7 @@
     <t>LOC-1056-1/12</t>
   </si>
   <si>
-    <t>53</t>
+    <t>62</t>
   </si>
   <si>
     <t>1318410840</t>
@@ -985,7 +985,7 @@
     <t>LOC-1060-1/12</t>
   </si>
   <si>
-    <t>67</t>
+    <t>76</t>
   </si>
   <si>
     <t>23.802.049/0001-63</t>
@@ -1015,7 +1015,7 @@
     <t>LOC-1063-1/12</t>
   </si>
   <si>
-    <t>68</t>
+    <t>77</t>
   </si>
   <si>
     <t>01327467981</t>
@@ -1069,7 +1069,7 @@
     <t>LOC-1067-1/12</t>
   </si>
   <si>
-    <t>80</t>
+    <t>89</t>
   </si>
   <si>
     <t>POLO TRACK 1.0 FLEX 12V 5P</t>
@@ -1096,204 +1096,183 @@
     <t>LOC-1068-1/12</t>
   </si>
   <si>
-    <t>22</t>
+    <t>31</t>
   </si>
   <si>
     <t>1325953650</t>
   </si>
   <si>
+    <t>ECM-1C93</t>
+  </si>
+  <si>
+    <t>704.631.134-03</t>
+  </si>
+  <si>
+    <t>9BWDB45U7LT066973</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>CTO-1070</t>
+  </si>
+  <si>
+    <t>LOC-1070-1/12</t>
+  </si>
+  <si>
+    <t>1207486415</t>
+  </si>
+  <si>
+    <t>QGT-1D67</t>
+  </si>
+  <si>
+    <t>9BWAG45U4MT005800</t>
+  </si>
+  <si>
+    <t>NEW CHARGER</t>
+  </si>
+  <si>
+    <t>CTO-1073</t>
+  </si>
+  <si>
+    <t>LOC-1073-1/2</t>
+  </si>
+  <si>
+    <t>46.346.152/0001-41</t>
+  </si>
+  <si>
+    <t>1225842635</t>
+  </si>
+  <si>
+    <t>QGT-9D86</t>
+  </si>
+  <si>
+    <t>009.896.264-74</t>
+  </si>
+  <si>
+    <t>9BWAG45U4MT107453</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>CTO-1071</t>
+  </si>
+  <si>
+    <t>LOC-1071-1/12</t>
+  </si>
+  <si>
+    <t>1253794054</t>
+  </si>
+  <si>
+    <t>RGE-7H02</t>
+  </si>
+  <si>
+    <t>059.640.564-23</t>
+  </si>
+  <si>
+    <t>92VCE4CC9VK025626</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>CTO-1075</t>
+  </si>
+  <si>
+    <t>LOC-1075-1/12</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>DOLPHIN MINI (ELÉTRICO)</t>
+  </si>
+  <si>
+    <t>01489393657</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>TSW-3H63</t>
+  </si>
+  <si>
+    <t>097.034.444-90</t>
+  </si>
+  <si>
+    <t>9BWAG45U5LT080519</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>CTO-1077</t>
+  </si>
+  <si>
+    <t>LOC-1077-1/4</t>
+  </si>
+  <si>
+    <t>1214268843</t>
+  </si>
+  <si>
+    <t>(84) 981787788</t>
+  </si>
+  <si>
+    <t>QGW-2B89</t>
+  </si>
+  <si>
+    <t>105.001.424-32</t>
+  </si>
+  <si>
+    <t>9BWAB45U2JT067951</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>CTO-1078</t>
+  </si>
+  <si>
+    <t>LOC-1078-1/12</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>GOL (NOVO) 1.6 MI TOTAL FLEX 8V 4P</t>
+  </si>
+  <si>
+    <t>01136312835</t>
+  </si>
+  <si>
+    <t>QGO-2H58</t>
+  </si>
+  <si>
+    <t>077.732.684-10</t>
+  </si>
+  <si>
+    <t>9BWDG45U9PT071678</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>CTO-1082</t>
+  </si>
+  <si>
+    <t>LOC-1082-1/8</t>
+  </si>
+  <si>
+    <t>01323779938</t>
+  </si>
+  <si>
+    <t>(84) 981675906</t>
+  </si>
+  <si>
     <t>CONFORME UNIDADE DO VEÍCULO</t>
   </si>
   <si>
-    <t>ECM-1C93</t>
-  </si>
-  <si>
-    <t>704.631.134-03</t>
-  </si>
-  <si>
-    <t>9BWDB45U7LT066973</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>CTO-1070</t>
-  </si>
-  <si>
-    <t>LOC-1070-1/12</t>
-  </si>
-  <si>
-    <t>1207486415</t>
-  </si>
-  <si>
-    <t>QGT-1D67</t>
-  </si>
-  <si>
-    <t>9BWAG45U4MT005800</t>
-  </si>
-  <si>
-    <t>NEW CHARGER</t>
-  </si>
-  <si>
-    <t>CTO-1073</t>
-  </si>
-  <si>
-    <t>LOC-1073-1/2</t>
-  </si>
-  <si>
-    <t>46.346.152/0001-41</t>
-  </si>
-  <si>
-    <t>1225842635</t>
-  </si>
-  <si>
-    <t>QGT-9D86</t>
-  </si>
-  <si>
-    <t>009.896.264-74</t>
-  </si>
-  <si>
-    <t>9BWAG45U4MT107453</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>CTO-1071</t>
-  </si>
-  <si>
-    <t>LOC-1071-1/12</t>
-  </si>
-  <si>
-    <t>1253794054</t>
-  </si>
-  <si>
-    <t>RGE-7H02</t>
-  </si>
-  <si>
-    <t>059.640.564-23</t>
-  </si>
-  <si>
-    <t>92VCE4CC9VK025626</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>CTO-1075</t>
-  </si>
-  <si>
-    <t>LOC-1075-1/12</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>DOLPHIN MINI (ELÉTRICO)</t>
-  </si>
-  <si>
-    <t>01489393657</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>TSW-3H63</t>
-  </si>
-  <si>
-    <t>097.034.444-90</t>
-  </si>
-  <si>
-    <t>9BWAG45U5LT080519</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>CTO-1077</t>
-  </si>
-  <si>
-    <t>LOC-1077-1/4</t>
-  </si>
-  <si>
-    <t>1214268843</t>
-  </si>
-  <si>
-    <t>(84) 981787788</t>
-  </si>
-  <si>
-    <t>QGW-2B89</t>
-  </si>
-  <si>
-    <t>031.396.964-77</t>
-  </si>
-  <si>
-    <t>92VCE4CC1VK025636</t>
-  </si>
-  <si>
-    <t>ADRIANO TEOTONIO DA SILVA</t>
-  </si>
-  <si>
-    <t>CTO-1074</t>
-  </si>
-  <si>
-    <t>LOC-1074-1/12</t>
-  </si>
-  <si>
-    <t>01489400122</t>
-  </si>
-  <si>
-    <t>TSW-3I03</t>
-  </si>
-  <si>
-    <t>105.001.424-32</t>
-  </si>
-  <si>
-    <t>9BWAB45U2JT067951</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>CTO-1078</t>
-  </si>
-  <si>
-    <t>LOC-1078-1/12</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>GOL (NOVO) 1.6 MI TOTAL FLEX 8V 4P</t>
-  </si>
-  <si>
-    <t>01136312835</t>
-  </si>
-  <si>
-    <t>QGO-2H58</t>
-  </si>
-  <si>
-    <t>077.732.684-10</t>
-  </si>
-  <si>
-    <t>9BWDG45U9PT071678</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>CTO-1082</t>
-  </si>
-  <si>
-    <t>LOC-1082-1/8</t>
-  </si>
-  <si>
-    <t>01323779938</t>
-  </si>
-  <si>
-    <t>(84) 981675906</t>
-  </si>
-  <si>
     <t>ELY-4D83</t>
   </si>
   <si>
@@ -1333,7 +1312,7 @@
     <t>LOC-1079-1/12</t>
   </si>
   <si>
-    <t>19</t>
+    <t>28</t>
   </si>
   <si>
     <t>01489397822</t>
@@ -1427,6 +1406,9 @@
   </si>
   <si>
     <t>LOC-1084-1/8</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
   <si>
     <t>1327460677</t>
@@ -1591,7 +1573,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:BJ51"/>
+  <dimension ref="A1:BJ50"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1" style="1"/>
@@ -1865,10 +1847,10 @@
     </row>
     <row r="6">
       <c r="A6" s="7">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B6" s="7">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>65</v>
@@ -1940,13 +1922,13 @@
         <v>75</v>
       </c>
       <c r="Z6" s="10">
-        <v>260.55</v>
+        <v>65.58</v>
       </c>
       <c r="AA6" s="10">
         <v>0</v>
       </c>
       <c r="AB6" s="10">
-        <v>260.55</v>
+        <v>65.58</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>76</v>
@@ -1958,10 +1940,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF6" s="7">
-        <v>83783</v>
+        <v>18588</v>
       </c>
       <c r="AG6" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH6" s="6" t="s">
         <v>77</v>
@@ -1970,7 +1952,7 @@
         <v>78</v>
       </c>
       <c r="AJ6" s="11">
-        <v>0.04059829059829</v>
+        <v>0.042943797305276</v>
       </c>
       <c r="AK6" s="6" t="s">
         <v>79</v>
@@ -2000,7 +1982,7 @@
         <v>81</v>
       </c>
       <c r="AT6" s="7">
-        <v>4268</v>
+        <v>932</v>
       </c>
       <c r="AU6" s="6" t="s">
         <v>82</v>
@@ -2033,13 +2015,13 @@
         <v>0</v>
       </c>
       <c r="BE6" s="10">
-        <v>46800</v>
+        <v>18629</v>
       </c>
       <c r="BF6" s="10">
-        <v>1900</v>
+        <v>800</v>
       </c>
       <c r="BG6" s="10">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="BH6" s="6" t="s">
         <v>88</v>
@@ -2128,16 +2110,16 @@
         <v>75</v>
       </c>
       <c r="Z7" s="10">
-        <v>32.79</v>
+        <v>98.37</v>
       </c>
       <c r="AA7" s="10">
         <v>0</v>
       </c>
       <c r="AB7" s="10">
-        <v>32.79</v>
+        <v>98.37</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AD7" s="6" t="s">
         <v>65</v>
@@ -2146,10 +2128,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF7" s="7">
-        <v>30242</v>
+        <v>15448</v>
       </c>
       <c r="AG7" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH7" s="6" t="s">
         <v>77</v>
@@ -2158,10 +2140,10 @@
         <v>78</v>
       </c>
       <c r="AJ7" s="11">
-        <v>0.113938473224458</v>
+        <v>0.042943797305276</v>
       </c>
       <c r="AK7" s="6" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="AL7" s="6" t="s">
         <v>65</v>
@@ -2185,10 +2167,10 @@
         <v>65</v>
       </c>
       <c r="AS7" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AT7" s="7">
-        <v>1540</v>
+        <v>775</v>
       </c>
       <c r="AU7" s="6" t="s">
         <v>82</v>
@@ -2221,19 +2203,19 @@
         <v>0</v>
       </c>
       <c r="BE7" s="10">
-        <v>7899</v>
+        <v>18629</v>
       </c>
       <c r="BF7" s="10">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="BG7" s="10">
-        <v>900</v>
+        <v>1600</v>
       </c>
       <c r="BH7" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="BI7" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="BJ7" s="6" t="s">
         <v>89</v>
@@ -2253,7 +2235,7 @@
         <v>65</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>65</v>
@@ -2277,7 +2259,7 @@
         <v>70</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>65</v>
@@ -2295,7 +2277,7 @@
         <v>65</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="T8" s="6" t="s">
         <v>73</v>
@@ -2316,16 +2298,16 @@
         <v>75</v>
       </c>
       <c r="Z8" s="10">
-        <v>65.58</v>
+        <v>32.79</v>
       </c>
       <c r="AA8" s="10">
         <v>0</v>
       </c>
       <c r="AB8" s="10">
-        <v>65.58</v>
+        <v>32.79</v>
       </c>
       <c r="AC8" s="6" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AD8" s="6" t="s">
         <v>65</v>
@@ -2334,10 +2316,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF8" s="7">
-        <v>18462</v>
+        <v>30542</v>
       </c>
       <c r="AG8" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH8" s="6" t="s">
         <v>77</v>
@@ -2346,10 +2328,10 @@
         <v>78</v>
       </c>
       <c r="AJ8" s="11">
-        <v>0.042943797305276</v>
+        <v>0.113938473224458</v>
       </c>
       <c r="AK8" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AL8" s="6" t="s">
         <v>65</v>
@@ -2373,10 +2355,10 @@
         <v>65</v>
       </c>
       <c r="AS8" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AT8" s="7">
-        <v>940</v>
+        <v>1532</v>
       </c>
       <c r="AU8" s="6" t="s">
         <v>82</v>
@@ -2409,19 +2391,19 @@
         <v>0</v>
       </c>
       <c r="BE8" s="10">
-        <v>18629</v>
+        <v>7899</v>
       </c>
       <c r="BF8" s="10">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="BG8" s="10">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="BH8" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="BI8" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="BJ8" s="6" t="s">
         <v>89</v>
@@ -2429,10 +2411,10 @@
     </row>
     <row r="9">
       <c r="A9" s="7">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B9" s="7">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>65</v>
@@ -2441,7 +2423,7 @@
         <v>65</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>65</v>
@@ -2465,7 +2447,7 @@
         <v>70</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>65</v>
@@ -2483,7 +2465,7 @@
         <v>65</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>73</v>
@@ -2504,16 +2486,16 @@
         <v>75</v>
       </c>
       <c r="Z9" s="10">
-        <v>98.37</v>
+        <v>260.55</v>
       </c>
       <c r="AA9" s="10">
         <v>0</v>
       </c>
       <c r="AB9" s="10">
-        <v>98.37</v>
+        <v>260.55</v>
       </c>
       <c r="AC9" s="6" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="AD9" s="6" t="s">
         <v>65</v>
@@ -2522,10 +2504,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF9" s="7">
-        <v>15278</v>
+        <v>84171</v>
       </c>
       <c r="AG9" s="9">
-        <v>46176.41266203704</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH9" s="6" t="s">
         <v>77</v>
@@ -2534,10 +2516,10 @@
         <v>78</v>
       </c>
       <c r="AJ9" s="11">
-        <v>0.042943797305276</v>
+        <v>0.04059829059829</v>
       </c>
       <c r="AK9" s="6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AL9" s="6" t="s">
         <v>65</v>
@@ -2564,7 +2546,7 @@
         <v>106</v>
       </c>
       <c r="AT9" s="7">
-        <v>778</v>
+        <v>4223</v>
       </c>
       <c r="AU9" s="6" t="s">
         <v>82</v>
@@ -2597,13 +2579,13 @@
         <v>0</v>
       </c>
       <c r="BE9" s="10">
-        <v>18629</v>
+        <v>46800</v>
       </c>
       <c r="BF9" s="10">
-        <v>800</v>
+        <v>1900</v>
       </c>
       <c r="BG9" s="10">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="BH9" s="6" t="s">
         <v>107</v>
@@ -2701,7 +2683,7 @@
         <v>284.37</v>
       </c>
       <c r="AC10" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD10" s="6" t="s">
         <v>65</v>
@@ -2710,10 +2692,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF10" s="7">
-        <v>176690</v>
+        <v>177302</v>
       </c>
       <c r="AG10" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH10" s="6" t="s">
         <v>65</v>
@@ -2725,7 +2707,7 @@
         <v>0.014939759036144</v>
       </c>
       <c r="AK10" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL10" s="6" t="s">
         <v>110</v>
@@ -2752,7 +2734,7 @@
         <v>115</v>
       </c>
       <c r="AT10" s="7">
-        <v>2655</v>
+        <v>2638</v>
       </c>
       <c r="AU10" s="6" t="s">
         <v>82</v>
@@ -2859,7 +2841,7 @@
         <v>65</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>120</v>
@@ -2880,16 +2862,16 @@
         <v>65</v>
       </c>
       <c r="Z11" s="10">
-        <v>1190.42</v>
+        <v>1914.17</v>
       </c>
       <c r="AA11" s="10">
         <v>0</v>
       </c>
       <c r="AB11" s="10">
-        <v>1190.42</v>
+        <v>1914.17</v>
       </c>
       <c r="AC11" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD11" s="6" t="s">
         <v>65</v>
@@ -2898,10 +2880,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF11" s="7">
-        <v>273298</v>
+        <v>274560</v>
       </c>
       <c r="AG11" s="9">
-        <v>46175.357523148145</v>
+        <v>46185.42972222222</v>
       </c>
       <c r="AH11" s="6" t="s">
         <v>65</v>
@@ -2913,7 +2895,7 @@
         <v>0.014823529411764</v>
       </c>
       <c r="AK11" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL11" s="6" t="s">
         <v>122</v>
@@ -2928,7 +2910,7 @@
         <v>65</v>
       </c>
       <c r="AP11" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ11" s="10">
         <v>0</v>
@@ -2937,10 +2919,10 @@
         <v>65</v>
       </c>
       <c r="AS11" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AT11" s="7">
-        <v>18390</v>
+        <v>17985</v>
       </c>
       <c r="AU11" s="6" t="s">
         <v>82</v>
@@ -2949,7 +2931,7 @@
         <v>83</v>
       </c>
       <c r="AW11" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AX11" s="6" t="s">
         <v>117</v>
@@ -2982,10 +2964,10 @@
         <v>630</v>
       </c>
       <c r="BH11" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BI11" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BJ11" s="6" t="s">
         <v>89</v>
@@ -2999,19 +2981,19 @@
         <v>2022</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>65</v>
@@ -3020,7 +3002,7 @@
         <v>68</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>68</v>
@@ -3029,28 +3011,28 @@
         <v>65</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O12" s="7">
-        <v>258527</v>
-      </c>
-      <c r="P12" s="8" t="s">
-        <v>65</v>
+        <v>258533</v>
+      </c>
+      <c r="P12" s="8">
+        <v>36526</v>
       </c>
       <c r="Q12" s="9">
-        <v>46091.541666666664</v>
+        <v>45873.333333333336</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U12" s="6" t="s">
         <v>65</v>
@@ -3068,16 +3050,16 @@
         <v>65</v>
       </c>
       <c r="Z12" s="10">
-        <v>694.95</v>
+        <v>2022.84</v>
       </c>
       <c r="AA12" s="10">
         <v>0</v>
       </c>
       <c r="AB12" s="10">
-        <v>766.78</v>
+        <v>2155.84</v>
       </c>
       <c r="AC12" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD12" s="6" t="s">
         <v>65</v>
@@ -3086,10 +3068,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF12" s="7">
-        <v>88758</v>
+        <v>149570</v>
       </c>
       <c r="AG12" s="9">
-        <v>46175.3575</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH12" s="6" t="s">
         <v>65</v>
@@ -3098,13 +3080,13 @@
         <v>78</v>
       </c>
       <c r="AJ12" s="11">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="AK12" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL12" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AM12" s="6" t="s">
         <v>65</v>
@@ -3116,19 +3098,19 @@
         <v>65</v>
       </c>
       <c r="AP12" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="AQ12" s="10">
-        <v>0</v>
+        <v>138</v>
+      </c>
+      <c r="AQ12" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR12" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS12" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AT12" s="7">
-        <v>16640</v>
+        <v>7091</v>
       </c>
       <c r="AU12" s="6" t="s">
         <v>82</v>
@@ -3137,7 +3119,7 @@
         <v>83</v>
       </c>
       <c r="AW12" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AX12" s="6" t="s">
         <v>117</v>
@@ -3149,7 +3131,7 @@
         <v>65</v>
       </c>
       <c r="BA12" s="8">
-        <v>46223.458333333336</v>
+        <v>46195.458333333336</v>
       </c>
       <c r="BB12" s="9" t="s">
         <v>65</v>
@@ -3157,23 +3139,23 @@
       <c r="BC12" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="BD12" s="10">
-        <v>0</v>
+      <c r="BD12" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BE12" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF12" s="10">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="BG12" s="10">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="BH12" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BI12" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BJ12" s="6" t="s">
         <v>89</v>
@@ -3181,25 +3163,25 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B13" s="7">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>65</v>
@@ -3208,7 +3190,7 @@
         <v>68</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>68</v>
@@ -3217,28 +3199,28 @@
         <v>65</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N13" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O13" s="7">
-        <v>258547</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>65</v>
+        <v>258539</v>
+      </c>
+      <c r="P13" s="8">
+        <v>45475.125</v>
       </c>
       <c r="Q13" s="9">
-        <v>46098.375</v>
+        <v>45873.333333333336</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="U13" s="6" t="s">
         <v>65</v>
@@ -3256,16 +3238,16 @@
         <v>65</v>
       </c>
       <c r="Z13" s="10">
-        <v>390.72</v>
+        <v>1039.98</v>
       </c>
       <c r="AA13" s="10">
         <v>0</v>
       </c>
       <c r="AB13" s="10">
-        <v>390.72</v>
+        <v>1039.98</v>
       </c>
       <c r="AC13" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD13" s="6" t="s">
         <v>65</v>
@@ -3274,10 +3256,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF13" s="7">
-        <v>101633</v>
+        <v>188159</v>
       </c>
       <c r="AG13" s="9">
-        <v>46175.357511574075</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH13" s="6" t="s">
         <v>65</v>
@@ -3286,13 +3268,13 @@
         <v>78</v>
       </c>
       <c r="AJ13" s="11">
-        <v>0</v>
+        <v>0.013846153846153</v>
       </c>
       <c r="AK13" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL13" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AM13" s="6" t="s">
         <v>65</v>
@@ -3304,19 +3286,19 @@
         <v>65</v>
       </c>
       <c r="AP13" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="AQ13" s="10" t="s">
-        <v>65</v>
+        <v>148</v>
+      </c>
+      <c r="AQ13" s="10">
+        <v>0</v>
       </c>
       <c r="AR13" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS13" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AT13" s="7">
-        <v>22826</v>
+        <v>10904</v>
       </c>
       <c r="AU13" s="6" t="s">
         <v>82</v>
@@ -3325,7 +3307,7 @@
         <v>83</v>
       </c>
       <c r="AW13" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AX13" s="6" t="s">
         <v>117</v>
@@ -3337,25 +3319,25 @@
         <v>65</v>
       </c>
       <c r="BA13" s="8">
-        <v>46202.99998842592</v>
+        <v>46223.99998842592</v>
       </c>
       <c r="BB13" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC13" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD13" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE13" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD13" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE13" s="10">
+        <v>45500</v>
       </c>
       <c r="BF13" s="10">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="BG13" s="10">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="BH13" s="6" t="s">
         <v>151</v>
@@ -3369,10 +3351,10 @@
     </row>
     <row r="14">
       <c r="A14" s="7">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="B14" s="7">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>152</v>
@@ -3411,10 +3393,10 @@
         <v>65</v>
       </c>
       <c r="O14" s="7">
-        <v>258533</v>
+        <v>258526</v>
       </c>
       <c r="P14" s="8">
-        <v>36526</v>
+        <v>45351</v>
       </c>
       <c r="Q14" s="9">
         <v>45873.333333333336</v>
@@ -3423,7 +3405,7 @@
         <v>65</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="T14" s="6" t="s">
         <v>152</v>
@@ -3444,16 +3426,16 @@
         <v>65</v>
       </c>
       <c r="Z14" s="10">
-        <v>2022.84</v>
+        <v>2430.95</v>
       </c>
       <c r="AA14" s="10">
         <v>0</v>
       </c>
       <c r="AB14" s="10">
-        <v>2155.84</v>
+        <v>2430.95</v>
       </c>
       <c r="AC14" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD14" s="6" t="s">
         <v>65</v>
@@ -3462,10 +3444,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF14" s="7">
-        <v>148702</v>
+        <v>240681</v>
       </c>
       <c r="AG14" s="9">
-        <v>46175.35748842593</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH14" s="6" t="s">
         <v>65</v>
@@ -3474,10 +3456,10 @@
         <v>78</v>
       </c>
       <c r="AJ14" s="11">
-        <v>650</v>
+        <v>0.01575</v>
       </c>
       <c r="AK14" s="6" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="AL14" s="6" t="s">
         <v>154</v>
@@ -3504,7 +3486,7 @@
         <v>158</v>
       </c>
       <c r="AT14" s="7">
-        <v>7214</v>
+        <v>10308</v>
       </c>
       <c r="AU14" s="6" t="s">
         <v>82</v>
@@ -3525,7 +3507,7 @@
         <v>65</v>
       </c>
       <c r="BA14" s="8">
-        <v>46195.458333333336</v>
+        <v>46223.458333333336</v>
       </c>
       <c r="BB14" s="9" t="s">
         <v>65</v>
@@ -3537,13 +3519,13 @@
         <v>65</v>
       </c>
       <c r="BE14" s="10">
-        <v>1</v>
+        <v>40000</v>
       </c>
       <c r="BF14" s="10">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="BG14" s="10">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="BH14" s="6" t="s">
         <v>160</v>
@@ -3611,7 +3593,7 @@
         <v>65</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>161</v>
@@ -3641,7 +3623,7 @@
         <v>433.8</v>
       </c>
       <c r="AC15" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD15" s="6" t="s">
         <v>65</v>
@@ -3650,10 +3632,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF15" s="7">
-        <v>129783</v>
+        <v>131418</v>
       </c>
       <c r="AG15" s="9">
-        <v>46175.3575</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH15" s="6" t="s">
         <v>65</v>
@@ -3665,7 +3647,7 @@
         <v>0.014028056112224</v>
       </c>
       <c r="AK15" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL15" s="6" t="s">
         <v>163</v>
@@ -3692,7 +3674,7 @@
         <v>167</v>
       </c>
       <c r="AT15" s="7">
-        <v>-11572</v>
+        <v>-10083</v>
       </c>
       <c r="AU15" s="6" t="s">
         <v>82</v>
@@ -3745,10 +3727,10 @@
     </row>
     <row r="16">
       <c r="A16" s="7">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B16" s="7">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>171</v>
@@ -3787,10 +3769,10 @@
         <v>65</v>
       </c>
       <c r="O16" s="7">
-        <v>258528</v>
+        <v>258551</v>
       </c>
       <c r="P16" s="8">
-        <v>45729</v>
+        <v>45092.125</v>
       </c>
       <c r="Q16" s="9">
         <v>45873.333333333336</v>
@@ -3799,7 +3781,7 @@
         <v>65</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="T16" s="6" t="s">
         <v>171</v>
@@ -3820,16 +3802,16 @@
         <v>65</v>
       </c>
       <c r="Z16" s="10">
-        <v>299.75</v>
+        <v>441.44</v>
       </c>
       <c r="AA16" s="10">
         <v>0</v>
       </c>
       <c r="AB16" s="10">
-        <v>299.75</v>
+        <v>441.44</v>
       </c>
       <c r="AC16" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="AD16" s="6" t="s">
         <v>65</v>
@@ -3838,10 +3820,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF16" s="7">
-        <v>121204</v>
+        <v>180280</v>
       </c>
       <c r="AG16" s="9">
-        <v>46175.3575</v>
+        <v>46185.44417824074</v>
       </c>
       <c r="AH16" s="6" t="s">
         <v>65</v>
@@ -3850,10 +3832,10 @@
         <v>78</v>
       </c>
       <c r="AJ16" s="11">
-        <v>0.014605100550499</v>
+        <v>0.013333333333333</v>
       </c>
       <c r="AK16" s="6" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="AL16" s="6" t="s">
         <v>173</v>
@@ -3868,19 +3850,19 @@
         <v>65</v>
       </c>
       <c r="AP16" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="AQ16" s="10" t="s">
-        <v>65</v>
+        <v>177</v>
+      </c>
+      <c r="AQ16" s="10">
+        <v>0</v>
       </c>
       <c r="AR16" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS16" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AT16" s="7">
-        <v>5274</v>
+        <v>7414</v>
       </c>
       <c r="AU16" s="6" t="s">
         <v>82</v>
@@ -3889,7 +3871,7 @@
         <v>83</v>
       </c>
       <c r="AW16" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AX16" s="6" t="s">
         <v>117</v>
@@ -3901,31 +3883,31 @@
         <v>65</v>
       </c>
       <c r="BA16" s="8">
-        <v>46181.458333333336</v>
+        <v>46202.99998842592</v>
       </c>
       <c r="BB16" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC16" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD16" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD16" s="10">
+        <v>0</v>
       </c>
       <c r="BE16" s="10">
-        <v>44505</v>
+        <v>45000</v>
       </c>
       <c r="BF16" s="10">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="BG16" s="10">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="BH16" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="BI16" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="BJ16" s="6" t="s">
         <v>89</v>
@@ -3933,25 +3915,25 @@
     </row>
     <row r="17">
       <c r="A17" s="7">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B17" s="7">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>65</v>
@@ -3960,7 +3942,7 @@
         <v>68</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>68</v>
@@ -3969,28 +3951,28 @@
         <v>65</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N17" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O17" s="7">
-        <v>258551</v>
-      </c>
-      <c r="P17" s="8">
-        <v>45092.125</v>
+        <v>258547</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="Q17" s="9">
-        <v>45873.333333333336</v>
+        <v>46098.375</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="U17" s="6" t="s">
         <v>65</v>
@@ -4008,16 +3990,16 @@
         <v>65</v>
       </c>
       <c r="Z17" s="10">
-        <v>350.48</v>
+        <v>390.72</v>
       </c>
       <c r="AA17" s="10">
         <v>0</v>
       </c>
       <c r="AB17" s="10">
-        <v>350.48</v>
+        <v>390.72</v>
       </c>
       <c r="AC17" s="6" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="AD17" s="6" t="s">
         <v>65</v>
@@ -4026,10 +4008,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF17" s="7">
-        <v>179292</v>
+        <v>102894</v>
       </c>
       <c r="AG17" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH17" s="6" t="s">
         <v>65</v>
@@ -4038,13 +4020,13 @@
         <v>78</v>
       </c>
       <c r="AJ17" s="11">
-        <v>0.013333333333333</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="6" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="AL17" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AM17" s="6" t="s">
         <v>65</v>
@@ -4058,8 +4040,8 @@
       <c r="AP17" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="AQ17" s="10">
-        <v>0</v>
+      <c r="AQ17" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR17" s="6" t="s">
         <v>65</v>
@@ -4068,7 +4050,7 @@
         <v>187</v>
       </c>
       <c r="AT17" s="7">
-        <v>7535</v>
+        <v>20964</v>
       </c>
       <c r="AU17" s="6" t="s">
         <v>82</v>
@@ -4095,25 +4077,25 @@
         <v>65</v>
       </c>
       <c r="BC17" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD17" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE17" s="10">
-        <v>45000</v>
+        <v>189</v>
+      </c>
+      <c r="BD17" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE17" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF17" s="10">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="BG17" s="10">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="BH17" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BI17" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BJ17" s="6" t="s">
         <v>89</v>
@@ -4121,25 +4103,25 @@
     </row>
     <row r="18">
       <c r="A18" s="7">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="7">
         <v>2022</v>
       </c>
-      <c r="B18" s="7">
-        <v>2021</v>
-      </c>
       <c r="C18" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>65</v>
@@ -4148,7 +4130,7 @@
         <v>68</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>68</v>
@@ -4157,16 +4139,16 @@
         <v>65</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O18" s="7">
-        <v>258539</v>
+        <v>258528</v>
       </c>
       <c r="P18" s="8">
-        <v>45475.125</v>
+        <v>45729</v>
       </c>
       <c r="Q18" s="9">
         <v>45873.333333333336</v>
@@ -4175,10 +4157,10 @@
         <v>65</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U18" s="6" t="s">
         <v>65</v>
@@ -4196,16 +4178,16 @@
         <v>65</v>
       </c>
       <c r="Z18" s="10">
-        <v>1039.98</v>
+        <v>299.75</v>
       </c>
       <c r="AA18" s="10">
         <v>0</v>
       </c>
       <c r="AB18" s="10">
-        <v>1039.98</v>
+        <v>299.75</v>
       </c>
       <c r="AC18" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD18" s="6" t="s">
         <v>65</v>
@@ -4214,10 +4196,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF18" s="7">
-        <v>187088</v>
+        <v>122267</v>
       </c>
       <c r="AG18" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH18" s="6" t="s">
         <v>65</v>
@@ -4226,13 +4208,13 @@
         <v>78</v>
       </c>
       <c r="AJ18" s="11">
-        <v>0.013846153846153</v>
+        <v>0.014605100550499</v>
       </c>
       <c r="AK18" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL18" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM18" s="6" t="s">
         <v>65</v>
@@ -4244,10 +4226,10 @@
         <v>65</v>
       </c>
       <c r="AP18" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="AQ18" s="10">
-        <v>0</v>
+        <v>157</v>
+      </c>
+      <c r="AQ18" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR18" s="6" t="s">
         <v>65</v>
@@ -4256,7 +4238,7 @@
         <v>196</v>
       </c>
       <c r="AT18" s="7">
-        <v>11120</v>
+        <v>5224</v>
       </c>
       <c r="AU18" s="6" t="s">
         <v>82</v>
@@ -4277,25 +4259,25 @@
         <v>65</v>
       </c>
       <c r="BA18" s="8">
-        <v>46223.99998842592</v>
+        <v>46265.458333333336</v>
       </c>
       <c r="BB18" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC18" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD18" s="10">
-        <v>0</v>
+        <v>189</v>
+      </c>
+      <c r="BD18" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BE18" s="10">
-        <v>45500</v>
+        <v>44505</v>
       </c>
       <c r="BF18" s="10">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="BG18" s="10">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="BH18" s="6" t="s">
         <v>198</v>
@@ -4309,10 +4291,10 @@
     </row>
     <row r="19">
       <c r="A19" s="7">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="B19" s="7">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>199</v>
@@ -4351,19 +4333,19 @@
         <v>65</v>
       </c>
       <c r="O19" s="7">
-        <v>258526</v>
-      </c>
-      <c r="P19" s="8">
-        <v>45351</v>
+        <v>258527</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="Q19" s="9">
-        <v>45873.333333333336</v>
+        <v>46091.541666666664</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="T19" s="6" t="s">
         <v>199</v>
@@ -4384,16 +4366,16 @@
         <v>65</v>
       </c>
       <c r="Z19" s="10">
-        <v>2430.95</v>
+        <v>694.95</v>
       </c>
       <c r="AA19" s="10">
         <v>0</v>
       </c>
       <c r="AB19" s="10">
-        <v>2430.95</v>
+        <v>766.78</v>
       </c>
       <c r="AC19" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD19" s="6" t="s">
         <v>65</v>
@@ -4402,10 +4384,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF19" s="7">
-        <v>239800</v>
+        <v>89572</v>
       </c>
       <c r="AG19" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH19" s="6" t="s">
         <v>65</v>
@@ -4414,10 +4396,10 @@
         <v>78</v>
       </c>
       <c r="AJ19" s="11">
-        <v>0.01575</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="6" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="AL19" s="6" t="s">
         <v>201</v>
@@ -4432,19 +4414,19 @@
         <v>65</v>
       </c>
       <c r="AP19" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="AQ19" s="10" t="s">
-        <v>65</v>
+        <v>204</v>
+      </c>
+      <c r="AQ19" s="10">
+        <v>0</v>
       </c>
       <c r="AR19" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS19" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AT19" s="7">
-        <v>10525</v>
+        <v>15347</v>
       </c>
       <c r="AU19" s="6" t="s">
         <v>82</v>
@@ -4453,7 +4435,7 @@
         <v>83</v>
       </c>
       <c r="AW19" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AX19" s="6" t="s">
         <v>117</v>
@@ -4473,23 +4455,23 @@
       <c r="BC19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="BD19" s="10" t="s">
-        <v>65</v>
+      <c r="BD19" s="10">
+        <v>0</v>
       </c>
       <c r="BE19" s="10">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="BF19" s="10">
         <v>630</v>
       </c>
       <c r="BG19" s="10">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="BH19" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="BI19" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="BJ19" s="6" t="s">
         <v>89</v>
@@ -4503,19 +4485,19 @@
         <v>2018</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>65</v>
@@ -4524,7 +4506,7 @@
         <v>68</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>68</v>
@@ -4533,7 +4515,7 @@
         <v>65</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N20" s="6" t="s">
         <v>65</v>
@@ -4551,10 +4533,10 @@
         <v>65</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="U20" s="6" t="s">
         <v>65</v>
@@ -4575,13 +4557,13 @@
         <v>200.77</v>
       </c>
       <c r="AA20" s="10">
-        <v>1076.7</v>
+        <v>1407.89</v>
       </c>
       <c r="AB20" s="10">
-        <v>1277.47</v>
+        <v>1608.66</v>
       </c>
       <c r="AC20" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD20" s="6" t="s">
         <v>65</v>
@@ -4590,10 +4572,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF20" s="7">
-        <v>238631</v>
+        <v>238627</v>
       </c>
       <c r="AG20" s="9">
-        <v>46164.408171296294</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH20" s="6" t="s">
         <v>65</v>
@@ -4605,10 +4587,10 @@
         <v>0.015897435897435</v>
       </c>
       <c r="AK20" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL20" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM20" s="6" t="s">
         <v>65</v>
@@ -4620,7 +4602,7 @@
         <v>65</v>
       </c>
       <c r="AP20" s="6" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="AQ20" s="10">
         <v>0</v>
@@ -4629,10 +4611,10 @@
         <v>65</v>
       </c>
       <c r="AS20" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AT20" s="7">
-        <v>8380</v>
+        <v>8140</v>
       </c>
       <c r="AU20" s="6" t="s">
         <v>82</v>
@@ -4641,7 +4623,7 @@
         <v>83</v>
       </c>
       <c r="AW20" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AX20" s="6" t="s">
         <v>117</v>
@@ -4674,10 +4656,10 @@
         <v>620</v>
       </c>
       <c r="BH20" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="BI20" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="BJ20" s="6" t="s">
         <v>89</v>
@@ -4691,19 +4673,19 @@
         <v>2020</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>65</v>
@@ -4712,7 +4694,7 @@
         <v>68</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>68</v>
@@ -4721,7 +4703,7 @@
         <v>65</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N21" s="6" t="s">
         <v>65</v>
@@ -4739,10 +4721,10 @@
         <v>65</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="T21" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U21" s="6" t="s">
         <v>65</v>
@@ -4769,7 +4751,7 @@
         <v>229.09</v>
       </c>
       <c r="AC21" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD21" s="6" t="s">
         <v>65</v>
@@ -4778,10 +4760,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF21" s="7">
-        <v>153244</v>
+        <v>154569</v>
       </c>
       <c r="AG21" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH21" s="6" t="s">
         <v>65</v>
@@ -4793,10 +4775,10 @@
         <v>0.013793103448275</v>
       </c>
       <c r="AK21" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL21" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM21" s="6" t="s">
         <v>65</v>
@@ -4808,7 +4790,7 @@
         <v>65</v>
       </c>
       <c r="AP21" s="6" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="AQ21" s="10">
         <v>0</v>
@@ -4817,10 +4799,10 @@
         <v>65</v>
       </c>
       <c r="AS21" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AT21" s="7">
-        <v>9903</v>
+        <v>9746</v>
       </c>
       <c r="AU21" s="6" t="s">
         <v>82</v>
@@ -4829,7 +4811,7 @@
         <v>83</v>
       </c>
       <c r="AW21" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AX21" s="6" t="s">
         <v>117</v>
@@ -4862,10 +4844,10 @@
         <v>600</v>
       </c>
       <c r="BH21" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="BI21" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="BJ21" s="6" t="s">
         <v>89</v>
@@ -4879,19 +4861,19 @@
         <v>2021</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D22" s="8">
         <v>45854.9691099537</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>65</v>
@@ -4900,7 +4882,7 @@
         <v>68</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>68</v>
@@ -4909,7 +4891,7 @@
         <v>65</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>65</v>
@@ -4927,10 +4909,10 @@
         <v>65</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="U22" s="6" t="s">
         <v>65</v>
@@ -4948,16 +4930,16 @@
         <v>65</v>
       </c>
       <c r="Z22" s="10">
-        <v>857.24</v>
+        <v>1200.84</v>
       </c>
       <c r="AA22" s="10">
         <v>0</v>
       </c>
       <c r="AB22" s="10">
-        <v>897.24</v>
+        <v>1240.84</v>
       </c>
       <c r="AC22" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD22" s="6" t="s">
         <v>65</v>
@@ -4966,10 +4948,10 @@
         <v>45861.56458333333</v>
       </c>
       <c r="AF22" s="7">
-        <v>191102</v>
+        <v>191103</v>
       </c>
       <c r="AG22" s="9">
-        <v>46163.392905092594</v>
+        <v>46185.441666666666</v>
       </c>
       <c r="AH22" s="6" t="s">
         <v>65</v>
@@ -4981,10 +4963,10 @@
         <v>0.015272727272727</v>
       </c>
       <c r="AK22" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL22" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM22" s="6" t="s">
         <v>65</v>
@@ -5008,7 +4990,7 @@
         <v>230</v>
       </c>
       <c r="AT22" s="7">
-        <v>3545</v>
+        <v>3444</v>
       </c>
       <c r="AU22" s="6" t="s">
         <v>82</v>
@@ -5061,10 +5043,10 @@
     </row>
     <row r="23">
       <c r="A23" s="7">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B23" s="7">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>233</v>
@@ -5103,19 +5085,19 @@
         <v>65</v>
       </c>
       <c r="O23" s="7">
-        <v>258549</v>
+        <v>258532</v>
       </c>
       <c r="P23" s="8">
-        <v>45105.125</v>
+        <v>45344.125</v>
       </c>
       <c r="Q23" s="9">
-        <v>45861.393055555556</v>
+        <v>45873.333333333336</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>105</v>
+        <v>238</v>
       </c>
       <c r="T23" s="6" t="s">
         <v>233</v>
@@ -5136,16 +5118,16 @@
         <v>65</v>
       </c>
       <c r="Z23" s="10">
-        <v>2040.16</v>
+        <v>381.44</v>
       </c>
       <c r="AA23" s="10">
-        <v>400</v>
+        <v>711.56</v>
       </c>
       <c r="AB23" s="10">
-        <v>2440.16</v>
+        <v>1093</v>
       </c>
       <c r="AC23" s="6" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="AD23" s="6" t="s">
         <v>65</v>
@@ -5154,22 +5136,22 @@
         <v>45873.458333333336</v>
       </c>
       <c r="AF23" s="7">
-        <v>292424</v>
+        <v>287560</v>
       </c>
       <c r="AG23" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH23" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AI23" s="6" t="s">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AJ23" s="11">
-        <v>0.014545454545454</v>
+        <v>0.016190476190476</v>
       </c>
       <c r="AK23" s="6" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="AL23" s="6" t="s">
         <v>235</v>
@@ -5184,19 +5166,19 @@
         <v>65</v>
       </c>
       <c r="AP23" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AQ23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS23" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="AQ23" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR23" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS23" s="6" t="s">
-        <v>240</v>
-      </c>
       <c r="AT23" s="7">
-        <v>20785</v>
+        <v>0</v>
       </c>
       <c r="AU23" s="6" t="s">
         <v>82</v>
@@ -5205,7 +5187,7 @@
         <v>83</v>
       </c>
       <c r="AW23" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AX23" s="6" t="s">
         <v>117</v>
@@ -5217,7 +5199,7 @@
         <v>65</v>
       </c>
       <c r="BA23" s="8">
-        <v>46223.99998842592</v>
+        <v>46188.99998842592</v>
       </c>
       <c r="BB23" s="9" t="s">
         <v>65</v>
@@ -5229,19 +5211,19 @@
         <v>0</v>
       </c>
       <c r="BE23" s="10">
-        <v>41250</v>
+        <v>42000</v>
       </c>
       <c r="BF23" s="10">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="BG23" s="10">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="BH23" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BI23" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BJ23" s="6" t="s">
         <v>89</v>
@@ -5249,25 +5231,25 @@
     </row>
     <row r="24">
       <c r="A24" s="7">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B24" s="7">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="F24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>244</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>245</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>65</v>
@@ -5276,7 +5258,7 @@
         <v>68</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>68</v>
@@ -5285,28 +5267,28 @@
         <v>65</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O24" s="7">
-        <v>258532</v>
+        <v>258549</v>
       </c>
       <c r="P24" s="8">
-        <v>45344.125</v>
+        <v>45105.125</v>
       </c>
       <c r="Q24" s="9">
-        <v>45873.333333333336</v>
+        <v>45861.393055555556</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S24" s="6" t="s">
-        <v>229</v>
+        <v>92</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U24" s="6" t="s">
         <v>65</v>
@@ -5324,16 +5306,16 @@
         <v>65</v>
       </c>
       <c r="Z24" s="10">
-        <v>381.44</v>
+        <v>2040.16</v>
       </c>
       <c r="AA24" s="10">
-        <v>711.56</v>
+        <v>400</v>
       </c>
       <c r="AB24" s="10">
-        <v>1093</v>
+        <v>2440.16</v>
       </c>
       <c r="AC24" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="AD24" s="6" t="s">
         <v>65</v>
@@ -5342,25 +5324,25 @@
         <v>45873.458333333336</v>
       </c>
       <c r="AF24" s="7">
-        <v>286674</v>
+        <v>293844</v>
       </c>
       <c r="AG24" s="9">
-        <v>46175.357511574075</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH24" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AI24" s="6" t="s">
-        <v>78</v>
+        <v>247</v>
       </c>
       <c r="AJ24" s="11">
-        <v>0.016190476190476</v>
+        <v>0.014545454545454</v>
       </c>
       <c r="AK24" s="6" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="AL24" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AM24" s="6" t="s">
         <v>65</v>
@@ -5372,7 +5354,7 @@
         <v>65</v>
       </c>
       <c r="AP24" s="6" t="s">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="AQ24" s="10">
         <v>0</v>
@@ -5384,7 +5366,7 @@
         <v>248</v>
       </c>
       <c r="AT24" s="7">
-        <v>0</v>
+        <v>20344</v>
       </c>
       <c r="AU24" s="6" t="s">
         <v>82</v>
@@ -5405,7 +5387,7 @@
         <v>65</v>
       </c>
       <c r="BA24" s="8">
-        <v>46188.99998842592</v>
+        <v>46223.99998842592</v>
       </c>
       <c r="BB24" s="9" t="s">
         <v>65</v>
@@ -5417,13 +5399,13 @@
         <v>0</v>
       </c>
       <c r="BE24" s="10">
-        <v>42000</v>
+        <v>41250</v>
       </c>
       <c r="BF24" s="10">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="BG24" s="10">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="BH24" s="6" t="s">
         <v>250</v>
@@ -5491,7 +5473,7 @@
         <v>65</v>
       </c>
       <c r="S25" s="6" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="T25" s="6" t="s">
         <v>251</v>
@@ -5521,7 +5503,7 @@
         <v>479.38</v>
       </c>
       <c r="AC25" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD25" s="6" t="s">
         <v>65</v>
@@ -5530,10 +5512,10 @@
         <v>45911.791666666664</v>
       </c>
       <c r="AF25" s="7">
-        <v>128962</v>
+        <v>130237</v>
       </c>
       <c r="AG25" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH25" s="6" t="s">
         <v>65</v>
@@ -5545,7 +5527,7 @@
         <v>0.013737373737373</v>
       </c>
       <c r="AK25" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL25" s="6" t="s">
         <v>253</v>
@@ -5560,7 +5542,7 @@
         <v>65</v>
       </c>
       <c r="AP25" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ25" s="10">
         <v>0</v>
@@ -5572,7 +5554,7 @@
         <v>257</v>
       </c>
       <c r="AT25" s="7">
-        <v>6019</v>
+        <v>5900</v>
       </c>
       <c r="AU25" s="6" t="s">
         <v>82</v>
@@ -5593,7 +5575,7 @@
         <v>65</v>
       </c>
       <c r="BA25" s="8">
-        <v>46181.48611111111</v>
+        <v>46230.48611111111</v>
       </c>
       <c r="BB25" s="9" t="s">
         <v>65</v>
@@ -5709,7 +5691,7 @@
         <v>670.08</v>
       </c>
       <c r="AC26" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD26" s="6" t="s">
         <v>65</v>
@@ -5718,10 +5700,10 @@
         <v>45915.458333333336</v>
       </c>
       <c r="AF26" s="7">
-        <v>117956</v>
+        <v>118475</v>
       </c>
       <c r="AG26" s="9">
-        <v>46175.3575</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH26" s="6" t="s">
         <v>65</v>
@@ -5733,7 +5715,7 @@
         <v>0.013765182186234</v>
       </c>
       <c r="AK26" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL26" s="6" t="s">
         <v>262</v>
@@ -5748,7 +5730,7 @@
         <v>65</v>
       </c>
       <c r="AP26" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ26" s="10">
         <v>0</v>
@@ -5760,7 +5742,7 @@
         <v>266</v>
       </c>
       <c r="AT26" s="7">
-        <v>3886</v>
+        <v>3814</v>
       </c>
       <c r="AU26" s="6" t="s">
         <v>82</v>
@@ -5781,7 +5763,7 @@
         <v>65</v>
       </c>
       <c r="BA26" s="8">
-        <v>46181.99998842592</v>
+        <v>46230.99998842592</v>
       </c>
       <c r="BB26" s="9" t="s">
         <v>65</v>
@@ -5897,7 +5879,7 @@
         <v>595.14</v>
       </c>
       <c r="AC27" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD27" s="6" t="s">
         <v>65</v>
@@ -5906,10 +5888,10 @@
         <v>45957.458333333336</v>
       </c>
       <c r="AF27" s="7">
-        <v>129846</v>
+        <v>130867</v>
       </c>
       <c r="AG27" s="9">
-        <v>46175.3575</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH27" s="6" t="s">
         <v>65</v>
@@ -5921,7 +5903,7 @@
         <v>0.013765182186234</v>
       </c>
       <c r="AK27" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL27" s="6" t="s">
         <v>271</v>
@@ -5936,7 +5918,7 @@
         <v>65</v>
       </c>
       <c r="AP27" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ27" s="10">
         <v>0</v>
@@ -5948,7 +5930,7 @@
         <v>275</v>
       </c>
       <c r="AT27" s="7">
-        <v>5371</v>
+        <v>5294</v>
       </c>
       <c r="AU27" s="6" t="s">
         <v>82</v>
@@ -5969,7 +5951,7 @@
         <v>65</v>
       </c>
       <c r="BA27" s="8">
-        <v>46181.99998842592</v>
+        <v>46230.99998842592</v>
       </c>
       <c r="BB27" s="9" t="s">
         <v>65</v>
@@ -6055,7 +6037,7 @@
         <v>65</v>
       </c>
       <c r="S28" s="6" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="T28" s="6" t="s">
         <v>278</v>
@@ -6085,7 +6067,7 @@
         <v>832.5</v>
       </c>
       <c r="AC28" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD28" s="6" t="s">
         <v>65</v>
@@ -6094,10 +6076,10 @@
         <v>45958.791666666664</v>
       </c>
       <c r="AF28" s="7">
-        <v>211265</v>
+        <v>212099</v>
       </c>
       <c r="AG28" s="9">
-        <v>46175.357511574075</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH28" s="6" t="s">
         <v>65</v>
@@ -6109,7 +6091,7 @@
         <v>0.015089820359281</v>
       </c>
       <c r="AK28" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL28" s="6" t="s">
         <v>280</v>
@@ -6124,7 +6106,7 @@
         <v>65</v>
       </c>
       <c r="AP28" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ28" s="10">
         <v>0</v>
@@ -6136,7 +6118,7 @@
         <v>283</v>
       </c>
       <c r="AT28" s="7">
-        <v>4878</v>
+        <v>4796</v>
       </c>
       <c r="AU28" s="6" t="s">
         <v>82</v>
@@ -6243,7 +6225,7 @@
         <v>65</v>
       </c>
       <c r="S29" s="6" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="T29" s="6" t="s">
         <v>286</v>
@@ -6273,7 +6255,7 @@
         <v>800.63</v>
       </c>
       <c r="AC29" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD29" s="6" t="s">
         <v>65</v>
@@ -6282,10 +6264,10 @@
         <v>45980.666666666664</v>
       </c>
       <c r="AF29" s="7">
-        <v>127507</v>
+        <v>127892</v>
       </c>
       <c r="AG29" s="9">
-        <v>46175.3575</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH29" s="6" t="s">
         <v>65</v>
@@ -6297,7 +6279,7 @@
         <v>0.014639397201291</v>
       </c>
       <c r="AK29" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL29" s="6" t="s">
         <v>288</v>
@@ -6312,7 +6294,7 @@
         <v>65</v>
       </c>
       <c r="AP29" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ29" s="10" t="s">
         <v>65</v>
@@ -6324,7 +6306,7 @@
         <v>291</v>
       </c>
       <c r="AT29" s="7">
-        <v>2913</v>
+        <v>2843</v>
       </c>
       <c r="AU29" s="6" t="s">
         <v>82</v>
@@ -6461,7 +6443,7 @@
         <v>0</v>
       </c>
       <c r="AC30" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD30" s="6" t="s">
         <v>65</v>
@@ -6470,10 +6452,10 @@
         <v>45986.458333333336</v>
       </c>
       <c r="AF30" s="7">
-        <v>103022</v>
+        <v>103115</v>
       </c>
       <c r="AG30" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH30" s="6" t="s">
         <v>65</v>
@@ -6485,7 +6467,7 @@
         <v>0.050560747663551</v>
       </c>
       <c r="AK30" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL30" s="6" t="s">
         <v>296</v>
@@ -6512,7 +6494,7 @@
         <v>301</v>
       </c>
       <c r="AT30" s="7">
-        <v>3735</v>
+        <v>3583</v>
       </c>
       <c r="AU30" s="6" t="s">
         <v>82</v>
@@ -6539,7 +6521,7 @@
         <v>65</v>
       </c>
       <c r="BC30" s="6" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="BD30" s="10">
         <v>0</v>
@@ -6649,7 +6631,7 @@
         <v>400.54</v>
       </c>
       <c r="AC31" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD31" s="6" t="s">
         <v>65</v>
@@ -6658,10 +6640,10 @@
         <v>46031.791666666664</v>
       </c>
       <c r="AF31" s="7">
-        <v>106081</v>
+        <v>106378</v>
       </c>
       <c r="AG31" s="9">
-        <v>46175.3575</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH31" s="6" t="s">
         <v>65</v>
@@ -6673,7 +6655,7 @@
         <v>0.013255360623781</v>
       </c>
       <c r="AK31" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL31" s="6" t="s">
         <v>306</v>
@@ -6688,7 +6670,7 @@
         <v>65</v>
       </c>
       <c r="AP31" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ31" s="10" t="s">
         <v>65</v>
@@ -6700,7 +6682,7 @@
         <v>310</v>
       </c>
       <c r="AT31" s="7">
-        <v>1519</v>
+        <v>1489</v>
       </c>
       <c r="AU31" s="6" t="s">
         <v>82</v>
@@ -6727,7 +6709,7 @@
         <v>65</v>
       </c>
       <c r="BC31" s="6" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="BD31" s="10" t="s">
         <v>65</v>
@@ -6837,7 +6819,7 @@
         <v>112.22</v>
       </c>
       <c r="AC32" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD32" s="6" t="s">
         <v>65</v>
@@ -6846,10 +6828,10 @@
         <v>46041.458333333336</v>
       </c>
       <c r="AF32" s="7">
-        <v>225001</v>
+        <v>225286</v>
       </c>
       <c r="AG32" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH32" s="6" t="s">
         <v>65</v>
@@ -6861,7 +6843,7 @@
         <v>0.05090909090909</v>
       </c>
       <c r="AK32" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL32" s="6" t="s">
         <v>65</v>
@@ -6876,7 +6858,7 @@
         <v>65</v>
       </c>
       <c r="AP32" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ32" s="10">
         <v>0</v>
@@ -6888,7 +6870,7 @@
         <v>319</v>
       </c>
       <c r="AT32" s="7">
-        <v>2920</v>
+        <v>2752</v>
       </c>
       <c r="AU32" s="6" t="s">
         <v>82</v>
@@ -7025,7 +7007,7 @@
         <v>143.59</v>
       </c>
       <c r="AC33" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD33" s="6" t="s">
         <v>65</v>
@@ -7034,10 +7016,10 @@
         <v>46087.625</v>
       </c>
       <c r="AF33" s="7">
-        <v>82643</v>
+        <v>83668</v>
       </c>
       <c r="AG33" s="9">
-        <v>46175.3575</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH33" s="6" t="s">
         <v>65</v>
@@ -7049,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL33" s="6" t="s">
         <v>324</v>
@@ -7064,7 +7046,7 @@
         <v>65</v>
       </c>
       <c r="AP33" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ33" s="10" t="s">
         <v>65</v>
@@ -7076,7 +7058,7 @@
         <v>328</v>
       </c>
       <c r="AT33" s="7">
-        <v>8678</v>
+        <v>8210</v>
       </c>
       <c r="AU33" s="6" t="s">
         <v>82</v>
@@ -7183,7 +7165,7 @@
         <v>65</v>
       </c>
       <c r="S34" s="6" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="T34" s="6" t="s">
         <v>331</v>
@@ -7204,16 +7186,16 @@
         <v>65</v>
       </c>
       <c r="Z34" s="10">
-        <v>294.79</v>
+        <v>802.87</v>
       </c>
       <c r="AA34" s="10">
         <v>0</v>
       </c>
       <c r="AB34" s="10">
-        <v>294.79</v>
+        <v>802.87</v>
       </c>
       <c r="AC34" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD34" s="6" t="s">
         <v>65</v>
@@ -7222,10 +7204,10 @@
         <v>46092.708333333336</v>
       </c>
       <c r="AF34" s="7">
-        <v>155332</v>
+        <v>156083</v>
       </c>
       <c r="AG34" s="9">
-        <v>46175.357511574075</v>
+        <v>46185.4762962963</v>
       </c>
       <c r="AH34" s="6" t="s">
         <v>65</v>
@@ -7237,7 +7219,7 @@
         <v>0.015831660251596</v>
       </c>
       <c r="AK34" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL34" s="6" t="s">
         <v>333</v>
@@ -7252,7 +7234,7 @@
         <v>65</v>
       </c>
       <c r="AP34" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ34" s="10">
         <v>0</v>
@@ -7264,7 +7246,7 @@
         <v>336</v>
       </c>
       <c r="AT34" s="7">
-        <v>-10230</v>
+        <v>-9036</v>
       </c>
       <c r="AU34" s="6" t="s">
         <v>82</v>
@@ -7401,7 +7383,7 @@
         <v>194.95</v>
       </c>
       <c r="AC35" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD35" s="6" t="s">
         <v>65</v>
@@ -7440,7 +7422,7 @@
         <v>65</v>
       </c>
       <c r="AP35" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ35" s="10" t="s">
         <v>65</v>
@@ -7473,7 +7455,7 @@
         <v>65</v>
       </c>
       <c r="BA35" s="8">
-        <v>46181.458333333336</v>
+        <v>46230.458333333336</v>
       </c>
       <c r="BB35" s="9" t="s">
         <v>65</v>
@@ -7589,7 +7571,7 @@
         <v>581.49</v>
       </c>
       <c r="AC36" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD36" s="6" t="s">
         <v>65</v>
@@ -7598,10 +7580,10 @@
         <v>46097.805555555555</v>
       </c>
       <c r="AF36" s="7">
-        <v>102507</v>
+        <v>103578</v>
       </c>
       <c r="AG36" s="9">
-        <v>46175.35748842593</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH36" s="6" t="s">
         <v>65</v>
@@ -7613,7 +7595,7 @@
         <v>0.013207547169811</v>
       </c>
       <c r="AK36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL36" s="6" t="s">
         <v>351</v>
@@ -7628,7 +7610,7 @@
         <v>65</v>
       </c>
       <c r="AP36" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ36" s="10">
         <v>0</v>
@@ -7640,7 +7622,7 @@
         <v>355</v>
       </c>
       <c r="AT36" s="7">
-        <v>4367</v>
+        <v>4288</v>
       </c>
       <c r="AU36" s="6" t="s">
         <v>82</v>
@@ -7661,13 +7643,13 @@
         <v>65</v>
       </c>
       <c r="BA36" s="8">
-        <v>46181.99998842592</v>
+        <v>46265.99998842592</v>
       </c>
       <c r="BB36" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC36" s="6" t="s">
-        <v>356</v>
+        <v>189</v>
       </c>
       <c r="BD36" s="10">
         <v>0</v>
@@ -7682,10 +7664,10 @@
         <v>700</v>
       </c>
       <c r="BH36" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BI36" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BJ36" s="6" t="s">
         <v>89</v>
@@ -7699,19 +7681,19 @@
         <v>2019</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D37" s="8">
         <v>46119.56219482639</v>
       </c>
       <c r="E37" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>359</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>360</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>65</v>
@@ -7720,7 +7702,7 @@
         <v>254</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>254</v>
@@ -7729,7 +7711,7 @@
         <v>65</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>65</v>
@@ -7747,10 +7729,10 @@
         <v>65</v>
       </c>
       <c r="S37" s="6" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="T37" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="U37" s="6" t="s">
         <v>65</v>
@@ -7777,7 +7759,7 @@
         <v>832.11</v>
       </c>
       <c r="AC37" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD37" s="6" t="s">
         <v>65</v>
@@ -7786,10 +7768,10 @@
         <v>46118.850694444445</v>
       </c>
       <c r="AF37" s="7">
-        <v>185000</v>
+        <v>184905</v>
       </c>
       <c r="AG37" s="9">
-        <v>46176.39858796296</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH37" s="6" t="s">
         <v>65</v>
@@ -7801,10 +7783,10 @@
         <v>0.015764705882352</v>
       </c>
       <c r="AK37" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL37" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AM37" s="6" t="s">
         <v>65</v>
@@ -7816,7 +7798,7 @@
         <v>65</v>
       </c>
       <c r="AP37" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ37" s="10">
         <v>0</v>
@@ -7825,10 +7807,10 @@
         <v>65</v>
       </c>
       <c r="AS37" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AT37" s="7">
-        <v>2038</v>
+        <v>1735</v>
       </c>
       <c r="AU37" s="6" t="s">
         <v>82</v>
@@ -7870,10 +7852,10 @@
         <v>670</v>
       </c>
       <c r="BH37" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="BI37" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="BJ37" s="6" t="s">
         <v>89</v>
@@ -7893,13 +7875,13 @@
         <v>46135.522659375</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>365</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>366</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>65</v>
@@ -7908,7 +7890,7 @@
         <v>254</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>254</v>
@@ -7917,7 +7899,7 @@
         <v>70</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>65</v>
@@ -7935,10 +7917,10 @@
         <v>65</v>
       </c>
       <c r="S38" s="6" t="s">
-        <v>354</v>
+        <v>125</v>
       </c>
       <c r="T38" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U38" s="6" t="s">
         <v>65</v>
@@ -7956,16 +7938,16 @@
         <v>65</v>
       </c>
       <c r="Z38" s="10">
-        <v>90.96</v>
+        <v>131.9</v>
       </c>
       <c r="AA38" s="10">
         <v>0</v>
       </c>
       <c r="AB38" s="10">
-        <v>90.96</v>
+        <v>131.9</v>
       </c>
       <c r="AC38" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD38" s="6" t="s">
         <v>65</v>
@@ -7974,10 +7956,10 @@
         <v>46119.708333333336</v>
       </c>
       <c r="AF38" s="7">
-        <v>248739</v>
+        <v>249059</v>
       </c>
       <c r="AG38" s="9">
-        <v>46175.357511574075</v>
+        <v>46185.43822916667</v>
       </c>
       <c r="AH38" s="6" t="s">
         <v>65</v>
@@ -7989,7 +7971,7 @@
         <v>0.053635736725155</v>
       </c>
       <c r="AK38" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL38" s="6" t="s">
         <v>65</v>
@@ -8004,7 +7986,7 @@
         <v>65</v>
       </c>
       <c r="AP38" s="6" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="AQ38" s="10">
         <v>0</v>
@@ -8013,10 +7995,10 @@
         <v>65</v>
       </c>
       <c r="AS38" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AT38" s="7">
-        <v>383</v>
+        <v>472</v>
       </c>
       <c r="AU38" s="6" t="s">
         <v>82</v>
@@ -8058,10 +8040,10 @@
         <v>2100</v>
       </c>
       <c r="BH38" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="BI38" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="BJ38" s="6" t="s">
         <v>89</v>
@@ -8075,19 +8057,19 @@
         <v>2021</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D39" s="8">
         <v>46127.52819641204</v>
       </c>
       <c r="E39" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G39" s="6" t="s">
         <v>373</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>374</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>65</v>
@@ -8096,7 +8078,7 @@
         <v>254</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>254</v>
@@ -8105,7 +8087,7 @@
         <v>65</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>65</v>
@@ -8123,10 +8105,10 @@
         <v>65</v>
       </c>
       <c r="S39" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="T39" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U39" s="6" t="s">
         <v>65</v>
@@ -8153,7 +8135,7 @@
         <v>150.96</v>
       </c>
       <c r="AC39" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD39" s="6" t="s">
         <v>65</v>
@@ -8162,10 +8144,10 @@
         <v>46125.458333333336</v>
       </c>
       <c r="AF39" s="7">
-        <v>200440</v>
+        <v>201539</v>
       </c>
       <c r="AG39" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH39" s="6" t="s">
         <v>65</v>
@@ -8177,10 +8159,10 @@
         <v>0.0208</v>
       </c>
       <c r="AK39" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL39" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AM39" s="6" t="s">
         <v>65</v>
@@ -8192,7 +8174,7 @@
         <v>65</v>
       </c>
       <c r="AP39" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ39" s="10">
         <v>0</v>
@@ -8201,10 +8183,10 @@
         <v>65</v>
       </c>
       <c r="AS39" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AT39" s="7">
-        <v>4010</v>
+        <v>3960</v>
       </c>
       <c r="AU39" s="6" t="s">
         <v>82</v>
@@ -8246,10 +8228,10 @@
         <v>650</v>
       </c>
       <c r="BH39" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="BI39" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="BJ39" s="6" t="s">
         <v>89</v>
@@ -8263,19 +8245,19 @@
         <v>2026</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D40" s="8">
         <v>46148.59058966435</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>380</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>381</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>65</v>
@@ -8284,7 +8266,7 @@
         <v>342</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>342</v>
@@ -8293,7 +8275,7 @@
         <v>65</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>65</v>
@@ -8311,10 +8293,10 @@
         <v>65</v>
       </c>
       <c r="S40" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="T40" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="U40" s="6" t="s">
         <v>65</v>
@@ -8338,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AB40" s="10">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AC40" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD40" s="6" t="s">
         <v>65</v>
@@ -8365,31 +8347,31 @@
         <v>0</v>
       </c>
       <c r="AK40" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="AL40" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ40" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AR40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS40" s="6" t="s">
         <v>385</v>
-      </c>
-      <c r="AL40" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="AM40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP40" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="AQ40" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="AR40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS40" s="6" t="s">
-        <v>386</v>
       </c>
       <c r="AT40" s="7">
         <v>0</v>
@@ -8419,7 +8401,7 @@
         <v>65</v>
       </c>
       <c r="BC40" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BD40" s="10" t="s">
         <v>65</v>
@@ -8434,10 +8416,10 @@
         <v>1200</v>
       </c>
       <c r="BH40" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BI40" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BJ40" s="6" t="s">
         <v>89</v>
@@ -8451,19 +8433,19 @@
         <v>2019</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D41" s="8">
         <v>45889.59072010417</v>
       </c>
       <c r="E41" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>390</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>391</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>65</v>
@@ -8472,7 +8454,7 @@
         <v>254</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>254</v>
@@ -8481,7 +8463,7 @@
         <v>65</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>65</v>
@@ -8499,10 +8481,10 @@
         <v>65</v>
       </c>
       <c r="S41" s="6" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="T41" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="U41" s="6" t="s">
         <v>65</v>
@@ -8529,7 +8511,7 @@
         <v>944.54</v>
       </c>
       <c r="AC41" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD41" s="6" t="s">
         <v>65</v>
@@ -8538,10 +8520,10 @@
         <v>46146.458333333336</v>
       </c>
       <c r="AF41" s="7">
-        <v>224499</v>
+        <v>225813</v>
       </c>
       <c r="AG41" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH41" s="6" t="s">
         <v>65</v>
@@ -8553,10 +8535,10 @@
         <v>0.014</v>
       </c>
       <c r="AK41" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL41" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AM41" s="6" t="s">
         <v>65</v>
@@ -8568,7 +8550,7 @@
         <v>65</v>
       </c>
       <c r="AP41" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ41" s="10" t="s">
         <v>65</v>
@@ -8577,10 +8559,10 @@
         <v>65</v>
       </c>
       <c r="AS41" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AT41" s="7">
-        <v>3293</v>
+        <v>3526</v>
       </c>
       <c r="AU41" s="6" t="s">
         <v>82</v>
@@ -8589,7 +8571,7 @@
         <v>83</v>
       </c>
       <c r="AW41" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AX41" s="6" t="s">
         <v>117</v>
@@ -8622,10 +8604,10 @@
         <v>630</v>
       </c>
       <c r="BH41" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="BI41" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="BJ41" s="6" t="s">
         <v>89</v>
@@ -8633,64 +8615,64 @@
     </row>
     <row r="42">
       <c r="A42" s="7">
-        <v>2027</v>
+        <v>2018</v>
       </c>
       <c r="B42" s="7">
-        <v>2026</v>
+        <v>2017</v>
       </c>
       <c r="C42" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="D42" s="8">
+        <v>46153.58720679398</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="D42" s="8">
-        <v>46148.57752453704</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="J42" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="H42" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="J42" s="6" t="s">
+      <c r="K42" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M42" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="K42" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M42" s="6" t="s">
+      <c r="N42" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O42" s="7">
+        <v>346470</v>
+      </c>
+      <c r="P42" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>46150.583333333336</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S42" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="N42" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O42" s="7">
-        <v>345716</v>
-      </c>
-      <c r="P42" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q42" s="9">
-        <v>46147.625</v>
-      </c>
-      <c r="R42" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S42" s="6" t="s">
-        <v>384</v>
-      </c>
       <c r="T42" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="U42" s="6" t="s">
         <v>65</v>
@@ -8717,19 +8699,19 @@
         <v>0</v>
       </c>
       <c r="AC42" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD42" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE42" s="8">
-        <v>46147.75</v>
+        <v>46150.67013888889</v>
       </c>
       <c r="AF42" s="7">
-        <v>24</v>
+        <v>107165</v>
       </c>
       <c r="AG42" s="9">
-        <v>46147.625</v>
+        <v>46150.583333333336</v>
       </c>
       <c r="AH42" s="6" t="s">
         <v>65</v>
@@ -8741,10 +8723,10 @@
         <v>0</v>
       </c>
       <c r="AK42" s="6" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="AL42" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AM42" s="6" t="s">
         <v>65</v>
@@ -8756,7 +8738,7 @@
         <v>65</v>
       </c>
       <c r="AP42" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ42" s="10" t="s">
         <v>65</v>
@@ -8765,7 +8747,7 @@
         <v>65</v>
       </c>
       <c r="AS42" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AT42" s="7">
         <v>0</v>
@@ -8795,7 +8777,7 @@
         <v>65</v>
       </c>
       <c r="BC42" s="6" t="s">
-        <v>387</v>
+        <v>87</v>
       </c>
       <c r="BD42" s="10" t="s">
         <v>65</v>
@@ -8804,16 +8786,16 @@
         <v>65</v>
       </c>
       <c r="BF42" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BG42" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BH42" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="BI42" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="BJ42" s="6" t="s">
         <v>89</v>
@@ -8821,25 +8803,25 @@
     </row>
     <row r="43">
       <c r="A43" s="7">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B43" s="7">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D43" s="8">
-        <v>46153.58720679398</v>
+        <v>45890.75695732639</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>65</v>
@@ -8848,7 +8830,7 @@
         <v>254</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>254</v>
@@ -8857,28 +8839,28 @@
         <v>65</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O43" s="7">
-        <v>346470</v>
-      </c>
-      <c r="P43" s="8" t="s">
-        <v>65</v>
+        <v>287667</v>
+      </c>
+      <c r="P43" s="8">
+        <v>45832.125</v>
       </c>
       <c r="Q43" s="9">
-        <v>46150.583333333336</v>
+        <v>46153.333333333336</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S43" s="6" t="s">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="T43" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="U43" s="6" t="s">
         <v>65</v>
@@ -8905,19 +8887,19 @@
         <v>0</v>
       </c>
       <c r="AC43" s="6" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="AD43" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE43" s="8">
-        <v>46150.67013888889</v>
+        <v>46153.458333333336</v>
       </c>
       <c r="AF43" s="7">
-        <v>107165</v>
+        <v>120149</v>
       </c>
       <c r="AG43" s="9">
-        <v>46150.583333333336</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH43" s="6" t="s">
         <v>65</v>
@@ -8926,37 +8908,37 @@
         <v>78</v>
       </c>
       <c r="AJ43" s="11">
-        <v>0</v>
+        <v>0.012903225806451</v>
       </c>
       <c r="AK43" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL43" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="AM43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP43" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="AQ43" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS43" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="AL43" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="AM43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP43" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="AQ43" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="AR43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS43" s="6" t="s">
-        <v>411</v>
-      </c>
       <c r="AT43" s="7">
-        <v>0</v>
+        <v>3036</v>
       </c>
       <c r="AU43" s="6" t="s">
         <v>82</v>
@@ -8965,7 +8947,7 @@
         <v>83</v>
       </c>
       <c r="AW43" s="6" t="s">
-        <v>65</v>
+        <v>411</v>
       </c>
       <c r="AX43" s="6" t="s">
         <v>117</v>
@@ -8977,31 +8959,31 @@
         <v>65</v>
       </c>
       <c r="BA43" s="8">
-        <v>46230.99998842592</v>
+        <v>46209.99998842592</v>
       </c>
       <c r="BB43" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC43" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD43" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE43" s="10" t="s">
-        <v>65</v>
+        <v>412</v>
+      </c>
+      <c r="BD43" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE43" s="10">
+        <v>52700</v>
       </c>
       <c r="BF43" s="10">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="BG43" s="10">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="BH43" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="BI43" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="BJ43" s="6" t="s">
         <v>89</v>
@@ -9009,65 +8991,65 @@
     </row>
     <row r="44">
       <c r="A44" s="7">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B44" s="7">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D44" s="8">
-        <v>45890.75695732639</v>
+        <v>46101.54787534722</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O44" s="7">
+        <v>337543</v>
+      </c>
+      <c r="P44" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q44" s="9">
+        <v>46147.625</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S44" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="T44" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M44" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="N44" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O44" s="7">
-        <v>287667</v>
-      </c>
-      <c r="P44" s="8">
-        <v>45832.125</v>
-      </c>
-      <c r="Q44" s="9">
-        <v>46153.333333333336</v>
-      </c>
-      <c r="R44" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S44" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="T44" s="6" t="s">
-        <v>413</v>
-      </c>
       <c r="U44" s="6" t="s">
         <v>65</v>
       </c>
@@ -9084,28 +9066,28 @@
         <v>65</v>
       </c>
       <c r="Z44" s="10">
-        <v>0</v>
+        <v>170.96</v>
       </c>
       <c r="AA44" s="10">
         <v>0</v>
       </c>
       <c r="AB44" s="10">
-        <v>0</v>
+        <v>170.96</v>
       </c>
       <c r="AC44" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="AD44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE44" s="8">
-        <v>46153.458333333336</v>
+        <v>46153.75</v>
       </c>
       <c r="AF44" s="7">
-        <v>118640</v>
+        <v>57766</v>
       </c>
       <c r="AG44" s="9">
-        <v>46175.3575</v>
+        <v>46185.45006944444</v>
       </c>
       <c r="AH44" s="6" t="s">
         <v>65</v>
@@ -9114,13 +9096,13 @@
         <v>78</v>
       </c>
       <c r="AJ44" s="11">
-        <v>0.012903225806451</v>
+        <v>0</v>
       </c>
       <c r="AK44" s="6" t="s">
-        <v>136</v>
+        <v>346</v>
       </c>
       <c r="AL44" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM44" s="6" t="s">
         <v>65</v>
@@ -9132,19 +9114,19 @@
         <v>65</v>
       </c>
       <c r="AP44" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="AQ44" s="10">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="AQ44" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS44" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AT44" s="7">
-        <v>2349</v>
+        <v>2018</v>
       </c>
       <c r="AU44" s="6" t="s">
         <v>82</v>
@@ -9153,7 +9135,7 @@
         <v>83</v>
       </c>
       <c r="AW44" s="6" t="s">
-        <v>419</v>
+        <v>65</v>
       </c>
       <c r="AX44" s="6" t="s">
         <v>117</v>
@@ -9165,25 +9147,25 @@
         <v>65</v>
       </c>
       <c r="BA44" s="8">
-        <v>46209.99998842592</v>
+        <v>46237.99998842592</v>
       </c>
       <c r="BB44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC44" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="BD44" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE44" s="10">
-        <v>52700</v>
+        <v>347</v>
+      </c>
+      <c r="BD44" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE44" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF44" s="10">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="BG44" s="10">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="BH44" s="6" t="s">
         <v>420</v>
@@ -9197,16 +9179,16 @@
     </row>
     <row r="45">
       <c r="A45" s="7">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="B45" s="7">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>421</v>
       </c>
       <c r="D45" s="8">
-        <v>46101.54787534722</v>
+        <v>46160.53526894676</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>422</v>
@@ -9239,19 +9221,19 @@
         <v>65</v>
       </c>
       <c r="O45" s="7">
-        <v>337543</v>
+        <v>347450</v>
       </c>
       <c r="P45" s="8" t="s">
         <v>65</v>
       </c>
       <c r="Q45" s="9">
-        <v>46147.625</v>
+        <v>46154.333333333336</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S45" s="6" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="T45" s="6" t="s">
         <v>421</v>
@@ -9281,19 +9263,19 @@
         <v>0</v>
       </c>
       <c r="AC45" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD45" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE45" s="8">
-        <v>46153.75</v>
+        <v>46154.458333333336</v>
       </c>
       <c r="AF45" s="7">
-        <v>55000</v>
+        <v>1</v>
       </c>
       <c r="AG45" s="9">
-        <v>46147.625</v>
+        <v>46154.333333333336</v>
       </c>
       <c r="AH45" s="6" t="s">
         <v>65</v>
@@ -9305,7 +9287,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="6" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="AL45" s="6" t="s">
         <v>423</v>
@@ -9320,7 +9302,7 @@
         <v>65</v>
       </c>
       <c r="AP45" s="6" t="s">
-        <v>239</v>
+        <v>92</v>
       </c>
       <c r="AQ45" s="10" t="s">
         <v>65</v>
@@ -9329,7 +9311,7 @@
         <v>65</v>
       </c>
       <c r="AS45" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AT45" s="7">
         <v>0</v>
@@ -9350,7 +9332,7 @@
         <v>118</v>
       </c>
       <c r="AZ45" s="6" t="s">
-        <v>65</v>
+        <v>428</v>
       </c>
       <c r="BA45" s="8">
         <v>46237.99998842592</v>
@@ -9359,7 +9341,7 @@
         <v>65</v>
       </c>
       <c r="BC45" s="6" t="s">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="BD45" s="10" t="s">
         <v>65</v>
@@ -9368,16 +9350,16 @@
         <v>65</v>
       </c>
       <c r="BF45" s="10">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="BG45" s="10">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="BH45" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="BI45" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="BJ45" s="6" t="s">
         <v>89</v>
@@ -9385,25 +9367,25 @@
     </row>
     <row r="46">
       <c r="A46" s="7">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="B46" s="7">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D46" s="8">
-        <v>46160.53526894676</v>
+        <v>46160.537332175925</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>65</v>
@@ -9412,7 +9394,7 @@
         <v>342</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>342</v>
@@ -9421,28 +9403,28 @@
         <v>65</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O46" s="7">
-        <v>347450</v>
-      </c>
-      <c r="P46" s="8" t="s">
-        <v>65</v>
+        <v>347451</v>
+      </c>
+      <c r="P46" s="8">
+        <v>45061.125</v>
       </c>
       <c r="Q46" s="9">
-        <v>46154.333333333336</v>
+        <v>46157.416666666664</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S46" s="6" t="s">
-        <v>433</v>
+        <v>92</v>
       </c>
       <c r="T46" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>65</v>
@@ -9460,28 +9442,28 @@
         <v>65</v>
       </c>
       <c r="Z46" s="10">
-        <v>0</v>
+        <v>266.88</v>
       </c>
       <c r="AA46" s="10">
         <v>0</v>
       </c>
       <c r="AB46" s="10">
-        <v>0</v>
+        <v>266.88</v>
       </c>
       <c r="AC46" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE46" s="8">
-        <v>46154.458333333336</v>
+        <v>46157.541666666664</v>
       </c>
       <c r="AF46" s="7">
-        <v>1</v>
+        <v>216396</v>
       </c>
       <c r="AG46" s="9">
-        <v>46154.333333333336</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH46" s="6" t="s">
         <v>65</v>
@@ -9490,13 +9472,13 @@
         <v>78</v>
       </c>
       <c r="AJ46" s="11">
-        <v>0</v>
+        <v>0.015662650602409</v>
       </c>
       <c r="AK46" s="6" t="s">
-        <v>385</v>
+        <v>105</v>
       </c>
       <c r="AL46" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AM46" s="6" t="s">
         <v>65</v>
@@ -9508,19 +9490,19 @@
         <v>65</v>
       </c>
       <c r="AP46" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="AQ46" s="10" t="s">
-        <v>65</v>
+        <v>92</v>
+      </c>
+      <c r="AQ46" s="10">
+        <v>0</v>
       </c>
       <c r="AR46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS46" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AT46" s="7">
-        <v>0</v>
+        <v>3027</v>
       </c>
       <c r="AU46" s="6" t="s">
         <v>82</v>
@@ -9538,7 +9520,7 @@
         <v>118</v>
       </c>
       <c r="AZ46" s="6" t="s">
-        <v>435</v>
+        <v>65</v>
       </c>
       <c r="BA46" s="8">
         <v>46237.99998842592</v>
@@ -9547,19 +9529,19 @@
         <v>65</v>
       </c>
       <c r="BC46" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="BD46" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE46" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD46" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE46" s="10">
+        <v>41500</v>
       </c>
       <c r="BF46" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BG46" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BH46" s="6" t="s">
         <v>436</v>
@@ -9573,16 +9555,16 @@
     </row>
     <row r="47">
       <c r="A47" s="7">
-        <v>2020</v>
+        <v>2027</v>
       </c>
       <c r="B47" s="7">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>437</v>
       </c>
       <c r="D47" s="8">
-        <v>46160.537332175925</v>
+        <v>46160.53851987269</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>438</v>
@@ -9615,19 +9597,19 @@
         <v>65</v>
       </c>
       <c r="O47" s="7">
-        <v>347451</v>
-      </c>
-      <c r="P47" s="8">
-        <v>45061.125</v>
+        <v>347452</v>
+      </c>
+      <c r="P47" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="Q47" s="9">
-        <v>46157.416666666664</v>
+        <v>46158.333333333336</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S47" s="6" t="s">
-        <v>105</v>
+        <v>426</v>
       </c>
       <c r="T47" s="6" t="s">
         <v>437</v>
@@ -9648,28 +9630,28 @@
         <v>65</v>
       </c>
       <c r="Z47" s="10">
-        <v>266.88</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="10">
         <v>0</v>
       </c>
       <c r="AB47" s="10">
-        <v>266.88</v>
+        <v>0</v>
       </c>
       <c r="AC47" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD47" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE47" s="8">
-        <v>46157.541666666664</v>
+        <v>46158.458333333336</v>
       </c>
       <c r="AF47" s="7">
-        <v>216088</v>
+        <v>1</v>
       </c>
       <c r="AG47" s="9">
-        <v>46176.428391203706</v>
+        <v>46158.333333333336</v>
       </c>
       <c r="AH47" s="6" t="s">
         <v>65</v>
@@ -9678,10 +9660,10 @@
         <v>78</v>
       </c>
       <c r="AJ47" s="11">
-        <v>0.015662650602409</v>
+        <v>0</v>
       </c>
       <c r="AK47" s="6" t="s">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="AL47" s="6" t="s">
         <v>439</v>
@@ -9696,10 +9678,10 @@
         <v>65</v>
       </c>
       <c r="AP47" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="AQ47" s="10">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="AQ47" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR47" s="6" t="s">
         <v>65</v>
@@ -9708,7 +9690,7 @@
         <v>442</v>
       </c>
       <c r="AT47" s="7">
-        <v>3849</v>
+        <v>0</v>
       </c>
       <c r="AU47" s="6" t="s">
         <v>82</v>
@@ -9726,7 +9708,7 @@
         <v>118</v>
       </c>
       <c r="AZ47" s="6" t="s">
-        <v>65</v>
+        <v>428</v>
       </c>
       <c r="BA47" s="8">
         <v>46237.99998842592</v>
@@ -9735,19 +9717,19 @@
         <v>65</v>
       </c>
       <c r="BC47" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD47" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE47" s="10">
-        <v>41500</v>
+        <v>386</v>
+      </c>
+      <c r="BD47" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE47" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF47" s="10">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="BG47" s="10">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="BH47" s="6" t="s">
         <v>443</v>
@@ -9761,16 +9743,16 @@
     </row>
     <row r="48">
       <c r="A48" s="7">
-        <v>2027</v>
+        <v>2021</v>
       </c>
       <c r="B48" s="7">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>444</v>
       </c>
       <c r="D48" s="8">
-        <v>46160.53851987269</v>
+        <v>46003.72969502315</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>445</v>
@@ -9785,13 +9767,13 @@
         <v>65</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>342</v>
+        <v>254</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>447</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>342</v>
+        <v>254</v>
       </c>
       <c r="L48" s="6" t="s">
         <v>65</v>
@@ -9803,19 +9785,19 @@
         <v>65</v>
       </c>
       <c r="O48" s="7">
-        <v>347452</v>
-      </c>
-      <c r="P48" s="8" t="s">
-        <v>65</v>
+        <v>320775</v>
+      </c>
+      <c r="P48" s="8">
+        <v>36526.083333333336</v>
       </c>
       <c r="Q48" s="9">
-        <v>46158.333333333336</v>
+        <v>46160.336805555555</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S48" s="6" t="s">
-        <v>433</v>
+        <v>92</v>
       </c>
       <c r="T48" s="6" t="s">
         <v>444</v>
@@ -9836,28 +9818,28 @@
         <v>65</v>
       </c>
       <c r="Z48" s="10">
-        <v>0</v>
+        <v>280.3</v>
       </c>
       <c r="AA48" s="10">
         <v>0</v>
       </c>
       <c r="AB48" s="10">
-        <v>0</v>
+        <v>280.3</v>
       </c>
       <c r="AC48" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE48" s="8">
-        <v>46158.458333333336</v>
+        <v>46160.461805555555</v>
       </c>
       <c r="AF48" s="7">
-        <v>1</v>
+        <v>30085</v>
       </c>
       <c r="AG48" s="9">
-        <v>46158.333333333336</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH48" s="6" t="s">
         <v>65</v>
@@ -9866,10 +9848,10 @@
         <v>78</v>
       </c>
       <c r="AJ48" s="11">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="AK48" s="6" t="s">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="AL48" s="6" t="s">
         <v>446</v>
@@ -9884,19 +9866,19 @@
         <v>65</v>
       </c>
       <c r="AP48" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="AQ48" s="10" t="s">
-        <v>65</v>
+        <v>177</v>
+      </c>
+      <c r="AQ48" s="10">
+        <v>0</v>
       </c>
       <c r="AR48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS48" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AT48" s="7">
-        <v>0</v>
+        <v>-174927</v>
       </c>
       <c r="AU48" s="6" t="s">
         <v>82</v>
@@ -9905,7 +9887,7 @@
         <v>83</v>
       </c>
       <c r="AW48" s="6" t="s">
-        <v>65</v>
+        <v>451</v>
       </c>
       <c r="AX48" s="6" t="s">
         <v>117</v>
@@ -9914,34 +9896,34 @@
         <v>118</v>
       </c>
       <c r="AZ48" s="6" t="s">
-        <v>435</v>
+        <v>65</v>
       </c>
       <c r="BA48" s="8">
-        <v>46237.99998842592</v>
+        <v>46216.99998842592</v>
       </c>
       <c r="BB48" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC48" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="BD48" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE48" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD48" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE48" s="10">
+        <v>1</v>
       </c>
       <c r="BF48" s="10">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="BG48" s="10">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="BH48" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BI48" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BJ48" s="6" t="s">
         <v>89</v>
@@ -9949,25 +9931,25 @@
     </row>
     <row r="49">
       <c r="A49" s="7">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B49" s="7">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D49" s="8">
-        <v>46003.72969502315</v>
+        <v>46057.51524019676</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>65</v>
@@ -9976,7 +9958,7 @@
         <v>254</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>254</v>
@@ -9985,28 +9967,28 @@
         <v>65</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O49" s="7">
-        <v>320775</v>
+        <v>329595</v>
       </c>
       <c r="P49" s="8">
-        <v>36526.083333333336</v>
+        <v>45934.125</v>
       </c>
       <c r="Q49" s="9">
-        <v>46160.336805555555</v>
+        <v>46160.375</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S49" s="6" t="s">
-        <v>105</v>
+        <v>458</v>
       </c>
       <c r="T49" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="U49" s="6" t="s">
         <v>65</v>
@@ -10024,28 +10006,28 @@
         <v>65</v>
       </c>
       <c r="Z49" s="10">
-        <v>280.3</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="10">
         <v>0</v>
       </c>
       <c r="AB49" s="10">
-        <v>280.3</v>
+        <v>0</v>
       </c>
       <c r="AC49" s="6" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="AD49" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE49" s="8">
-        <v>46160.461805555555</v>
+        <v>46160.5</v>
       </c>
       <c r="AF49" s="7">
-        <v>193340</v>
+        <v>135595</v>
       </c>
       <c r="AG49" s="9">
-        <v>46176.39202546296</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH49" s="6" t="s">
         <v>65</v>
@@ -10054,13 +10036,13 @@
         <v>78</v>
       </c>
       <c r="AJ49" s="11">
-        <v>630</v>
+        <v>0.013359528487229</v>
       </c>
       <c r="AK49" s="6" t="s">
-        <v>456</v>
+        <v>137</v>
       </c>
       <c r="AL49" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AM49" s="6" t="s">
         <v>65</v>
@@ -10072,7 +10054,7 @@
         <v>65</v>
       </c>
       <c r="AP49" s="6" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="AQ49" s="10">
         <v>0</v>
@@ -10081,10 +10063,10 @@
         <v>65</v>
       </c>
       <c r="AS49" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AT49" s="7">
-        <v>907</v>
+        <v>2682</v>
       </c>
       <c r="AU49" s="6" t="s">
         <v>82</v>
@@ -10093,7 +10075,7 @@
         <v>83</v>
       </c>
       <c r="AW49" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AX49" s="6" t="s">
         <v>117</v>
@@ -10111,287 +10093,99 @@
         <v>65</v>
       </c>
       <c r="BC49" s="6" t="s">
-        <v>87</v>
+        <v>412</v>
       </c>
       <c r="BD49" s="10">
         <v>0</v>
       </c>
       <c r="BE49" s="10">
-        <v>1</v>
+        <v>50900</v>
       </c>
       <c r="BF49" s="10">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="BG49" s="10">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="BH49" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="BI49" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="BJ49" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="7">
-        <v>2023</v>
-      </c>
-      <c r="B50" s="7">
-        <v>2022</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D50" s="8">
-        <v>46057.51524019676</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M50" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="N50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O50" s="7">
-        <v>329595</v>
-      </c>
-      <c r="P50" s="8">
-        <v>45934.125</v>
-      </c>
-      <c r="Q50" s="9">
-        <v>46160.375</v>
-      </c>
-      <c r="R50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S50" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="T50" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="U50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="V50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="W50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z50" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB50" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC50" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AD50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE50" s="8">
-        <v>46160.5</v>
-      </c>
-      <c r="AF50" s="7">
-        <v>134362</v>
-      </c>
-      <c r="AG50" s="9">
-        <v>46175.357511574075</v>
-      </c>
-      <c r="AH50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI50" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ50" s="11">
-        <v>0.013359528487229</v>
-      </c>
-      <c r="AK50" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="AL50" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="AM50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP50" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="AQ50" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS50" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="AT50" s="7">
-        <v>2003</v>
-      </c>
-      <c r="AU50" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV50" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW50" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="AX50" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY50" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="BA50" s="8">
-        <v>46216.99998842592</v>
-      </c>
-      <c r="BB50" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="BC50" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="BD50" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE50" s="10">
-        <v>50900</v>
-      </c>
-      <c r="BF50" s="10">
-        <v>680</v>
-      </c>
-      <c r="BG50" s="10">
-        <v>680</v>
-      </c>
-      <c r="BH50" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="BI50" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="BJ50" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="51" ht="23" customHeight="1">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="12"/>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="14"/>
-      <c r="Q51" s="15"/>
-      <c r="R51" s="12"/>
-      <c r="S51" s="12"/>
-      <c r="T51" s="12"/>
-      <c r="U51" s="12"/>
-      <c r="V51" s="12"/>
-      <c r="W51" s="12"/>
-      <c r="X51" s="12"/>
-      <c r="Y51" s="12"/>
-      <c r="Z51" s="16">
-        <f>SUM(Z6:Z50)</f>
-      </c>
-      <c r="AA51" s="16">
-        <f>SUM(AA6:AA50)</f>
-      </c>
-      <c r="AB51" s="16">
-        <f>SUM(AB6:AB50)</f>
-      </c>
-      <c r="AC51" s="12"/>
-      <c r="AD51" s="12"/>
-      <c r="AE51" s="14"/>
-      <c r="AF51" s="13"/>
-      <c r="AG51" s="15"/>
-      <c r="AH51" s="12"/>
-      <c r="AI51" s="12"/>
-      <c r="AJ51" s="17"/>
-      <c r="AK51" s="12"/>
-      <c r="AL51" s="12"/>
-      <c r="AM51" s="12"/>
-      <c r="AN51" s="12"/>
-      <c r="AO51" s="12"/>
-      <c r="AP51" s="12"/>
-      <c r="AQ51" s="16"/>
-      <c r="AR51" s="12"/>
-      <c r="AS51" s="12"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="12"/>
-      <c r="AV51" s="12"/>
-      <c r="AW51" s="12"/>
-      <c r="AX51" s="12"/>
-      <c r="AY51" s="12"/>
-      <c r="AZ51" s="12"/>
-      <c r="BA51" s="14"/>
-      <c r="BB51" s="15"/>
-      <c r="BC51" s="12"/>
-      <c r="BD51" s="16"/>
-      <c r="BE51" s="16"/>
-      <c r="BF51" s="16"/>
-      <c r="BG51" s="16"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51" s="12"/>
-      <c r="BJ51" s="12"/>
+    <row r="50" ht="23" customHeight="1">
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="12"/>
+      <c r="M50" s="12"/>
+      <c r="N50" s="12"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="14"/>
+      <c r="Q50" s="15"/>
+      <c r="R50" s="12"/>
+      <c r="S50" s="12"/>
+      <c r="T50" s="12"/>
+      <c r="U50" s="12"/>
+      <c r="V50" s="12"/>
+      <c r="W50" s="12"/>
+      <c r="X50" s="12"/>
+      <c r="Y50" s="12"/>
+      <c r="Z50" s="16">
+        <f>SUM(Z6:Z49)</f>
+      </c>
+      <c r="AA50" s="16">
+        <f>SUM(AA6:AA49)</f>
+      </c>
+      <c r="AB50" s="16">
+        <f>SUM(AB6:AB49)</f>
+      </c>
+      <c r="AC50" s="12"/>
+      <c r="AD50" s="12"/>
+      <c r="AE50" s="14"/>
+      <c r="AF50" s="13"/>
+      <c r="AG50" s="15"/>
+      <c r="AH50" s="12"/>
+      <c r="AI50" s="12"/>
+      <c r="AJ50" s="17"/>
+      <c r="AK50" s="12"/>
+      <c r="AL50" s="12"/>
+      <c r="AM50" s="12"/>
+      <c r="AN50" s="12"/>
+      <c r="AO50" s="12"/>
+      <c r="AP50" s="12"/>
+      <c r="AQ50" s="16"/>
+      <c r="AR50" s="12"/>
+      <c r="AS50" s="12"/>
+      <c r="AT50" s="13"/>
+      <c r="AU50" s="12"/>
+      <c r="AV50" s="12"/>
+      <c r="AW50" s="12"/>
+      <c r="AX50" s="12"/>
+      <c r="AY50" s="12"/>
+      <c r="AZ50" s="12"/>
+      <c r="BA50" s="14"/>
+      <c r="BB50" s="15"/>
+      <c r="BC50" s="12"/>
+      <c r="BD50" s="16"/>
+      <c r="BE50" s="16"/>
+      <c r="BF50" s="16"/>
+      <c r="BG50" s="16"/>
+      <c r="BH50" s="12"/>
+      <c r="BI50" s="12"/>
+      <c r="BJ50" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:BJ5"/>
